--- a/data/ai-tools.xlsx
+++ b/data/ai-tools.xlsx
@@ -8,7 +8,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カテゴリ一覧" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AIツール一覧'!$A$1:$L$993</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AIツール一覧'!$A$1:$O$993</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="29" min="1" max="1"/>
@@ -689,65 +689,75 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>英語の列</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>サイトを英語に切り替えたときに使います。「AI名（英語）」「無料利用範囲（英語）」は空欄なら日本語版・標準の文が使われます。「強み（英語）」は日本語の強みと同じく4行で入れてください。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>サイトに反映する手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>このファイルを保存します（ファイル名は ai-tools.xlsx のまま）。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>GitHubのリポジトリで data フォルダを開き、「Add file」→「Upload files」でこのファイルをアップロードして「Commit changes」を押します。</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>このファイルを保存します（ファイル名は ai-tools.xlsx のまま）。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>「Actions」タブで「ExcelからJSONに変換」が緑の ✓ になれば完了です。数分でサイトに反映されます。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>GitHubのリポジトリで data フォルダを開き、「Add file」→「Upload files」でこのファイルをアップロードして「Commit changes」を押します。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="29">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>「Actions」タブで「ExcelからJSONに変換」が緑の ✓ になれば完了です。数分でサイトに反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="29">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>赤い ✕ になった場合は、入力ミスがあります。✕ をクリックすると、何行目のどこが間違っているかが表示されます。サイトは前の状態のまま壊れません。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="29"/>
     <row r="23" ht="15.75" customHeight="1" s="29"/>
     <row r="24" ht="15.75" customHeight="1" s="29"/>
     <row r="25" ht="15.75" customHeight="1" s="29"/>
@@ -1743,7 +1753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L993"/>
+  <dimension ref="A1:O993"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24" customWidth="1" style="29" min="1" max="1"/>
@@ -1758,6 +1768,9 @@
     <col width="9" customWidth="1" style="29" min="10" max="10"/>
     <col width="10" customWidth="1" style="29" min="11" max="11"/>
     <col width="13" customWidth="1" style="29" min="12" max="26"/>
+    <col width="26" customWidth="1" style="29" min="13" max="13"/>
+    <col width="52" customWidth="1" style="29" min="14" max="14"/>
+    <col width="34" customWidth="1" style="29" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="29">
@@ -1821,6 +1834,21 @@
           <t>対応端末</t>
         </is>
       </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>AI名（英語）</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>強み（英語）</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>無料利用範囲（英語）</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="66" customHeight="1" s="29">
       <c r="A2" s="30" t="inlineStr">
@@ -1884,6 +1912,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M2" s="32" t="n"/>
+      <c r="N2" s="32" t="inlineStr">
+        <is>
+          <t>Chat, writing, summaries and translation in one
+Generates and understands images
+Analyzes uploaded PDFs and Excel files
+Voice conversation in the mobile app</t>
+        </is>
+      </c>
+      <c r="O2" s="32" t="n"/>
     </row>
     <row r="3" ht="66" customHeight="1" s="29">
       <c r="A3" s="30" t="inlineStr">
@@ -1943,6 +1981,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M3" s="32" t="n"/>
+      <c r="N3" s="32" t="inlineStr">
+        <is>
+          <t>Reads very long documents at once
+Natural, careful writing
+Strong at writing and fixing code
+Builds working apps and diagrams on screen</t>
+        </is>
+      </c>
+      <c r="O3" s="32" t="n"/>
     </row>
     <row r="4" ht="66" customHeight="1" s="29">
       <c r="A4" s="30" t="inlineStr">
@@ -2002,6 +2050,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="inlineStr">
+        <is>
+          <t>Works with Gmail, Drive and YouTube
+Uses Google Search for up-to-date answers
+Image and video generation (Imagen, Veo)
+Deep Research reports</t>
+        </is>
+      </c>
+      <c r="O4" s="33" t="n"/>
     </row>
     <row r="5" ht="66" customHeight="1" s="29">
       <c r="A5" s="30" t="inlineStr">
@@ -2065,6 +2123,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="inlineStr">
+        <is>
+          <t>Answers with sources from Bing search
+Free image generation
+Built into Windows and Edge
+Voice conversation</t>
+        </is>
+      </c>
+      <c r="O5" s="33" t="inlineStr">
+        <is>
+          <t>Free with a Microsoft account</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="66" customHeight="1" s="29">
       <c r="A6" s="30" t="inlineStr">
@@ -2124,6 +2196,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="inlineStr">
+        <is>
+          <t>Available in Instagram, WhatsApp and Messenger
+Image generation and editing
+Free to chat
+Powered by Llama models</t>
+        </is>
+      </c>
+      <c r="O6" s="33" t="n"/>
     </row>
     <row r="7" ht="66" customHeight="1" s="29">
       <c r="A7" s="30" t="inlineStr">
@@ -2183,6 +2265,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M7" s="33" t="n"/>
+      <c r="N7" s="33" t="inlineStr">
+        <is>
+          <t>Answers on trending topics using posts on X
+Image generation and editing
+Web and mobile apps
+Deep reasoning mode</t>
+        </is>
+      </c>
+      <c r="O7" s="33" t="n"/>
     </row>
     <row r="8" ht="66" customHeight="1" s="29">
       <c r="A8" s="30" t="inlineStr">
@@ -2246,6 +2338,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M8" s="32" t="n"/>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>Shows source links for every answer
+Summarizes many websites at once
+Search focused on papers or news
+In-depth Research mode</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="n"/>
     </row>
     <row r="9" ht="66" customHeight="1" s="29">
       <c r="A9" s="30" t="inlineStr">
@@ -2305,6 +2407,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M9" s="32" t="n"/>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>Strong at math and logical reasoning
+Good at writing code
+Free on web and app
+Open-weight models</t>
+        </is>
+      </c>
+      <c r="O9" s="32" t="n"/>
     </row>
     <row r="10" ht="66" customHeight="1" s="29">
       <c r="A10" s="30" t="inlineStr">
@@ -2362,6 +2474,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M10" s="32" t="inlineStr">
+        <is>
+          <t>Qwen Chat</t>
+        </is>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>Reads long documents
+Image and video generation
+Builds web pages and apps
+Many languages supported</t>
+        </is>
+      </c>
+      <c r="O10" s="32" t="n"/>
     </row>
     <row r="11" ht="66" customHeight="1" s="29">
       <c r="A11" s="30" t="inlineStr">
@@ -2419,6 +2545,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M11" s="32" t="n"/>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>Reads very long documents and many files
+Searches the web and summarizes
+Creates slide decks
+Free reasoning model</t>
+        </is>
+      </c>
+      <c r="O11" s="32" t="n"/>
     </row>
     <row r="12" ht="66" customHeight="1" s="29">
       <c r="A12" s="30" t="inlineStr">
@@ -2476,6 +2612,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M12" s="32" t="inlineStr">
+        <is>
+          <t>Doubao</t>
+        </is>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
+        <is>
+          <t>Popular AI assistant in China
+Natural voice conversation
+Image generation and photo editing
+Writing and translation</t>
+        </is>
+      </c>
+      <c r="O12" s="32" t="n"/>
     </row>
     <row r="13" ht="66" customHeight="1" s="29">
       <c r="A13" s="30" t="inlineStr">
@@ -2533,6 +2683,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>ERNIE Bot</t>
+        </is>
+      </c>
+      <c r="N13" s="32" t="inlineStr">
+        <is>
+          <t>Integrated with Baidu search
+Strong in Chinese text and knowledge
+Image generation
+Free for personal use</t>
+        </is>
+      </c>
+      <c r="O13" s="32" t="n"/>
     </row>
     <row r="14" ht="66" customHeight="1" s="29">
       <c r="A14" s="22" t="inlineStr">
@@ -2590,6 +2754,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>ChatGLM (Zhipu Qingyan)</t>
+        </is>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>GLM models from Tsinghua University
+Chinese conversation and writing
+Web search and file reading
+Agent features</t>
+        </is>
+      </c>
+      <c r="O14" s="32" t="n"/>
     </row>
     <row r="15" ht="66" customHeight="1" s="29">
       <c r="A15" s="22" t="inlineStr">
@@ -2647,6 +2825,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M15" s="33" t="inlineStr">
+        <is>
+          <t>Tencent Yuanbao</t>
+        </is>
+      </c>
+      <c r="N15" s="33" t="inlineStr">
+        <is>
+          <t>Searches WeChat articles
+Switch between DeepSeek and Hunyuan
+File summaries
+Free to use</t>
+        </is>
+      </c>
+      <c r="O15" s="33" t="n"/>
     </row>
     <row r="16" ht="66" customHeight="1" s="29">
       <c r="A16" s="22" t="inlineStr">
@@ -2704,6 +2896,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>iFlytek Spark</t>
+        </is>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>Strong speech recognition and synthesis
+Chinese–English translation
+Education and office features
+Writing help</t>
+        </is>
+      </c>
+      <c r="O16" s="32" t="n"/>
     </row>
     <row r="17" ht="66" customHeight="1" s="29">
       <c r="A17" s="30" t="inlineStr">
@@ -2761,6 +2967,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>Very fast responses
+Web search with sources
+Image generation
+European privacy standards</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="n"/>
     </row>
     <row r="18" ht="66" customHeight="1" s="29">
       <c r="A18" s="30" t="inlineStr">
@@ -2818,6 +3034,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="33" t="inlineStr">
+        <is>
+          <t>Switch between ChatGPT, Claude, Gemini and more
+Easy to compare answers
+Create your own bots
+Mobile app</t>
+        </is>
+      </c>
+      <c r="O18" s="33" t="n"/>
     </row>
     <row r="19" ht="66" customHeight="1" s="29">
       <c r="A19" s="30" t="inlineStr">
@@ -2875,6 +3101,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M19" s="32" t="n"/>
+      <c r="N19" s="32" t="inlineStr">
+        <is>
+          <t>Empathetic conversation partner
+Gentle chat and advice
+Voice conversation
+Try it without signing up</t>
+        </is>
+      </c>
+      <c r="O19" s="32" t="n"/>
     </row>
     <row r="20" ht="66" customHeight="1" s="29">
       <c r="A20" s="30" t="inlineStr">
@@ -2936,6 +3172,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="inlineStr">
+        <is>
+          <t>AI search with sources
+Research mode
+Choose from several AI models
+Ask questions about uploaded files</t>
+        </is>
+      </c>
+      <c r="O20" s="33" t="n"/>
     </row>
     <row r="21" ht="66" customHeight="1" s="29">
       <c r="A21" s="30" t="inlineStr">
@@ -2993,6 +3239,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M21" s="32" t="n"/>
+      <c r="N21" s="32" t="inlineStr">
+        <is>
+          <t>Builds summary pages from search results
+Creates slides, sheets and documents
+Agents that can make calls
+Combines several AIs</t>
+        </is>
+      </c>
+      <c r="O21" s="32" t="n"/>
     </row>
     <row r="22" ht="66" customHeight="1" s="29">
       <c r="A22" s="30" t="inlineStr">
@@ -3050,6 +3306,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M22" s="32" t="n"/>
+      <c r="N22" s="32" t="inlineStr">
+        <is>
+          <t>AI search made in Japan
+Answers with sources in many languages
+Turns results into slides or mind maps
+Summarizes and translates multilingual info</t>
+        </is>
+      </c>
+      <c r="O22" s="32" t="n"/>
     </row>
     <row r="23" ht="66" customHeight="1" s="29">
       <c r="A23" s="30" t="inlineStr">
@@ -3107,6 +3373,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="32" t="inlineStr">
+        <is>
+          <t>Plans and carries out tasks on its own
+Creates reports and websites
+You can watch its progress
+Handles multi-step tasks</t>
+        </is>
+      </c>
+      <c r="O23" s="32" t="n"/>
     </row>
     <row r="24" ht="66" customHeight="1" s="29">
       <c r="A24" s="30" t="inlineStr">
@@ -3164,6 +3440,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M24" s="32" t="n"/>
+      <c r="N24" s="32" t="inlineStr">
+        <is>
+          <t>Browser extension that summarizes pages
+Summarizes YouTube videos
+Translation and rewriting
+Access to several AI models</t>
+        </is>
+      </c>
+      <c r="O24" s="32" t="n"/>
     </row>
     <row r="25" ht="66" customHeight="1" s="29">
       <c r="A25" s="30" t="inlineStr">
@@ -3221,6 +3507,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M25" s="32" t="n"/>
+      <c r="N25" s="32" t="inlineStr">
+        <is>
+          <t>Russian conversation and writing
+Image generation (Kandinsky)
+Made by Sber
+Free to use</t>
+        </is>
+      </c>
+      <c r="O25" s="32" t="n"/>
     </row>
     <row r="26" ht="66" customHeight="1" s="29">
       <c r="A26" s="30" t="inlineStr">
@@ -3278,6 +3574,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M26" s="32" t="n"/>
+      <c r="N26" s="32" t="inlineStr">
+        <is>
+          <t>Russian voice assistant
+Works with Yandex search
+Smart speaker support
+Writing help</t>
+        </is>
+      </c>
+      <c r="O26" s="32" t="n"/>
     </row>
     <row r="27" ht="66" customHeight="1" s="29">
       <c r="A27" s="30" t="inlineStr">
@@ -3335,6 +3641,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M27" s="32" t="inlineStr">
+        <is>
+          <t>Wrtn</t>
+        </is>
+      </c>
+      <c r="N27" s="32" t="inlineStr">
+        <is>
+          <t>Latest AI models for free
+Japanese interface available
+Image generation
+Collection of AI tools by purpose</t>
+        </is>
+      </c>
+      <c r="O27" s="32" t="n"/>
     </row>
     <row r="28" ht="66" customHeight="1" s="29">
       <c r="A28" s="30" t="inlineStr">
@@ -3396,6 +3716,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="33" t="inlineStr">
+        <is>
+          <t>Built into the Brave browser
+Summarizes pages and videos
+Does not store chat history
+Usable without an account</t>
+        </is>
+      </c>
+      <c r="O28" s="33" t="n"/>
     </row>
     <row r="29" ht="66" customHeight="1" s="29">
       <c r="A29" s="22" t="inlineStr">
@@ -3453,6 +3783,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>Metaso AI Search</t>
+        </is>
+      </c>
+      <c r="N29" s="32" t="inlineStr">
+        <is>
+          <t>Ad-free AI search
+Organizes answers as mind maps
+Academic paper search
+Strong for Chinese information</t>
+        </is>
+      </c>
+      <c r="O29" s="32" t="n"/>
     </row>
     <row r="30" ht="66" customHeight="1" s="29">
       <c r="A30" s="30" t="inlineStr">
@@ -3510,6 +3854,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M30" s="32" t="n"/>
+      <c r="N30" s="32" t="inlineStr">
+        <is>
+          <t>Turns research into reports
+Generates slides, sheets and web pages
+Multiple agents work together
+With sources</t>
+        </is>
+      </c>
+      <c r="O30" s="32" t="n"/>
     </row>
     <row r="31" ht="66" customHeight="1" s="29">
       <c r="A31" s="30" t="inlineStr">
@@ -3567,6 +3921,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M31" s="32" t="n"/>
+      <c r="N31" s="32" t="inlineStr">
+        <is>
+          <t>Search with no ads or tracking
+AI summaries of results
+Boost or block sites you choose
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O31" s="32" t="inlineStr">
+        <is>
+          <t>Limited trial searches only (paid after)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="66" customHeight="1" s="29">
       <c r="A32" s="30" t="inlineStr">
@@ -3624,6 +3992,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M32" s="32" t="n"/>
+      <c r="N32" s="32" t="inlineStr">
+        <is>
+          <t>Prioritizes trustworthy sources
+Paper search with citations
+Save highlights from web pages
+Usable in Japanese</t>
+        </is>
+      </c>
+      <c r="O32" s="32" t="n"/>
     </row>
     <row r="33" ht="66" customHeight="1" s="29">
       <c r="A33" s="30" t="inlineStr">
@@ -3681,6 +4059,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M33" s="32" t="n"/>
+      <c r="N33" s="32" t="inlineStr">
+        <is>
+          <t>Predicts and continues your writing
+Agent that operates your browser
+Research and summaries
+Email drafting</t>
+        </is>
+      </c>
+      <c r="O33" s="32" t="n"/>
     </row>
     <row r="34" ht="66" customHeight="1" s="29">
       <c r="A34" s="30" t="inlineStr">
@@ -3738,6 +4126,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="33" t="inlineStr">
+        <is>
+          <t>Meta's flagship open model
+Runs on your PC or server
+Freely customizable
+Commercial use allowed (with conditions)</t>
+        </is>
+      </c>
+      <c r="O34" s="33" t="n"/>
     </row>
     <row r="35" ht="66" customHeight="1" s="29">
       <c r="A35" s="30" t="inlineStr">
@@ -3795,6 +4193,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M35" s="33" t="n"/>
+      <c r="N35" s="33" t="inlineStr">
+        <is>
+          <t>Lightweight open model from Google
+Runs on ordinary PCs
+Versions that understand images
+Small versions for phones</t>
+        </is>
+      </c>
+      <c r="O35" s="33" t="n"/>
     </row>
     <row r="36" ht="66" customHeight="1" s="29">
       <c r="A36" s="30" t="inlineStr">
@@ -3852,6 +4260,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M36" s="33" t="n"/>
+      <c r="N36" s="33" t="inlineStr">
+        <is>
+          <t>Small model from Microsoft
+Runs with little memory
+Good at reasoning and math
+Open weights</t>
+        </is>
+      </c>
+      <c r="O36" s="33" t="n"/>
     </row>
     <row r="37" ht="66" customHeight="1" s="29">
       <c r="A37" s="30" t="inlineStr">
@@ -3909,6 +4327,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M37" s="32" t="n"/>
+      <c r="N37" s="32" t="inlineStr">
+        <is>
+          <t>Training data and methods fully public
+For research and education
+You can retrain it yourself
+Made by a non-profit</t>
+        </is>
+      </c>
+      <c r="O37" s="32" t="n"/>
     </row>
     <row r="38" ht="66" customHeight="1" s="29">
       <c r="A38" s="30" t="inlineStr">
@@ -3966,6 +4394,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="inlineStr">
+        <is>
+          <t>Developed by a UAE research institute
+Open model
+Multilingual including Arabic
+Several sizes from small to large</t>
+        </is>
+      </c>
+      <c r="O38" s="33" t="n"/>
     </row>
     <row r="39" ht="66" customHeight="1" s="29">
       <c r="A39" s="30" t="inlineStr">
@@ -4023,6 +4461,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M39" s="32" t="n"/>
+      <c r="N39" s="32" t="inlineStr">
+        <is>
+          <t>Developed by LG AI Research
+Strong in Korean and English
+High reasoning performance
+Open model</t>
+        </is>
+      </c>
+      <c r="O39" s="32" t="n"/>
     </row>
     <row r="40" ht="66" customHeight="1" s="29">
       <c r="A40" s="30" t="inlineStr">
@@ -4080,6 +4528,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M40" s="33" t="n"/>
+      <c r="N40" s="33" t="inlineStr">
+        <is>
+          <t>Llama and others further trained on Japanese
+Strong Japanese reading and writing
+Openly released
+For research and business</t>
+        </is>
+      </c>
+      <c r="O40" s="33" t="n"/>
     </row>
     <row r="41" hidden="1" ht="66" customHeight="1" s="29">
       <c r="A41" s="30" t="inlineStr">
@@ -4137,6 +4595,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M41" s="32" t="n"/>
+      <c r="N41" s="32" t="inlineStr">
+        <is>
+          <t>Japanese LLM led by the National Institute of Informatics
+Training data is public
+Specialized in Japanese
+For research and development</t>
+        </is>
+      </c>
+      <c r="O41" s="32" t="n"/>
     </row>
     <row r="42" ht="66" customHeight="1" s="29">
       <c r="A42" s="30" t="inlineStr">
@@ -4194,6 +4662,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M42" s="32" t="n"/>
+      <c r="N42" s="32" t="inlineStr">
+        <is>
+          <t>Japanese LLM from a University of Tokyo startup
+Follows Japanese instructions well
+Open models
+Enterprise support</t>
+        </is>
+      </c>
+      <c r="O42" s="32" t="inlineStr">
+        <is>
+          <t>Published models are free</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="66" customHeight="1" s="29">
       <c r="A43" s="30" t="inlineStr">
@@ -4255,6 +4737,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M43" s="32" t="n"/>
+      <c r="N43" s="32" t="inlineStr">
+        <is>
+          <t>Download an AI to your PC with one command
+Works offline
+Supports Llama, Gemma and more
+Other apps can call it</t>
+        </is>
+      </c>
+      <c r="O43" s="32" t="n"/>
     </row>
     <row r="44" ht="66" customHeight="1" s="29">
       <c r="A44" s="30" t="inlineStr">
@@ -4316,6 +4808,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M44" s="32" t="n"/>
+      <c r="N44" s="32" t="inlineStr">
+        <is>
+          <t>Use local AI through a simple interface
+Easy model search and download
+Japanese interface
+No programming needed</t>
+        </is>
+      </c>
+      <c r="O44" s="32" t="n"/>
     </row>
     <row r="45" ht="66" customHeight="1" s="29">
       <c r="A45" s="30" t="inlineStr">
@@ -4377,6 +4879,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M45" s="32" t="n"/>
+      <c r="N45" s="32" t="inlineStr">
+        <is>
+          <t>AI chat that works offline
+Ask questions about your own documents
+Runs on ordinary PCs
+Free and open source</t>
+        </is>
+      </c>
+      <c r="O45" s="32" t="n"/>
     </row>
     <row r="46" ht="66" customHeight="1" s="29">
       <c r="A46" s="30" t="inlineStr">
@@ -4438,6 +4950,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M46" s="33" t="n"/>
+      <c r="N46" s="33" t="inlineStr">
+        <is>
+          <t>ChatGPT-like app for local AI
+Keeps data on your PC
+Open source
+Can connect to online AIs too</t>
+        </is>
+      </c>
+      <c r="O46" s="33" t="n"/>
     </row>
     <row r="47" ht="66" customHeight="1" s="29">
       <c r="A47" s="30" t="inlineStr">
@@ -4495,6 +5017,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M47" s="32" t="n"/>
+      <c r="N47" s="32" t="inlineStr">
+        <is>
+          <t>Your own AI chat interface on a PC or server
+Works with Ollama
+Document search (RAG)
+Multi-user</t>
+        </is>
+      </c>
+      <c r="O47" s="32" t="n"/>
     </row>
     <row r="48" ht="66" customHeight="1" s="29">
       <c r="A48" s="30" t="inlineStr">
@@ -4552,6 +5084,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M48" s="32" t="n"/>
+      <c r="N48" s="32" t="inlineStr">
+        <is>
+          <t>Hundreds of thousands of models and datasets
+Browser demos (Spaces)
+Share and publish models
+AI developer community</t>
+        </is>
+      </c>
+      <c r="O48" s="32" t="n"/>
     </row>
     <row r="49" ht="66" customHeight="1" s="29">
       <c r="A49" s="30" t="inlineStr">
@@ -4609,6 +5151,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M49" s="33" t="n"/>
+      <c r="N49" s="33" t="inlineStr">
+        <is>
+          <t>Try Gemini for free
+Get an API key instantly
+Tune and compare prompts
+Prototype apps by chatting</t>
+        </is>
+      </c>
+      <c r="O49" s="33" t="n"/>
     </row>
     <row r="50" ht="66" customHeight="1" s="29">
       <c r="A50" s="30" t="inlineStr">
@@ -4666,6 +5218,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M50" s="32" t="n"/>
+      <c r="N50" s="32" t="inlineStr">
+        <is>
+          <t>Run Python in your browser
+Free GPU access
+Saves to Google Drive
+Great for training AI</t>
+        </is>
+      </c>
+      <c r="O50" s="32" t="inlineStr">
+        <is>
+          <t>Free GPU with time limits</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="66" customHeight="1" s="29">
       <c r="A51" s="30" t="inlineStr">
@@ -4723,6 +5289,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M51" s="32" t="n"/>
+      <c r="N51" s="32" t="inlineStr">
+        <is>
+          <t>Many free datasets
+Python and GPU in the browser
+Data science competitions
+Learning courses</t>
+        </is>
+      </c>
+      <c r="O51" s="32" t="n"/>
     </row>
     <row r="52" ht="66" customHeight="1" s="29">
       <c r="A52" s="30" t="inlineStr">
@@ -4780,6 +5356,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M52" s="32" t="n"/>
+      <c r="N52" s="32" t="inlineStr">
+        <is>
+          <t>Very fast responses on dedicated chips
+Open models via API
+Free tier
+For real-time uses</t>
+        </is>
+      </c>
+      <c r="O52" s="32" t="n"/>
     </row>
     <row r="53" ht="66" customHeight="1" s="29">
       <c r="A53" s="30" t="inlineStr">
@@ -4837,6 +5423,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M53" s="32" t="n"/>
+      <c r="N53" s="32" t="inlineStr">
+        <is>
+          <t>Hundreds of AI models through one API
+Compare price and speed
+Free models available
+Easy switching</t>
+        </is>
+      </c>
+      <c r="O53" s="32" t="n"/>
     </row>
     <row r="54" ht="66" customHeight="1" s="29">
       <c r="A54" s="30" t="inlineStr">
@@ -4894,6 +5490,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M54" s="32" t="n"/>
+      <c r="N54" s="32" t="inlineStr">
+        <is>
+          <t>Image, video and audio models via API
+Publish your own models
+Pay only for what you use
+Trial usage only</t>
+        </is>
+      </c>
+      <c r="O54" s="32" t="n"/>
     </row>
     <row r="55" ht="66" customHeight="1" s="29">
       <c r="A55" s="30" t="inlineStr">
@@ -4951,6 +5557,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M55" s="32" t="n"/>
+      <c r="N55" s="32" t="inlineStr">
+        <is>
+          <t>Fast API for open models
+Fine-tuning
+GPU rental
+Initial credits only</t>
+        </is>
+      </c>
+      <c r="O55" s="32" t="n"/>
     </row>
     <row r="56" ht="66" customHeight="1" s="29">
       <c r="A56" s="30" t="inlineStr">
@@ -5008,6 +5624,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M56" s="32" t="n"/>
+      <c r="N56" s="32" t="inlineStr">
+        <is>
+          <t>Strong for document search (RAG)
+Multilingual embedding models
+Enterprise-grade safety
+Free trial key</t>
+        </is>
+      </c>
+      <c r="O56" s="32" t="n"/>
     </row>
     <row r="57" ht="66" customHeight="1" s="29">
       <c r="A57" s="30" t="inlineStr">
@@ -5065,6 +5691,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M57" s="32" t="n"/>
+      <c r="N57" s="32" t="inlineStr">
+        <is>
+          <t>Build AI chatbots without code
+Answers from your own documents
+Automate with workflows
+Japanese interface</t>
+        </is>
+      </c>
+      <c r="O57" s="32" t="inlineStr">
+        <is>
+          <t>Free cloud tier; free when self-hosted</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="66" customHeight="1" s="29">
       <c r="A58" s="30" t="inlineStr">
@@ -5122,6 +5762,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M58" s="32" t="n"/>
+      <c r="N58" s="32" t="inlineStr">
+        <is>
+          <t>Build AI apps by connecting blocks
+Supports LangChain
+Runs free on your PC
+Open source</t>
+        </is>
+      </c>
+      <c r="O58" s="32" t="n"/>
     </row>
     <row r="59" ht="66" customHeight="1" s="29">
       <c r="A59" s="30" t="inlineStr">
@@ -5179,6 +5829,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M59" s="33" t="n"/>
+      <c r="N59" s="33" t="inlineStr">
+        <is>
+          <t>Standard library for AI apps
+Connects to tools and data
+Build agents
+Python and JavaScript</t>
+        </is>
+      </c>
+      <c r="O59" s="33" t="n"/>
     </row>
     <row r="60" hidden="1" ht="66" customHeight="1" s="29">
       <c r="A60" s="30" t="inlineStr">
@@ -5236,6 +5896,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M60" s="32" t="n"/>
+      <c r="N60" s="32" t="inlineStr">
+        <is>
+          <t>Lets AI read your documents
+Supports PDFs, databases and more
+Better search accuracy
+Open source</t>
+        </is>
+      </c>
+      <c r="O60" s="32" t="n"/>
     </row>
     <row r="61" ht="66" customHeight="1" s="29">
       <c r="A61" s="30" t="inlineStr">
@@ -5293,6 +5963,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M61" s="32" t="n"/>
+      <c r="N61" s="32" t="inlineStr">
+        <is>
+          <t>Several AIs with different roles work together
+Split work like research then writing
+Built in Python
+Open source</t>
+        </is>
+      </c>
+      <c r="O61" s="32" t="n"/>
     </row>
     <row r="62" ht="66" customHeight="1" s="29">
       <c r="A62" s="30" t="inlineStr">
@@ -5350,6 +6030,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M62" s="32" t="n"/>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>Plans and acts on its own from a goal
+Build agents with blocks
+A pioneer of AI automation
+Open source</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="n"/>
     </row>
     <row r="63" ht="66" customHeight="1" s="29">
       <c r="A63" s="30" t="inlineStr">
@@ -5407,6 +6097,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M63" s="32" t="n"/>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>AI demo interfaces in a few lines of Python
+Share with a public link
+Works with Hugging Face
+Handles image and audio in and out</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="n"/>
     </row>
     <row r="64" ht="66" customHeight="1" s="29">
       <c r="A64" s="30" t="inlineStr">
@@ -5464,6 +6164,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M64" s="33" t="n"/>
+      <c r="N64" s="33" t="inlineStr">
+        <is>
+          <t>Web apps with just Python
+Easy charts and data views
+Free publishing
+Build AI chat interfaces</t>
+        </is>
+      </c>
+      <c r="O64" s="33" t="n"/>
     </row>
     <row r="65" ht="66" customHeight="1" s="29">
       <c r="A65" s="30" t="inlineStr">
@@ -5521,6 +6231,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M65" s="32" t="n"/>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>Standard deep learning framework
+Widely used in research
+GPU support
+Many pretrained models</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="n"/>
     </row>
     <row r="66" ht="66" customHeight="1" s="29">
       <c r="A66" s="30" t="inlineStr">
@@ -5578,6 +6298,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M66" s="33" t="n"/>
+      <c r="N66" s="33" t="inlineStr">
+        <is>
+          <t>Machine learning library from Google
+LiteRT for phones
+Easy to write with Keras
+Plenty of tutorials</t>
+        </is>
+      </c>
+      <c r="O66" s="33" t="n"/>
     </row>
     <row r="67" ht="66" customHeight="1" s="29">
       <c r="A67" s="30" t="inlineStr">
@@ -5635,6 +6365,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M67" s="32" t="n"/>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>Classic library for learning machine learning
+Classification, regression, clustering
+Rich preprocessing tools
+Simple Python API</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="n"/>
     </row>
     <row r="68" ht="66" customHeight="1" s="29">
       <c r="A68" s="30" t="inlineStr">
@@ -5692,6 +6432,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M68" s="32" t="n"/>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>Strong predictions on tabular data
+Fast computation
+Popular in data competitions
+Python and R</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="n"/>
     </row>
     <row r="69" ht="66" customHeight="1" s="29">
       <c r="A69" s="30" t="inlineStr">
@@ -5749,6 +6499,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M69" s="32" t="n"/>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>Notebooks with code and results side by side
+Charts shown inline
+Supports many languages
+Widely used in education</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="n"/>
     </row>
     <row r="70" ht="66" customHeight="1" s="29">
       <c r="A70" s="30" t="inlineStr">
@@ -5806,6 +6566,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M70" s="33" t="n"/>
+      <c r="N70" s="33" t="inlineStr">
+        <is>
+          <t>Automatically logs AI training
+Compare runs in charts
+Share with your team
+Free tier for individuals</t>
+        </is>
+      </c>
+      <c r="O70" s="33" t="n"/>
     </row>
     <row r="71" ht="66" customHeight="1" s="29">
       <c r="A71" s="30" t="inlineStr">
@@ -5863,6 +6633,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M71" s="32" t="n"/>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>Vector database without managing servers
+Fast similarity search
+Ideal for RAG
+Free plan</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n"/>
     </row>
     <row r="72" ht="66" customHeight="1" s="29">
       <c r="A72" s="30" t="inlineStr">
@@ -5920,6 +6700,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M72" s="32" t="n"/>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>Combines vector and keyword search
+Open source
+Cloud version available
+Multilingual</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n"/>
     </row>
     <row r="73" ht="66" customHeight="1" s="29">
       <c r="A73" s="30" t="inlineStr">
@@ -5977,6 +6767,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M73" s="32" t="n"/>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>Fast vector database
+Written in Rust, memory-efficient
+Open source
+Great filtered search</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n"/>
     </row>
     <row r="74" ht="66" customHeight="1" s="29">
       <c r="A74" s="30" t="inlineStr">
@@ -6034,6 +6834,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M74" s="32" t="n"/>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>Easy vector database in a few lines
+Works well with Python
+Runs locally
+Open source</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n"/>
     </row>
     <row r="75" ht="66" customHeight="1" s="29">
       <c r="A75" s="30" t="inlineStr">
@@ -6091,6 +6901,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M75" s="32" t="n"/>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>Vector search over huge datasets
+Distributed processing
+Open source
+Cloud version (Zilliz)</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n"/>
     </row>
     <row r="76" ht="66" customHeight="1" s="29">
       <c r="A76" s="30" t="inlineStr">
@@ -6148,6 +6968,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M76" s="32" t="n"/>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>Database and login in one service
+Vector search (pgvector)
+Free plan
+Speeds up app development</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="n"/>
     </row>
     <row r="77" ht="66" customHeight="1" s="29">
       <c r="A77" s="30" t="inlineStr">
@@ -6205,6 +7035,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M77" s="32" t="n"/>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>Large-scale search and ranking
+Plug in machine learning models
+Open source
+Originally from Yahoo</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="n"/>
     </row>
     <row r="78" ht="66" customHeight="1" s="29">
       <c r="A78" s="30" t="inlineStr">
@@ -6262,6 +7102,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M78" s="32" t="n"/>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>Train image, sound or pose recognition in the browser
+No coding
+Export your model
+Popular in classrooms</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n"/>
     </row>
     <row r="79" ht="66" customHeight="1" s="29">
       <c r="A79" s="30" t="inlineStr">
@@ -6319,6 +7169,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M79" s="32" t="n"/>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>Development environment in the browser
+Prototype apps with Gemini
+Android emulator
+Works with Firebase</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n"/>
     </row>
     <row r="80" ht="66" customHeight="1" s="29">
       <c r="A80" s="30" t="inlineStr">
@@ -6376,6 +7236,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M80" s="32" t="n"/>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>Suggests the next lines as you type
+Chat to ask and fix code
+Works in VS Code and Android Studio
+Free plan available</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>Copilot Free (monthly limits)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="66" customHeight="1" s="29">
       <c r="A81" s="30" t="inlineStr">
@@ -6435,6 +7309,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M81" s="33" t="n"/>
+      <c r="N81" s="33" t="inlineStr">
+        <is>
+          <t>AI-first code editor
+Understands and edits your whole project
+Edits many files at once
+Supports VS Code extensions</t>
+        </is>
+      </c>
+      <c r="O81" s="33" t="n"/>
     </row>
     <row r="82" ht="66" customHeight="1" s="29">
       <c r="A82" s="30" t="inlineStr">
@@ -6492,6 +7376,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M82" s="33" t="inlineStr">
+        <is>
+          <t>Devin Desktop (formerly Windsurf)</t>
+        </is>
+      </c>
+      <c r="N82" s="33" t="inlineStr">
+        <is>
+          <t>Code editor with AI agents
+Understands your project and works on it
+Manages local and cloud agents
+Free plan</t>
+        </is>
+      </c>
+      <c r="O82" s="33" t="n"/>
     </row>
     <row r="83" ht="66" customHeight="1" s="29">
       <c r="A83" s="30" t="inlineStr">
@@ -6549,6 +7447,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M83" s="32" t="n"/>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>Free code completion for individuals
+VS Code and JetBrains
+Chat about your code
+GitHub code review</t>
+        </is>
+      </c>
+      <c r="O83" s="32" t="inlineStr">
+        <is>
+          <t>Free for individuals</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="66" customHeight="1" s="29">
       <c r="A84" s="30" t="inlineStr">
@@ -6606,6 +7518,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M84" s="33" t="n"/>
+      <c r="N84" s="33" t="inlineStr">
+        <is>
+          <t>Answers AWS questions
+Converts and upgrades code
+Security scanning
+Free plan</t>
+        </is>
+      </c>
+      <c r="O84" s="33" t="n"/>
     </row>
     <row r="85" ht="66" customHeight="1" s="29">
       <c r="A85" s="30" t="inlineStr">
@@ -6663,6 +7585,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M85" s="32" t="n"/>
+      <c r="N85" s="32" t="inlineStr">
+        <is>
+          <t>Writes a spec before coding
+Agent-based IDE
+Automates development steps
+Made by Amazon</t>
+        </is>
+      </c>
+      <c r="O85" s="32" t="n"/>
     </row>
     <row r="86" ht="66" customHeight="1" s="29">
       <c r="A86" s="30" t="inlineStr">
@@ -6720,6 +7652,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M86" s="33" t="n"/>
+      <c r="N86" s="33" t="inlineStr">
+        <is>
+          <t>Works on your GitHub repository for you
+Fixes bugs and adds tests
+Works asynchronously
+Made by Google</t>
+        </is>
+      </c>
+      <c r="O86" s="33" t="n"/>
     </row>
     <row r="87" ht="66" customHeight="1" s="29">
       <c r="A87" s="30" t="inlineStr">
@@ -6777,6 +7719,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M87" s="33" t="n"/>
+      <c r="N87" s="33" t="inlineStr">
+        <is>
+          <t>AI completion for VS Code and JetBrains
+Connect any AI model
+Local AI supported
+Open source</t>
+        </is>
+      </c>
+      <c r="O87" s="33" t="n"/>
     </row>
     <row r="88" ht="66" customHeight="1" s="29">
       <c r="A88" s="30" t="inlineStr">
@@ -6834,6 +7786,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M88" s="33" t="n"/>
+      <c r="N88" s="33" t="inlineStr">
+        <is>
+          <t>Edits files and runs commands in VS Code
+Review changes before applying
+Connect any AI
+Open source</t>
+        </is>
+      </c>
+      <c r="O88" s="33" t="inlineStr">
+        <is>
+          <t>Extension is free (AI usage billed separately)</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="66" customHeight="1" s="29">
       <c r="A89" s="30" t="inlineStr">
@@ -6891,6 +7857,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M89" s="32" t="n"/>
+      <c r="N89" s="32" t="inlineStr">
+        <is>
+          <t>Edit code with AI in the terminal
+Automatic Git commits
+Works with many AIs
+Open source</t>
+        </is>
+      </c>
+      <c r="O89" s="32" t="inlineStr">
+        <is>
+          <t>Tool is free (AI usage billed separately)</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="66" customHeight="1" s="29">
       <c r="A90" s="30" t="inlineStr">
@@ -6948,6 +7928,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M90" s="32" t="n"/>
+      <c r="N90" s="32" t="inlineStr">
+        <is>
+          <t>Program in the browser
+Ask AI to build an app
+Publish with one click
+Good for learning</t>
+        </is>
+      </c>
+      <c r="O90" s="32" t="n"/>
     </row>
     <row r="91" ht="66" customHeight="1" s="29">
       <c r="A91" s="30" t="inlineStr">
@@ -7005,6 +7995,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M91" s="32" t="n"/>
+      <c r="N91" s="32" t="inlineStr">
+        <is>
+          <t>Build web apps from a prompt
+Instant preview in the browser
+Publish directly
+Edit the code too</t>
+        </is>
+      </c>
+      <c r="O91" s="32" t="n"/>
     </row>
     <row r="92" ht="66" customHeight="1" s="29">
       <c r="A92" s="30" t="inlineStr">
@@ -7062,6 +8062,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M92" s="32" t="n"/>
+      <c r="N92" s="32" t="inlineStr">
+        <is>
+          <t>Build web apps by chatting
+Polished design
+Database integration (Supabase)
+Save to GitHub</t>
+        </is>
+      </c>
+      <c r="O92" s="32" t="n"/>
     </row>
     <row r="93" ht="66" customHeight="1" s="29">
       <c r="A93" s="30" t="inlineStr">
@@ -7119,6 +8129,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M93" s="32" t="n"/>
+      <c r="N93" s="32" t="inlineStr">
+        <is>
+          <t>Generates UI from text
+React and Next.js code
+Deploy instantly on Vercel
+Recreate screens from images</t>
+        </is>
+      </c>
+      <c r="O93" s="32" t="n"/>
     </row>
     <row r="94" ht="66" customHeight="1" s="29">
       <c r="A94" s="30" t="inlineStr">
@@ -7176,6 +8196,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M94" s="33" t="n"/>
+      <c r="N94" s="33" t="inlineStr">
+        <is>
+          <t>Terminal with AI
+Suggests commands from plain language
+Explains errors
+Carries out tasks</t>
+        </is>
+      </c>
+      <c r="O94" s="33" t="n"/>
     </row>
     <row r="95" ht="66" customHeight="1" s="29">
       <c r="A95" s="30" t="inlineStr">
@@ -7233,6 +8263,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M95" s="32" t="n"/>
+      <c r="N95" s="32" t="inlineStr">
+        <is>
+          <t>Generates test code
+Reviews pull requests
+Checks code quality
+Free plan</t>
+        </is>
+      </c>
+      <c r="O95" s="32" t="n"/>
     </row>
     <row r="96" ht="66" customHeight="1" s="29">
       <c r="A96" s="30" t="inlineStr">
@@ -7290,6 +8330,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M96" s="33" t="n"/>
+      <c r="N96" s="33" t="inlineStr">
+        <is>
+          <t>Works in IntelliJ and Android Studio family IDEs
+Code completion and explanations
+Refactoring suggestions
+Writes commit messages</t>
+        </is>
+      </c>
+      <c r="O96" s="33" t="n"/>
     </row>
     <row r="97" ht="66" customHeight="1" s="29">
       <c r="A97" s="30" t="inlineStr">
@@ -7347,6 +8397,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M97" s="33" t="n"/>
+      <c r="N97" s="33" t="inlineStr">
+        <is>
+          <t>AI editor from ByteDance
+Agents that build for you
+Generous free tier
+Feels like VS Code</t>
+        </is>
+      </c>
+      <c r="O97" s="33" t="n"/>
     </row>
     <row r="98" ht="66" customHeight="1" s="29">
       <c r="A98" s="22" t="inlineStr">
@@ -7404,6 +8464,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M98" s="33" t="inlineStr">
+        <is>
+          <t>Tongyi Lingma</t>
+        </is>
+      </c>
+      <c r="N98" s="33" t="inlineStr">
+        <is>
+          <t>Free code completion from Alibaba
+VS Code and JetBrains
+Explains code and writes tests
+Chinese and English</t>
+        </is>
+      </c>
+      <c r="O98" s="33" t="n"/>
     </row>
     <row r="99" ht="66" customHeight="1" s="29">
       <c r="A99" s="30" t="inlineStr">
@@ -7461,6 +8535,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M99" s="32" t="n"/>
+      <c r="N99" s="32" t="inlineStr">
+        <is>
+          <t>Code completion from Tsinghua and Zhipu
+Free
+Converts code between languages
+Open model</t>
+        </is>
+      </c>
+      <c r="O99" s="32" t="n"/>
     </row>
     <row r="100" ht="66" customHeight="1" s="29">
       <c r="A100" s="30" t="inlineStr">
@@ -7518,6 +8602,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M100" s="32" t="n"/>
+      <c r="N100" s="32" t="inlineStr">
+        <is>
+          <t>Generates and searches code
+Reads code from images and videos
+Browser extension
+VS Code support</t>
+        </is>
+      </c>
+      <c r="O100" s="32" t="n"/>
     </row>
     <row r="101" ht="66" customHeight="1" s="29">
       <c r="A101" s="30" t="inlineStr">
@@ -7575,6 +8669,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M101" s="32" t="n"/>
+      <c r="N101" s="32" t="inlineStr">
+        <is>
+          <t>Artistic, beautiful images
+Distinctive texture and composition
+Style and character references
+Paid plans only</t>
+        </is>
+      </c>
+      <c r="O101" s="32" t="inlineStr">
+        <is>
+          <t>Paid plans only (free trials are occasional)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="66" customHeight="1" s="29">
       <c r="A102" s="30" t="inlineStr">
@@ -7632,6 +8740,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M102" s="32" t="n"/>
+      <c r="N102" s="32" t="inlineStr">
+        <is>
+          <t>Free image generation
+Uses OpenAI image models
+Sign in with a Microsoft account
+Also in Copilot</t>
+        </is>
+      </c>
+      <c r="O102" s="32" t="n"/>
     </row>
     <row r="103" ht="66" customHeight="1" s="29">
       <c r="A103" s="30" t="inlineStr">
@@ -7689,6 +8807,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M103" s="33" t="n"/>
+      <c r="N103" s="33" t="inlineStr">
+        <is>
+          <t>Designs for social posts and invitations
+Image generation and editing
+Background removal
+Templates</t>
+        </is>
+      </c>
+      <c r="O103" s="33" t="n"/>
     </row>
     <row r="104" ht="66" customHeight="1" s="29">
       <c r="A104" s="30" t="inlineStr">
@@ -7746,6 +8874,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M104" s="32" t="n"/>
+      <c r="N104" s="32" t="inlineStr">
+        <is>
+          <t>Trained with copyright in mind
+Generative fill and expand
+Works with Photoshop and Illustrator
+Monthly free credits</t>
+        </is>
+      </c>
+      <c r="O104" s="32" t="inlineStr">
+        <is>
+          <t>Monthly free credits</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="66" customHeight="1" s="29">
       <c r="A105" s="30" t="inlineStr">
@@ -7803,6 +8945,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M105" s="32" t="n"/>
+      <c r="N105" s="32" t="inlineStr">
+        <is>
+          <t>Great for game assets and characters
+Many models and styles
+Image to video
+Daily free credits</t>
+        </is>
+      </c>
+      <c r="O105" s="32" t="inlineStr">
+        <is>
+          <t>Daily free credits</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="66" customHeight="1" s="29">
       <c r="A106" s="30" t="inlineStr">
@@ -7860,6 +9016,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M106" s="32" t="n"/>
+      <c r="N106" s="32" t="inlineStr">
+        <is>
+          <t>Renders text inside images cleanly
+Good for logos and posters
+Style controls
+Free tier</t>
+        </is>
+      </c>
+      <c r="O106" s="32" t="n"/>
     </row>
     <row r="107" ht="66" customHeight="1" s="29">
       <c r="A107" s="30" t="inlineStr">
@@ -7917,6 +9083,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M107" s="32" t="n"/>
+      <c r="N107" s="32" t="inlineStr">
+        <is>
+          <t>Open image generation model
+Unlimited generation on your PC
+Customize with models and LoRA
+Commercial use allowed (with conditions)</t>
+        </is>
+      </c>
+      <c r="O107" s="32" t="inlineStr">
+        <is>
+          <t>Free when run locally</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="66" customHeight="1" s="29">
       <c r="A108" s="30" t="inlineStr">
@@ -7974,6 +9154,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M108" s="32" t="n"/>
+      <c r="N108" s="32" t="inlineStr">
+        <is>
+          <t>Community for sharing image models and LoRA
+Browse examples and prompts
+Generate in the browser
+Active community</t>
+        </is>
+      </c>
+      <c r="O108" s="32" t="n"/>
     </row>
     <row r="109" ht="66" customHeight="1" s="29">
       <c r="A109" s="30" t="inlineStr">
@@ -8031,6 +9221,24 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M109" s="32" t="inlineStr">
+        <is>
+          <t>Google Flow (formerly ImageFX &amp; Whisk)</t>
+        </is>
+      </c>
+      <c r="N109" s="32" t="inlineStr">
+        <is>
+          <t>Generates cinematic scenes from text (Veo)
+Keeps characters and backgrounds across scenes
+Image generation and editing too
+Mobile app available</t>
+        </is>
+      </c>
+      <c r="O109" s="32" t="inlineStr">
+        <is>
+          <t>50 free credits daily (video may be unavailable at peak times)</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="66" customHeight="1" s="29">
       <c r="A110" s="30" t="inlineStr">
@@ -8092,6 +9300,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M110" s="32" t="n"/>
+      <c r="N110" s="32" t="inlineStr">
+        <is>
+          <t>Watch AI-made videos for free
+Shows the prompt behind each video
+Channels by genre
+Experience what video AI can do</t>
+        </is>
+      </c>
+      <c r="O110" s="32" t="inlineStr">
+        <is>
+          <t>Free to watch, no sign-up</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="66" customHeight="1" s="29">
       <c r="A111" s="30" t="inlineStr">
@@ -8149,6 +9371,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M111" s="32" t="n"/>
+      <c r="N111" s="32" t="inlineStr">
+        <is>
+          <t>Image generation for design
+Poster and T-shirt templates
+Edit parts of an image
+Free tier</t>
+        </is>
+      </c>
+      <c r="O111" s="32" t="n"/>
     </row>
     <row r="112" ht="66" customHeight="1" s="29">
       <c r="A112" s="30" t="inlineStr">
@@ -8206,6 +9438,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M112" s="32" t="n"/>
+      <c r="N112" s="32" t="inlineStr">
+        <is>
+          <t>Choose from several image models
+Community to share artwork
+Daily free credits
+Creative challenges</t>
+        </is>
+      </c>
+      <c r="O112" s="32" t="n"/>
     </row>
     <row r="113" ht="66" customHeight="1" s="29">
       <c r="A113" s="30" t="inlineStr">
@@ -8267,6 +9509,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M113" s="32" t="n"/>
+      <c r="N113" s="32" t="inlineStr">
+        <is>
+          <t>Generate images without signing up
+Completely free
+Several ideas at once
+Easy to try</t>
+        </is>
+      </c>
+      <c r="O113" s="32" t="inlineStr">
+        <is>
+          <t>Free (with ads)</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="66" customHeight="1" s="29">
       <c r="A114" s="30" t="inlineStr">
@@ -8324,6 +9580,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M114" s="32" t="n"/>
+      <c r="N114" s="32" t="inlineStr">
+        <is>
+          <t>Generates in real time as you draw
+Image upscaling
+Video generation
+Many models</t>
+        </is>
+      </c>
+      <c r="O114" s="32" t="n"/>
     </row>
     <row r="115" ht="66" customHeight="1" s="29">
       <c r="A115" s="30" t="inlineStr">
@@ -8381,6 +9647,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M115" s="32" t="n"/>
+      <c r="N115" s="32" t="inlineStr">
+        <is>
+          <t>Photorealistic, high-quality images
+Good at rendering text
+Some models openly released
+German research team</t>
+        </is>
+      </c>
+      <c r="O115" s="32" t="inlineStr">
+        <is>
+          <t>Published models are free locally</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="66" customHeight="1" s="29">
       <c r="A116" s="30" t="inlineStr">
@@ -8438,6 +9718,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M116" s="32" t="n"/>
+      <c r="N116" s="32" t="inlineStr">
+        <is>
+          <t>Generates vector images (SVG)
+Icon and logo sets
+Keeps brand colors consistent
+Mockups</t>
+        </is>
+      </c>
+      <c r="O116" s="32" t="n"/>
     </row>
     <row r="117" ht="66" customHeight="1" s="29">
       <c r="A117" s="30" t="inlineStr">
@@ -8495,6 +9785,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M117" s="32" t="n"/>
+      <c r="N117" s="32" t="inlineStr">
+        <is>
+          <t>Many anime and illustration models
+Image to video
+Character chat
+Daily credits</t>
+        </is>
+      </c>
+      <c r="O117" s="32" t="n"/>
     </row>
     <row r="118" ht="66" customHeight="1" s="29">
       <c r="A118" s="30" t="inlineStr">
@@ -8552,6 +9852,24 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M118" s="33" t="inlineStr">
+        <is>
+          <t>Dreamina</t>
+        </is>
+      </c>
+      <c r="N118" s="33" t="inlineStr">
+        <is>
+          <t>Image and video generation from ByteDance
+Japanese prompts OK
+Lip-sync videos
+Daily credits</t>
+        </is>
+      </c>
+      <c r="O118" s="33" t="inlineStr">
+        <is>
+          <t>Daily free credits</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="66" customHeight="1" s="29">
       <c r="A119" s="30" t="inlineStr">
@@ -8609,6 +9927,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M119" s="32" t="n"/>
+      <c r="N119" s="32" t="inlineStr">
+        <is>
+          <t>Many models in one place
+Keeps the same character across images
+Editing and upscaling
+Share workflows</t>
+        </is>
+      </c>
+      <c r="O119" s="32" t="n"/>
     </row>
     <row r="120" ht="66" customHeight="1" s="29">
       <c r="A120" s="30" t="inlineStr">
@@ -8666,6 +9994,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M120" s="32" t="n"/>
+      <c r="N120" s="32" t="inlineStr">
+        <is>
+          <t>Built into the Freepik stock site
+Image, video and audio generation
+Upscaling and editing
+Combine with stock assets</t>
+        </is>
+      </c>
+      <c r="O120" s="32" t="n"/>
     </row>
     <row r="121" ht="66" customHeight="1" s="29">
       <c r="A121" s="30" t="inlineStr">
@@ -8723,6 +10061,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M121" s="32" t="n"/>
+      <c r="N121" s="32" t="inlineStr">
+        <is>
+          <t>Simple image generation
+Several models
+Try for free
+Fast</t>
+        </is>
+      </c>
+      <c r="O121" s="32" t="n"/>
     </row>
     <row r="122" ht="66" customHeight="1" s="29">
       <c r="A122" s="30" t="inlineStr">
@@ -8780,6 +10128,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M122" s="32" t="n"/>
+      <c r="N122" s="32" t="inlineStr">
+        <is>
+          <t>Mix images to create new ones
+Design character faces
+Generate from collages
+Collaborative creation</t>
+        </is>
+      </c>
+      <c r="O122" s="32" t="n"/>
     </row>
     <row r="123" ht="66" customHeight="1" s="29">
       <c r="A123" s="30" t="inlineStr">
@@ -8837,6 +10195,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M123" s="32" t="n"/>
+      <c r="N123" s="32" t="inlineStr">
+        <is>
+          <t>Node-based image and video generation
+Fine-grained control
+Quickly supports new models
+Free and open source</t>
+        </is>
+      </c>
+      <c r="O123" s="32" t="n"/>
     </row>
     <row r="124" ht="66" customHeight="1" s="29">
       <c r="A124" s="30" t="inlineStr">
@@ -8894,6 +10262,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M124" s="32" t="n"/>
+      <c r="N124" s="32" t="inlineStr">
+        <is>
+          <t>Paint and fix on a canvas
+Free locally
+Layer management
+Professional workflow</t>
+        </is>
+      </c>
+      <c r="O124" s="32" t="inlineStr">
+        <is>
+          <t>Local version is free</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="66" customHeight="1" s="29">
       <c r="A125" s="30" t="inlineStr">
@@ -8951,6 +10333,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M125" s="32" t="n"/>
+      <c r="N125" s="32" t="inlineStr">
+        <is>
+          <t>Accurately renders Chinese and English text in images
+Image editing model too
+Open weights
+Runs locally</t>
+        </is>
+      </c>
+      <c r="O125" s="32" t="n"/>
     </row>
     <row r="126" ht="66" customHeight="1" s="29">
       <c r="A126" s="30" t="inlineStr">
@@ -9008,6 +10400,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M126" s="32" t="n"/>
+      <c r="N126" s="32" t="inlineStr">
+        <is>
+          <t>Great at anime-style illustrations
+AI that continues your stories
+Japanese interface
+Paid plans</t>
+        </is>
+      </c>
+      <c r="O126" s="32" t="n"/>
     </row>
     <row r="127" ht="66" customHeight="1" s="29">
       <c r="A127" s="30" t="inlineStr">
@@ -9065,6 +10467,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M127" s="32" t="n"/>
+      <c r="N127" s="32" t="inlineStr">
+        <is>
+          <t>Huge range of templates
+AI for images, text and video
+Slides, flyers and social posts
+Collaborative editing</t>
+        </is>
+      </c>
+      <c r="O127" s="32" t="n"/>
     </row>
     <row r="128" ht="66" customHeight="1" s="29">
       <c r="A128" s="30" t="inlineStr">
@@ -9126,6 +10538,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M128" s="32" t="n"/>
+      <c r="N128" s="32" t="inlineStr">
+        <is>
+          <t>Removes photo backgrounds in seconds
+Accurate down to hair
+Batch processing
+Free at small size</t>
+        </is>
+      </c>
+      <c r="O128" s="32" t="inlineStr">
+        <is>
+          <t>Free at low resolution</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="66" customHeight="1" s="29">
       <c r="A129" s="30" t="inlineStr">
@@ -9183,6 +10609,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M129" s="32" t="n"/>
+      <c r="N129" s="32" t="inlineStr">
+        <is>
+          <t>Product photo backgrounds
+Generate new backgrounds with AI
+Automatic shadows
+Handy mobile app</t>
+        </is>
+      </c>
+      <c r="O129" s="32" t="n"/>
     </row>
     <row r="130" ht="66" customHeight="1" s="29">
       <c r="A130" s="30" t="inlineStr">
@@ -9240,6 +10676,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M130" s="32" t="n"/>
+      <c r="N130" s="32" t="inlineStr">
+        <is>
+          <t>Background removal
+Erase unwanted objects
+Image upscaling
+Relighting</t>
+        </is>
+      </c>
+      <c r="O130" s="32" t="n"/>
     </row>
     <row r="131" ht="66" customHeight="1" s="29">
       <c r="A131" s="30" t="inlineStr">
@@ -9301,6 +10747,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M131" s="32" t="n"/>
+      <c r="N131" s="32" t="inlineStr">
+        <is>
+          <t>Brush over people or objects to remove them
+Natural background fill
+Easy in the browser
+Free tier</t>
+        </is>
+      </c>
+      <c r="O131" s="32" t="n"/>
     </row>
     <row r="132" ht="66" customHeight="1" s="29">
       <c r="A132" s="30" t="inlineStr">
@@ -9362,6 +10818,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M132" s="32" t="n"/>
+      <c r="N132" s="32" t="inlineStr">
+        <is>
+          <t>Enlarge images without losing quality
+Free PC software
+Windows, Mac and Linux
+Batch processing</t>
+        </is>
+      </c>
+      <c r="O132" s="32" t="n"/>
     </row>
     <row r="133" ht="66" customHeight="1" s="29">
       <c r="A133" s="30" t="inlineStr">
@@ -9419,6 +10885,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M133" s="32" t="n"/>
+      <c r="N133" s="32" t="inlineStr">
+        <is>
+          <t>Sharpens and enlarges low-quality images
+Anime model included
+Noise reduction
+Open source</t>
+        </is>
+      </c>
+      <c r="O133" s="32" t="n"/>
     </row>
     <row r="134" ht="66" customHeight="1" s="29">
       <c r="A134" s="30" t="inlineStr">
@@ -9480,6 +10956,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M134" s="32" t="n"/>
+      <c r="N134" s="32" t="inlineStr">
+        <is>
+          <t>Enlarges illustrations and anime images
+Noise reduction
+Free in the browser
+Made in Japan</t>
+        </is>
+      </c>
+      <c r="O134" s="32" t="n"/>
     </row>
     <row r="135" ht="66" customHeight="1" s="29">
       <c r="A135" s="30" t="inlineStr">
@@ -9537,6 +11023,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M135" s="32" t="n"/>
+      <c r="N135" s="32" t="inlineStr">
+        <is>
+          <t>Upscaling for print
+Color and brightness correction
+Batch processing
+Free tier</t>
+        </is>
+      </c>
+      <c r="O135" s="32" t="n"/>
     </row>
     <row r="136" ht="66" customHeight="1" s="29">
       <c r="A136" s="30" t="inlineStr">
@@ -9594,6 +11090,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M136" s="32" t="n"/>
+      <c r="N136" s="32" t="inlineStr">
+        <is>
+          <t>Professional upscaling
+Noise and blur removal
+Face recovery
+Paid software (trial)</t>
+        </is>
+      </c>
+      <c r="O136" s="32" t="n"/>
     </row>
     <row r="137" ht="66" customHeight="1" s="29">
       <c r="A137" s="30" t="inlineStr">
@@ -9651,6 +11157,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M137" s="32" t="n"/>
+      <c r="N137" s="32" t="inlineStr">
+        <is>
+          <t>Image editor in the browser
+AI generation and background removal
+Templates
+No install needed</t>
+        </is>
+      </c>
+      <c r="O137" s="32" t="n"/>
     </row>
     <row r="138" ht="66" customHeight="1" s="29">
       <c r="A138" s="30" t="inlineStr">
@@ -9708,6 +11224,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M138" s="32" t="n"/>
+      <c r="N138" s="32" t="inlineStr">
+        <is>
+          <t>Automatic photo enhancement
+Background and object removal
+AI image generation
+Templates</t>
+        </is>
+      </c>
+      <c r="O138" s="32" t="n"/>
     </row>
     <row r="139" ht="66" customHeight="1" s="29">
       <c r="A139" s="30" t="inlineStr">
@@ -9769,6 +11295,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M139" s="33" t="n"/>
+      <c r="N139" s="33" t="inlineStr">
+        <is>
+          <t>Photoshop-like editing in the browser
+Opens PSD files
+AI replaces parts of images
+Free (with ads)</t>
+        </is>
+      </c>
+      <c r="O139" s="33" t="inlineStr">
+        <is>
+          <t>Free (with ads)</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="66" customHeight="1" s="29">
       <c r="A140" s="30" t="inlineStr">
@@ -9826,6 +11366,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M140" s="32" t="n"/>
+      <c r="N140" s="32" t="inlineStr">
+        <is>
+          <t>Photo editing on your phone
+AI image generation and background change
+Sticker maker
+Social media templates</t>
+        </is>
+      </c>
+      <c r="O140" s="32" t="n"/>
     </row>
     <row r="141" ht="66" customHeight="1" s="29">
       <c r="A141" s="30" t="inlineStr">
@@ -9887,6 +11437,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M141" s="33" t="n"/>
+      <c r="N141" s="33" t="inlineStr">
+        <is>
+          <t>Photo editing app by Google
+Selective adjustments and brushes
+Auto enhance
+Completely free</t>
+        </is>
+      </c>
+      <c r="O141" s="33" t="n"/>
     </row>
     <row r="142" ht="66" customHeight="1" s="29">
       <c r="A142" s="30" t="inlineStr">
@@ -9944,6 +11504,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M142" s="33" t="n"/>
+      <c r="N142" s="33" t="inlineStr">
+        <is>
+          <t>Batch background removal with Python
+Simple commands
+Local processing
+Open source</t>
+        </is>
+      </c>
+      <c r="O142" s="33" t="n"/>
     </row>
     <row r="143" ht="66" customHeight="1" s="29">
       <c r="A143" s="30" t="inlineStr">
@@ -10001,6 +11571,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M143" s="32" t="n"/>
+      <c r="N143" s="32" t="inlineStr">
+        <is>
+          <t>Brush to erase unwanted objects
+Runs locally
+Several AI models
+Open source</t>
+        </is>
+      </c>
+      <c r="O143" s="32" t="n"/>
     </row>
     <row r="144" ht="66" customHeight="1" s="29">
       <c r="A144" s="30" t="inlineStr">
@@ -10058,6 +11638,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M144" s="32" t="n"/>
+      <c r="N144" s="32" t="inlineStr">
+        <is>
+          <t>Upscales while adding detail
+Enhances texture
+For professionals
+Paid</t>
+        </is>
+      </c>
+      <c r="O144" s="32" t="n"/>
     </row>
     <row r="145" ht="66" customHeight="1" s="29">
       <c r="A145" s="30" t="inlineStr">
@@ -10115,6 +11705,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M145" s="33" t="n"/>
+      <c r="N145" s="33" t="inlineStr">
+        <is>
+          <t>AI photo editing
+Sky replacement
+Portrait retouching
+Paid software (trial)</t>
+        </is>
+      </c>
+      <c r="O145" s="33" t="n"/>
     </row>
     <row r="146" ht="66" customHeight="1" s="29">
       <c r="A146" s="30" t="inlineStr">
@@ -10172,6 +11772,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M146" s="32" t="n"/>
+      <c r="N146" s="32" t="inlineStr">
+        <is>
+          <t>Social media graphics from templates
+Image generation with Firefly
+Background removal
+Video editing</t>
+        </is>
+      </c>
+      <c r="O146" s="32" t="n"/>
     </row>
     <row r="147" ht="66" customHeight="1" s="29">
       <c r="A147" s="30" t="inlineStr">
@@ -10229,6 +11839,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M147" s="32" t="n"/>
+      <c r="N147" s="32" t="inlineStr">
+        <is>
+          <t>Background removal
+Photo enhancement
+Old photo restoration
+Batch processing</t>
+        </is>
+      </c>
+      <c r="O147" s="32" t="n"/>
     </row>
     <row r="148" ht="66" customHeight="1" s="29">
       <c r="A148" s="30" t="inlineStr">
@@ -10290,6 +11910,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M148" s="32" t="n"/>
+      <c r="N148" s="32" t="inlineStr">
+        <is>
+          <t>Enlarge images in the browser
+Try without signing up
+Up to 4x
+Simple</t>
+        </is>
+      </c>
+      <c r="O148" s="32" t="n"/>
     </row>
     <row r="149" ht="66" customHeight="1" s="29">
       <c r="A149" s="30" t="inlineStr">
@@ -10347,6 +11977,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M149" s="32" t="n"/>
+      <c r="N149" s="32" t="inlineStr">
+        <is>
+          <t>Film-quality video generation
+Video editing and background removal
+Control camera movement
+Free credits only at first</t>
+        </is>
+      </c>
+      <c r="O149" s="32" t="inlineStr">
+        <is>
+          <t>Free credits only at first</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="66" customHeight="1" s="29">
       <c r="A150" s="30" t="inlineStr">
@@ -10404,6 +12048,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M150" s="32" t="n"/>
+      <c r="N150" s="32" t="inlineStr">
+        <is>
+          <t>Short videos from text or images
+Add effects to videos
+Easy to use
+Free tier</t>
+        </is>
+      </c>
+      <c r="O150" s="32" t="n"/>
     </row>
     <row r="151" ht="66" customHeight="1" s="29">
       <c r="A151" s="30" t="inlineStr">
@@ -10461,6 +12115,24 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M151" s="32" t="inlineStr">
+        <is>
+          <t>Kling AI</t>
+        </is>
+      </c>
+      <c r="N151" s="32" t="inlineStr">
+        <is>
+          <t>Natural human motion in videos
+Longer videos up to minutes
+Lip sync
+Daily free credits</t>
+        </is>
+      </c>
+      <c r="O151" s="32" t="inlineStr">
+        <is>
+          <t>Daily free credits</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="66" customHeight="1" s="29">
       <c r="A152" s="30" t="inlineStr">
@@ -10518,6 +12190,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M152" s="32" t="inlineStr">
+        <is>
+          <t>Hailuo AI</t>
+        </is>
+      </c>
+      <c r="N152" s="32" t="inlineStr">
+        <is>
+          <t>Expressive video generation
+Camera movement control
+Image to video
+Free tier</t>
+        </is>
+      </c>
+      <c r="O152" s="32" t="n"/>
     </row>
     <row r="153" ht="66" customHeight="1" s="29">
       <c r="A153" s="30" t="inlineStr">
@@ -10575,6 +12261,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M153" s="32" t="n"/>
+      <c r="N153" s="32" t="inlineStr">
+        <is>
+          <t>Keeps characters consistent
+Great at anime style
+References multiple images
+Fast generation</t>
+        </is>
+      </c>
+      <c r="O153" s="32" t="n"/>
     </row>
     <row r="154" ht="66" customHeight="1" s="29">
       <c r="A154" s="30" t="inlineStr">
@@ -10632,6 +12328,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M154" s="33" t="n"/>
+      <c r="N154" s="33" t="inlineStr">
+        <is>
+          <t>Short videos for social media
+Many effects
+Image to video
+Free tier</t>
+        </is>
+      </c>
+      <c r="O154" s="33" t="n"/>
     </row>
     <row r="155" ht="66" customHeight="1" s="29">
       <c r="A155" s="30" t="inlineStr">
@@ -10689,6 +12395,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M155" s="32" t="n"/>
+      <c r="N155" s="32" t="inlineStr">
+        <is>
+          <t>Natural motion in videos
+Image generation (Photon)
+Camera control
+Free tier</t>
+        </is>
+      </c>
+      <c r="O155" s="32" t="n"/>
     </row>
     <row r="156" ht="66" customHeight="1" s="29">
       <c r="A156" s="30" t="inlineStr">
@@ -10746,6 +12462,24 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M156" s="33" t="inlineStr">
+        <is>
+          <t>Wan</t>
+        </is>
+      </c>
+      <c r="N156" s="33" t="inlineStr">
+        <is>
+          <t>Open video model from Alibaba
+Runs on your PC
+Text or image to video
+High quality</t>
+        </is>
+      </c>
+      <c r="O156" s="33" t="inlineStr">
+        <is>
+          <t>Published models are free</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="66" customHeight="1" s="29">
       <c r="A157" s="30" t="inlineStr">
@@ -10803,6 +12537,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M157" s="33" t="n"/>
+      <c r="N157" s="33" t="inlineStr">
+        <is>
+          <t>Open video model from Tencent
+High-quality video
+For research and development
+Runs locally</t>
+        </is>
+      </c>
+      <c r="O157" s="33" t="n"/>
     </row>
     <row r="158" ht="66" customHeight="1" s="29">
       <c r="A158" s="30" t="inlineStr">
@@ -10860,6 +12604,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M158" s="33" t="n"/>
+      <c r="N158" s="33" t="inlineStr">
+        <is>
+          <t>Open video model from Zhipu
+Relatively lightweight
+Text to video
+For research</t>
+        </is>
+      </c>
+      <c r="O158" s="33" t="n"/>
     </row>
     <row r="159" ht="66" customHeight="1" s="29">
       <c r="A159" s="30" t="inlineStr">
@@ -10917,6 +12671,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M159" s="33" t="n"/>
+      <c r="N159" s="33" t="inlineStr">
+        <is>
+          <t>Open video model from Genmo
+Smooth motion
+Runs locally
+Free</t>
+        </is>
+      </c>
+      <c r="O159" s="33" t="n"/>
     </row>
     <row r="160" ht="66" customHeight="1" s="29">
       <c r="A160" s="30" t="inlineStr">
@@ -10974,6 +12738,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M160" s="33" t="n"/>
+      <c r="N160" s="33" t="inlineStr">
+        <is>
+          <t>Videos with AI avatars speaking
+140+ languages
+Training and manual videos
+Free plan</t>
+        </is>
+      </c>
+      <c r="O160" s="33" t="n"/>
     </row>
     <row r="161" ht="66" customHeight="1" s="29">
       <c r="A161" s="30" t="inlineStr">
@@ -11031,6 +12805,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M161" s="33" t="n"/>
+      <c r="N161" s="33" t="inlineStr">
+        <is>
+          <t>AI avatar videos
+Dubs videos with matching lip movement
+Create your own avatar
+Japanese interface</t>
+        </is>
+      </c>
+      <c r="O161" s="33" t="n"/>
     </row>
     <row r="162" ht="66" customHeight="1" s="29">
       <c r="A162" s="30" t="inlineStr">
@@ -11088,6 +12872,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M162" s="32" t="n"/>
+      <c r="N162" s="32" t="inlineStr">
+        <is>
+          <t>Makes people in photos talk
+Presentation avatars
+Multilingual
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O162" s="32" t="n"/>
     </row>
     <row r="163" ht="66" customHeight="1" s="29">
       <c r="A163" s="30" t="inlineStr">
@@ -11145,6 +12939,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M163" s="32" t="n"/>
+      <c r="N163" s="32" t="inlineStr">
+        <is>
+          <t>Characters that talk and sing
+Very expressive
+Syncs voice and lip movement
+Free tier</t>
+        </is>
+      </c>
+      <c r="O163" s="32" t="n"/>
     </row>
     <row r="164" ht="66" customHeight="1" s="29">
       <c r="A164" s="30" t="inlineStr">
@@ -11202,6 +13006,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M164" s="32" t="n"/>
+      <c r="N164" s="32" t="inlineStr">
+        <is>
+          <t>Automatic subtitles
+AI avatars
+Eye contact correction
+For short videos</t>
+        </is>
+      </c>
+      <c r="O164" s="32" t="n"/>
     </row>
     <row r="165" ht="66" customHeight="1" s="29">
       <c r="A165" s="30" t="inlineStr">
@@ -11259,6 +13073,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M165" s="32" t="n"/>
+      <c r="N165" s="32" t="inlineStr">
+        <is>
+          <t>Full video editing for free
+Auto captions and transcription
+Many templates
+Phone and PC</t>
+        </is>
+      </c>
+      <c r="O165" s="32" t="n"/>
     </row>
     <row r="166" ht="66" customHeight="1" s="29">
       <c r="A166" s="30" t="inlineStr">
@@ -11316,6 +13140,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M166" s="32" t="n"/>
+      <c r="N166" s="32" t="inlineStr">
+        <is>
+          <t>Edit video by editing the transcript
+Removes filler words automatically
+Noise removal
+Screen recording</t>
+        </is>
+      </c>
+      <c r="O166" s="32" t="n"/>
     </row>
     <row r="167" ht="66" customHeight="1" s="29">
       <c r="A167" s="30" t="inlineStr">
@@ -11373,6 +13207,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M167" s="32" t="n"/>
+      <c r="N167" s="32" t="inlineStr">
+        <is>
+          <t>Video editing in the browser
+Auto subtitles and translation
+Cuts silent parts
+Collaborative editing</t>
+        </is>
+      </c>
+      <c r="O167" s="32" t="n"/>
     </row>
     <row r="168" ht="66" customHeight="1" s="29">
       <c r="A168" s="30" t="inlineStr">
@@ -11430,6 +13274,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M168" s="32" t="n"/>
+      <c r="N168" s="32" t="inlineStr">
+        <is>
+          <t>Creates videos from text automatically
+Lots of stock footage
+Narration included
+Watermark on free plan</t>
+        </is>
+      </c>
+      <c r="O168" s="32" t="inlineStr">
+        <is>
+          <t>Free plan adds a watermark</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="66" customHeight="1" s="29">
       <c r="A169" s="30" t="inlineStr">
@@ -11487,6 +13345,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M169" s="32" t="n"/>
+      <c r="N169" s="32" t="inlineStr">
+        <is>
+          <t>Turns blogs and text into videos
+Natural narration in many languages
+Auto subtitles
+Media library</t>
+        </is>
+      </c>
+      <c r="O169" s="32" t="n"/>
     </row>
     <row r="170" ht="66" customHeight="1" s="29">
       <c r="A170" s="30" t="inlineStr">
@@ -11544,6 +13412,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M170" s="32" t="n"/>
+      <c r="N170" s="32" t="inlineStr">
+        <is>
+          <t>Turns articles into videos
+Highlights from long videos
+Auto subtitles
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O170" s="32" t="n"/>
     </row>
     <row r="171" ht="66" customHeight="1" s="29">
       <c r="A171" s="30" t="inlineStr">
@@ -11601,6 +13479,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M171" s="32" t="n"/>
+      <c r="N171" s="32" t="inlineStr">
+        <is>
+          <t>Automatically clips highlights from long videos
+Converts to vertical shorts
+Auto captions
+For social media</t>
+        </is>
+      </c>
+      <c r="O171" s="32" t="n"/>
     </row>
     <row r="172" ht="66" customHeight="1" s="29">
       <c r="A172" s="30" t="inlineStr">
@@ -11658,6 +13546,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M172" s="32" t="n"/>
+      <c r="N172" s="32" t="inlineStr">
+        <is>
+          <t>Automatic subtitles from speech
+Cut video like editing text
+Japanese support
+AI voices</t>
+        </is>
+      </c>
+      <c r="O172" s="32" t="n"/>
     </row>
     <row r="173" ht="66" customHeight="1" s="29">
       <c r="A173" s="30" t="inlineStr">
@@ -11715,6 +13613,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M173" s="32" t="n"/>
+      <c r="N173" s="32" t="inlineStr">
+        <is>
+          <t>Record screen and camera together
+Share instantly with a link
+AI titles and summaries
+Great for work manuals</t>
+        </is>
+      </c>
+      <c r="O173" s="32" t="n"/>
     </row>
     <row r="174" ht="66" customHeight="1" s="29">
       <c r="A174" s="30" t="inlineStr">
@@ -11772,6 +13680,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M174" s="32" t="n"/>
+      <c r="N174" s="32" t="inlineStr">
+        <is>
+          <t>Video editing in the browser
+Auto subtitles and translation
+Templates
+Team sharing</t>
+        </is>
+      </c>
+      <c r="O174" s="32" t="n"/>
     </row>
     <row r="175" ht="66" customHeight="1" s="29">
       <c r="A175" s="30" t="inlineStr">
@@ -11829,6 +13747,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M175" s="33" t="n"/>
+      <c r="N175" s="33" t="inlineStr">
+        <is>
+          <t>Video editor built into Windows
+Auto captions
+Text to speech
+Free to use</t>
+        </is>
+      </c>
+      <c r="O175" s="33" t="n"/>
     </row>
     <row r="176" ht="66" customHeight="1" s="29">
       <c r="A176" s="30" t="inlineStr">
@@ -11886,6 +13814,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M176" s="32" t="n"/>
+      <c r="N176" s="32" t="inlineStr">
+        <is>
+          <t>Beginner-friendly video editor
+AI silence cutting and captions
+Lots of effects
+Watermark on free version</t>
+        </is>
+      </c>
+      <c r="O176" s="32" t="inlineStr">
+        <is>
+          <t>Free version adds a watermark</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="66" customHeight="1" s="29">
       <c r="A177" s="30" t="inlineStr">
@@ -11943,6 +13885,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M177" s="32" t="n"/>
+      <c r="N177" s="32" t="inlineStr">
+        <is>
+          <t>Upscales old videos
+Frame interpolation for smoothness
+Stabilization
+Paid software</t>
+        </is>
+      </c>
+      <c r="O177" s="32" t="n"/>
     </row>
     <row r="178" ht="66" customHeight="1" s="29">
       <c r="A178" s="30" t="inlineStr">
@@ -12000,6 +13952,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M178" s="32" t="n"/>
+      <c r="N178" s="32" t="inlineStr">
+        <is>
+          <t>Many video generation models in one place
+Lip-sync videos
+Dance and music video templates
+Image generation</t>
+        </is>
+      </c>
+      <c r="O178" s="32" t="n"/>
     </row>
     <row r="179" ht="66" customHeight="1" s="29">
       <c r="A179" s="30" t="inlineStr">
@@ -12057,6 +14019,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M179" s="32" t="n"/>
+      <c r="N179" s="32" t="inlineStr">
+        <is>
+          <t>Generates songs with lyrics and melody
+Supports Japanese lyrics
+Choose genre and mood
+Daily free credits</t>
+        </is>
+      </c>
+      <c r="O179" s="32" t="inlineStr">
+        <is>
+          <t>Daily free credits</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="66" customHeight="1" s="29">
       <c r="A180" s="30" t="inlineStr">
@@ -12114,6 +14090,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M180" s="32" t="n"/>
+      <c r="N180" s="32" t="inlineStr">
+        <is>
+          <t>High-quality song generation
+Detailed genre control
+Extend and edit songs
+Lyrics generation</t>
+        </is>
+      </c>
+      <c r="O180" s="32" t="n"/>
     </row>
     <row r="181" ht="66" customHeight="1" s="29">
       <c r="A181" s="30" t="inlineStr">
@@ -12171,6 +14157,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M181" s="32" t="n"/>
+      <c r="N181" s="32" t="inlineStr">
+        <is>
+          <t>Composition and lyrics
+Generates in the style of a reference song
+Choose a singing voice
+Free tier</t>
+        </is>
+      </c>
+      <c r="O181" s="32" t="n"/>
     </row>
     <row r="182" ht="66" customHeight="1" s="29">
       <c r="A182" s="30" t="inlineStr">
@@ -12228,6 +14224,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M182" s="32" t="n"/>
+      <c r="N182" s="32" t="inlineStr">
+        <is>
+          <t>Generates sound effects and music
+High audio quality
+Audio-to-audio transformation
+Made by Stability AI</t>
+        </is>
+      </c>
+      <c r="O182" s="32" t="n"/>
     </row>
     <row r="183" ht="66" customHeight="1" s="29">
       <c r="A183" s="30" t="inlineStr">
@@ -12285,6 +14291,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M183" s="32" t="n"/>
+      <c r="N183" s="32" t="inlineStr">
+        <is>
+          <t>Background music generator from Japan
+Adjust length and structure
+Royalty-free use
+For videos and streams</t>
+        </is>
+      </c>
+      <c r="O183" s="32" t="inlineStr">
+        <is>
+          <t>Creating and previewing are free (downloads are paid)</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="66" customHeight="1" s="29">
       <c r="A184" s="30" t="inlineStr">
@@ -12342,6 +14362,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M184" s="32" t="n"/>
+      <c r="N184" s="32" t="inlineStr">
+        <is>
+          <t>Classical and film music composition
+Export sheet music (MIDI)
+Customize the mood
+Free tier</t>
+        </is>
+      </c>
+      <c r="O184" s="32" t="n"/>
     </row>
     <row r="185" ht="66" customHeight="1" s="29">
       <c r="A185" s="30" t="inlineStr">
@@ -12399,6 +14429,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M185" s="32" t="n"/>
+      <c r="N185" s="32" t="inlineStr">
+        <is>
+          <t>Pick a mood to make background music
+Matches your video length
+For podcasts
+Free tier</t>
+        </is>
+      </c>
+      <c r="O185" s="32" t="n"/>
     </row>
     <row r="186" ht="66" customHeight="1" s="29">
       <c r="A186" s="30" t="inlineStr">
@@ -12456,6 +14496,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M186" s="32" t="n"/>
+      <c r="N186" s="32" t="inlineStr">
+        <is>
+          <t>Make a song in one click
+Release to music streaming services
+Beginner-friendly
+Free tier</t>
+        </is>
+      </c>
+      <c r="O186" s="32" t="n"/>
     </row>
     <row r="187" ht="66" customHeight="1" s="29">
       <c r="A187" s="30" t="inlineStr">
@@ -12513,6 +14563,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M187" s="33" t="n"/>
+      <c r="N187" s="33" t="inlineStr">
+        <is>
+          <t>Generates endless background music
+For streams and videos
+Choose mood and length
+Free tier</t>
+        </is>
+      </c>
+      <c r="O187" s="33" t="n"/>
     </row>
     <row r="188" ht="66" customHeight="1" s="29">
       <c r="A188" s="30" t="inlineStr">
@@ -12566,6 +14626,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M188" s="32" t="inlineStr">
+        <is>
+          <t>Google Flow Music (formerly Riffusion)</t>
+        </is>
+      </c>
+      <c r="N188" s="32" t="inlineStr">
+        <is>
+          <t>Compose with a conversational AI producer
+Songs from text, images or audio
+Replace or extend parts of a song
+Generates music videos</t>
+        </is>
+      </c>
+      <c r="O188" s="32" t="n"/>
     </row>
     <row r="189" ht="66" customHeight="1" s="29">
       <c r="A189" s="30" t="inlineStr">
@@ -12623,6 +14697,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M189" s="32" t="n"/>
+      <c r="N189" s="32" t="inlineStr">
+        <is>
+          <t>Royalty-free background music
+Choose genre and tempo
+For videos and streams
+Free tier</t>
+        </is>
+      </c>
+      <c r="O189" s="32" t="n"/>
     </row>
     <row r="190" ht="66" customHeight="1" s="29">
       <c r="A190" s="30" t="inlineStr">
@@ -12680,6 +14764,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M190" s="33" t="n"/>
+      <c r="N190" s="33" t="inlineStr">
+        <is>
+          <t>Music generation plus a sound library
+Adjust song length
+Commercial licenses
+Free tier</t>
+        </is>
+      </c>
+      <c r="O190" s="33" t="n"/>
     </row>
     <row r="191" ht="66" customHeight="1" s="29">
       <c r="A191" s="30" t="inlineStr">
@@ -12737,6 +14831,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M191" s="32" t="n"/>
+      <c r="N191" s="32" t="inlineStr">
+        <is>
+          <t>Separates vocals, drums and bass
+Change tempo and key
+Chord detection
+For practicing instruments</t>
+        </is>
+      </c>
+      <c r="O191" s="32" t="n"/>
     </row>
     <row r="192" ht="66" customHeight="1" s="29">
       <c r="A192" s="30" t="inlineStr">
@@ -12794,6 +14898,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M192" s="32" t="n"/>
+      <c r="N192" s="32" t="inlineStr">
+        <is>
+          <t>Accurate stem separation
+Extract vocals or backing track
+Noise removal
+Free only for the first uses</t>
+        </is>
+      </c>
+      <c r="O192" s="32" t="inlineStr">
+        <is>
+          <t>Free only for the first uses</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="66" customHeight="1" s="29">
       <c r="A193" s="30" t="inlineStr">
@@ -12855,6 +14973,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M193" s="32" t="n"/>
+      <c r="N193" s="32" t="inlineStr">
+        <is>
+          <t>Separates vocals and instruments
+Free on PC
+Several AI models
+Open source</t>
+        </is>
+      </c>
+      <c r="O193" s="32" t="n"/>
     </row>
     <row r="194" ht="66" customHeight="1" s="29">
       <c r="A194" s="30" t="inlineStr">
@@ -12912,6 +15040,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M194" s="32" t="n"/>
+      <c r="N194" s="32" t="inlineStr">
+        <is>
+          <t>Very natural speech synthesis
+Clone your own voice
+Multilingual video dubbing
+Sound effect generation</t>
+        </is>
+      </c>
+      <c r="O194" s="32" t="n"/>
     </row>
     <row r="195" ht="66" customHeight="1" s="29">
       <c r="A195" s="30" t="inlineStr">
@@ -12969,6 +15107,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M195" s="32" t="n"/>
+      <c r="N195" s="32" t="inlineStr">
+        <is>
+          <t>Create voiceovers
+Wide range of voices
+Adjust intonation and speed
+For videos and slides</t>
+        </is>
+      </c>
+      <c r="O195" s="32" t="n"/>
     </row>
     <row r="196" ht="66" customHeight="1" s="29">
       <c r="A196" s="30" t="inlineStr">
@@ -13026,6 +15174,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M196" s="32" t="n"/>
+      <c r="N196" s="32" t="inlineStr">
+        <is>
+          <t>Reads text, PDFs and web pages aloud
+Any reading speed
+Celebrity-style voices
+For studying and reading</t>
+        </is>
+      </c>
+      <c r="O196" s="32" t="n"/>
     </row>
     <row r="197" ht="66" customHeight="1" s="29">
       <c r="A197" s="30" t="inlineStr">
@@ -13083,6 +15241,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M197" s="32" t="n"/>
+      <c r="N197" s="32" t="inlineStr">
+        <is>
+          <t>Reads documents and PDFs aloud
+Natural voices
+Browser extension
+Convert to audio files</t>
+        </is>
+      </c>
+      <c r="O197" s="32" t="n"/>
     </row>
     <row r="198" ht="66" customHeight="1" s="29">
       <c r="A198" s="30" t="inlineStr">
@@ -13144,6 +15312,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M198" s="32" t="n"/>
+      <c r="N198" s="32" t="inlineStr">
+        <is>
+          <t>Free Japanese speech synthesis software
+Many character voices
+Fine intonation control
+Commercial use OK (rules per character)</t>
+        </is>
+      </c>
+      <c r="O198" s="32" t="n"/>
     </row>
     <row r="199" ht="66" customHeight="1" s="29">
       <c r="A199" s="30" t="inlineStr">
@@ -13201,6 +15379,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M199" s="32" t="n"/>
+      <c r="N199" s="32" t="inlineStr">
+        <is>
+          <t>Many Japanese voices
+Turn your own voice into AI
+Create narration
+For videos</t>
+        </is>
+      </c>
+      <c r="O199" s="32" t="n"/>
     </row>
     <row r="200" ht="66" customHeight="1" s="29">
       <c r="A200" s="30" t="inlineStr">
@@ -13258,6 +15446,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M200" s="32" t="n"/>
+      <c r="N200" s="32" t="inlineStr">
+        <is>
+          <t>Expressive Japanese speech
+Train your own voice
+Free locally
+Open source</t>
+        </is>
+      </c>
+      <c r="O200" s="32" t="n"/>
     </row>
     <row r="201" ht="66" customHeight="1" s="29">
       <c r="A201" s="30" t="inlineStr">
@@ -13315,6 +15513,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M201" s="32" t="n"/>
+      <c r="N201" s="32" t="inlineStr">
+        <is>
+          <t>Voice cloning
+Emotional expression
+Detects fake (deepfake) audio
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O201" s="32" t="n"/>
     </row>
     <row r="202" ht="66" customHeight="1" s="29">
       <c r="A202" s="30" t="inlineStr">
@@ -13372,6 +15580,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M202" s="32" t="n"/>
+      <c r="N202" s="32" t="inlineStr">
+        <is>
+          <t>Makes recordings sound studio-quality
+Noise removal
+Easy in the browser
+Free tier</t>
+        </is>
+      </c>
+      <c r="O202" s="32" t="n"/>
     </row>
     <row r="203" ht="66" customHeight="1" s="29">
       <c r="A203" s="30" t="inlineStr">
@@ -13429,6 +15647,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M203" s="32" t="n"/>
+      <c r="N203" s="32" t="inlineStr">
+        <is>
+          <t>Multilingual speech synthesis
+Clone a voice from a short sample
+Open models
+Free tier</t>
+        </is>
+      </c>
+      <c r="O203" s="32" t="n"/>
     </row>
     <row r="204" ht="66" customHeight="1" s="29">
       <c r="A204" s="30" t="inlineStr">
@@ -13486,6 +15714,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M204" s="32" t="n"/>
+      <c r="N204" s="32" t="inlineStr">
+        <is>
+          <t>Highly accurate transcription
+Many languages including Japanese
+Robust to noise
+Free on PC</t>
+        </is>
+      </c>
+      <c r="O204" s="32" t="n"/>
     </row>
     <row r="205" ht="66" customHeight="1" s="29">
       <c r="A205" s="30" t="inlineStr">
@@ -13543,6 +15781,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M205" s="32" t="n"/>
+      <c r="N205" s="32" t="inlineStr">
+        <is>
+          <t>Automatic meeting transcription
+Summaries and minutes
+Works with Zoom and Meet
+Especially good in English</t>
+        </is>
+      </c>
+      <c r="O205" s="32" t="n"/>
     </row>
     <row r="206" ht="66" customHeight="1" s="29">
       <c r="A206" s="30" t="inlineStr">
@@ -13600,6 +15848,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M206" s="33" t="n"/>
+      <c r="N206" s="33" t="inlineStr">
+        <is>
+          <t>AI and human transcription
+Subtitle files
+High accuracy
+Free tier</t>
+        </is>
+      </c>
+      <c r="O206" s="33" t="n"/>
     </row>
     <row r="207" ht="66" customHeight="1" s="29">
       <c r="A207" s="30" t="inlineStr">
@@ -13657,6 +15915,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M207" s="32" t="n"/>
+      <c r="N207" s="32" t="inlineStr">
+        <is>
+          <t>Excellent Japanese transcription
+Meeting summaries
+Works with Zoom, Meet and Teams
+Translation</t>
+        </is>
+      </c>
+      <c r="O207" s="32" t="n"/>
     </row>
     <row r="208" ht="66" customHeight="1" s="29">
       <c r="A208" s="30" t="inlineStr">
@@ -13714,6 +15982,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M208" s="32" t="n"/>
+      <c r="N208" s="32" t="inlineStr">
+        <is>
+          <t>Records and transcribes meetings
+Auto summaries and action items
+Search conversations
+Many integrations</t>
+        </is>
+      </c>
+      <c r="O208" s="32" t="n"/>
     </row>
     <row r="209" ht="66" customHeight="1" s="29">
       <c r="A209" s="30" t="inlineStr">
@@ -13771,6 +16049,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M209" s="33" t="n"/>
+      <c r="N209" s="33" t="inlineStr">
+        <is>
+          <t>Records Meet, Zoom and Teams
+AI meeting notes
+Japanese interface
+Clip key moments</t>
+        </is>
+      </c>
+      <c r="O209" s="33" t="n"/>
     </row>
     <row r="210" ht="66" customHeight="1" s="29">
       <c r="A210" s="30" t="inlineStr">
@@ -13828,6 +16116,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M210" s="32" t="n"/>
+      <c r="N210" s="32" t="inlineStr">
+        <is>
+          <t>Free meeting recording and transcription
+Automatic summaries
+Share highlights
+CRM integration</t>
+        </is>
+      </c>
+      <c r="O210" s="32" t="n"/>
     </row>
     <row r="211" ht="66" customHeight="1" s="29">
       <c r="A211" s="30" t="inlineStr">
@@ -13885,6 +16183,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M211" s="33" t="n"/>
+      <c r="N211" s="33" t="inlineStr">
+        <is>
+          <t>Real-time transcription for Google Meet
+Browser extension
+Summaries
+Share meeting notes</t>
+        </is>
+      </c>
+      <c r="O211" s="33" t="n"/>
     </row>
     <row r="212" ht="66" customHeight="1" s="29">
       <c r="A212" s="30" t="inlineStr">
@@ -13942,6 +16250,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M212" s="32" t="n"/>
+      <c r="N212" s="32" t="inlineStr">
+        <is>
+          <t>Meeting summaries
+Email and chat summaries
+Meeting analytics
+Many integrations</t>
+        </is>
+      </c>
+      <c r="O212" s="32" t="n"/>
     </row>
     <row r="213" ht="66" customHeight="1" s="29">
       <c r="A213" s="30" t="inlineStr">
@@ -13999,6 +16317,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M213" s="32" t="n"/>
+      <c r="N213" s="32" t="inlineStr">
+        <is>
+          <t>Removes background noise during calls
+Meeting transcription
+Summary notes
+Works with Zoom and more</t>
+        </is>
+      </c>
+      <c r="O213" s="32" t="n"/>
     </row>
     <row r="214" ht="66" customHeight="1" s="29">
       <c r="A214" s="30" t="inlineStr">
@@ -14056,6 +16384,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M214" s="32" t="n"/>
+      <c r="N214" s="32" t="inlineStr">
+        <is>
+          <t>Real-time speech recognition API
+Multilingual
+Speaker identification
+For developers</t>
+        </is>
+      </c>
+      <c r="O214" s="32" t="n"/>
     </row>
     <row r="215" ht="66" customHeight="1" s="29">
       <c r="A215" s="30" t="inlineStr">
@@ -14113,6 +16451,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M215" s="32" t="n"/>
+      <c r="N215" s="32" t="inlineStr">
+        <is>
+          <t>Accurate speech recognition API
+Speaker separation
+Summaries and sentiment
+Initial credits only</t>
+        </is>
+      </c>
+      <c r="O215" s="32" t="inlineStr">
+        <is>
+          <t>Initial credits only</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="66" customHeight="1" s="29">
       <c r="A216" s="30" t="inlineStr">
@@ -14170,6 +16522,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M216" s="32" t="n"/>
+      <c r="N216" s="32" t="inlineStr">
+        <is>
+          <t>Fast speech recognition API
+Real-time processing
+Speech synthesis
+Initial credits only</t>
+        </is>
+      </c>
+      <c r="O216" s="32" t="inlineStr">
+        <is>
+          <t>Initial credits only</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="66" customHeight="1" s="29">
       <c r="A217" s="30" t="inlineStr">
@@ -14231,6 +16597,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M217" s="32" t="n"/>
+      <c r="N217" s="32" t="inlineStr">
+        <is>
+          <t>Voice typing in the browser
+No sign-up
+Supports Japanese
+Save as notes</t>
+        </is>
+      </c>
+      <c r="O217" s="32" t="n"/>
     </row>
     <row r="218" ht="66" customHeight="1" s="29">
       <c r="A218" s="30" t="inlineStr">
@@ -14288,6 +16664,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M218" s="32" t="n"/>
+      <c r="N218" s="32" t="inlineStr">
+        <is>
+          <t>Transcription specialized in Japanese
+Fast processing
+Summaries
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O218" s="32" t="n"/>
     </row>
     <row r="219" ht="66" customHeight="1" s="29">
       <c r="A219" s="30" t="inlineStr">
@@ -14345,6 +16731,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M219" s="32" t="n"/>
+      <c r="N219" s="32" t="inlineStr">
+        <is>
+          <t>Writes blog articles automatically
+SEO-aware structure
+Analyzes visibility in AI search
+Multilingual</t>
+        </is>
+      </c>
+      <c r="O219" s="32" t="n"/>
     </row>
     <row r="220" ht="66" customHeight="1" s="29">
       <c r="A220" s="30" t="inlineStr">
@@ -14402,6 +16798,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M220" s="33" t="n"/>
+      <c r="N220" s="33" t="inlineStr">
+        <is>
+          <t>40+ templates by purpose
+30+ languages
+Choose the tone
+Free tier</t>
+        </is>
+      </c>
+      <c r="O220" s="33" t="n"/>
     </row>
     <row r="221" ht="66" customHeight="1" s="29">
       <c r="A221" s="30" t="inlineStr">
@@ -14459,6 +16865,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M221" s="32" t="n"/>
+      <c r="N221" s="32" t="inlineStr">
+        <is>
+          <t>Marketing copy
+Consistent brand voice
+Team management
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O221" s="32" t="n"/>
     </row>
     <row r="222" ht="66" customHeight="1" s="29">
       <c r="A222" s="30" t="inlineStr">
@@ -14516,6 +16932,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M222" s="32" t="n"/>
+      <c r="N222" s="32" t="inlineStr">
+        <is>
+          <t>Ads and sales emails
+Workflow automation
+Templates
+Free tier</t>
+        </is>
+      </c>
+      <c r="O222" s="32" t="n"/>
     </row>
     <row r="223" ht="66" customHeight="1" s="29">
       <c r="A223" s="30" t="inlineStr">
@@ -14573,6 +16999,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M223" s="32" t="n"/>
+      <c r="N223" s="32" t="inlineStr">
+        <is>
+          <t>Predicts ad copy performance
+Compare several versions
+Write for each audience
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O223" s="32" t="n"/>
     </row>
     <row r="224" ht="66" customHeight="1" s="29">
       <c r="A224" s="30" t="inlineStr">
@@ -14630,6 +17066,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M224" s="32" t="n"/>
+      <c r="N224" s="32" t="inlineStr">
+        <is>
+          <t>Analyzes top-ranking articles
+Creates article outlines
+SEO score
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O224" s="32" t="n"/>
     </row>
     <row r="225" ht="66" customHeight="1" s="29">
       <c r="A225" s="30" t="inlineStr">
@@ -14687,6 +17133,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M225" s="32" t="n"/>
+      <c r="N225" s="32" t="inlineStr">
+        <is>
+          <t>Suggests English rewrites
+Adjust sentence length
+Summaries
+Browser extension</t>
+        </is>
+      </c>
+      <c r="O225" s="32" t="n"/>
     </row>
     <row r="226" ht="66" customHeight="1" s="29">
       <c r="A226" s="30" t="inlineStr">
@@ -14744,6 +17200,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M226" s="32" t="n"/>
+      <c r="N226" s="32" t="inlineStr">
+        <is>
+          <t>Paraphrasing
+Summaries
+Grammar checking
+Translation</t>
+        </is>
+      </c>
+      <c r="O226" s="32" t="n"/>
     </row>
     <row r="227" ht="66" customHeight="1" s="29">
       <c r="A227" s="30" t="inlineStr">
@@ -14801,6 +17267,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M227" s="32" t="n"/>
+      <c r="N227" s="32" t="inlineStr">
+        <is>
+          <t>English grammar and spelling checks
+Tone adjustments
+Works in browsers and Word
+Free tier</t>
+        </is>
+      </c>
+      <c r="O227" s="32" t="n"/>
     </row>
     <row r="228" ht="66" customHeight="1" s="29">
       <c r="A228" s="30" t="inlineStr">
@@ -14858,6 +17334,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M228" s="32" t="n"/>
+      <c r="N228" s="32" t="inlineStr">
+        <is>
+          <t>Proofreads many languages including Japanese
+Grammar and consistency
+Browser extension
+Free tier</t>
+        </is>
+      </c>
+      <c r="O228" s="32" t="n"/>
     </row>
     <row r="229" ht="66" customHeight="1" s="29">
       <c r="A229" s="30" t="inlineStr">
@@ -14915,6 +17401,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M229" s="32" t="n"/>
+      <c r="N229" s="32" t="inlineStr">
+        <is>
+          <t>English style checks
+Detailed reports
+For novels and papers
+Free tier</t>
+        </is>
+      </c>
+      <c r="O229" s="32" t="n"/>
     </row>
     <row r="230" ht="66" customHeight="1" s="29">
       <c r="A230" s="30" t="inlineStr">
@@ -14972,6 +17468,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M230" s="32" t="n"/>
+      <c r="N230" s="32" t="inlineStr">
+        <is>
+          <t>Helps write fiction
+Plot ideas
+Adds descriptions
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O230" s="32" t="n"/>
     </row>
     <row r="231" ht="66" customHeight="1" s="29">
       <c r="A231" s="30" t="inlineStr">
@@ -15029,6 +17535,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M231" s="32" t="n"/>
+      <c r="N231" s="32" t="inlineStr">
+        <is>
+          <t>Text, design and video in one place
+Schedule social posts
+For teams
+Free tier</t>
+        </is>
+      </c>
+      <c r="O231" s="32" t="n"/>
     </row>
     <row r="232" ht="66" customHeight="1" s="29">
       <c r="A232" s="30" t="inlineStr">
@@ -15086,6 +17602,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M232" s="32" t="n"/>
+      <c r="N232" s="32" t="inlineStr">
+        <is>
+          <t>Writing and rewriting
+Browser extension
+Learns your writing style
+Free tier</t>
+        </is>
+      </c>
+      <c r="O232" s="32" t="n"/>
     </row>
     <row r="233" ht="66" customHeight="1" s="29">
       <c r="A233" s="30" t="inlineStr">
@@ -15147,6 +17673,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M233" s="32" t="n"/>
+      <c r="N233" s="32" t="inlineStr">
+        <is>
+          <t>Corrects and rewrites text
+Suggests natural wording
+Supports Japanese
+Free to use</t>
+        </is>
+      </c>
+      <c r="O233" s="32" t="n"/>
     </row>
     <row r="234" ht="66" customHeight="1" s="29">
       <c r="A234" s="30" t="inlineStr">
@@ -15204,6 +17740,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M234" s="32" t="n"/>
+      <c r="N234" s="32" t="inlineStr">
+        <is>
+          <t>Japanese proofreading for typos and consistency
+Manage article writing
+Team reviews
+Free tier</t>
+        </is>
+      </c>
+      <c r="O234" s="32" t="n"/>
     </row>
     <row r="235" ht="66" customHeight="1" s="29">
       <c r="A235" s="30" t="inlineStr">
@@ -15261,6 +17807,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M235" s="32" t="n"/>
+      <c r="N235" s="32" t="inlineStr">
+        <is>
+          <t>Japanese catchphrase generator
+Templates for ads, social posts and proposals
+100+ use cases
+Free tier</t>
+        </is>
+      </c>
+      <c r="O235" s="32" t="n"/>
     </row>
     <row r="236" ht="66" customHeight="1" s="29">
       <c r="A236" s="30" t="inlineStr">
@@ -15318,6 +17874,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M236" s="32" t="n"/>
+      <c r="N236" s="32" t="inlineStr">
+        <is>
+          <t>Suggests the next part of your paper
+Reference management
+Insert citations
+Free tier</t>
+        </is>
+      </c>
+      <c r="O236" s="32" t="n"/>
     </row>
     <row r="237" ht="66" customHeight="1" s="29">
       <c r="A237" s="30" t="inlineStr">
@@ -15375,6 +17941,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M237" s="32" t="n"/>
+      <c r="N237" s="32" t="inlineStr">
+        <is>
+          <t>Proofreads English papers
+Academic phrasing
+Pre-submission checks
+Free tier</t>
+        </is>
+      </c>
+      <c r="O237" s="32" t="n"/>
     </row>
     <row r="238" ht="66" customHeight="1" s="29">
       <c r="A238" s="30" t="inlineStr">
@@ -15432,6 +18008,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M238" s="33" t="n"/>
+      <c r="N238" s="33" t="inlineStr">
+        <is>
+          <t>Summarizes and organizes notes in Notion
+Meeting notes
+Searches your workspace
+Free plan is trial only</t>
+        </is>
+      </c>
+      <c r="O238" s="33" t="inlineStr">
+        <is>
+          <t>Free plan includes limited trial uses</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="66" customHeight="1" s="29">
       <c r="A239" s="30" t="inlineStr">
@@ -15489,6 +18079,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M239" s="32" t="n"/>
+      <c r="N239" s="32" t="inlineStr">
+        <is>
+          <t>Creates slides from a topic
+Also web pages and documents
+Automatic design
+Free tier</t>
+        </is>
+      </c>
+      <c r="O239" s="32" t="n"/>
     </row>
     <row r="240" ht="66" customHeight="1" s="29">
       <c r="A240" s="30" t="inlineStr">
@@ -15546,6 +18146,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M240" s="32" t="n"/>
+      <c r="N240" s="32" t="inlineStr">
+        <is>
+          <t>Turns text into diagrams and charts
+Choose a design
+Paste into documents
+Free tier</t>
+        </is>
+      </c>
+      <c r="O240" s="32" t="n"/>
     </row>
     <row r="241" ht="66" customHeight="1" s="29">
       <c r="A241" s="30" t="inlineStr">
@@ -15607,6 +18217,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M241" s="32" t="n"/>
+      <c r="N241" s="32" t="inlineStr">
+        <is>
+          <t>Natural, accurate translation
+Translates Word and PDF files as is
+Glossaries
+Character limit on free plan</t>
+        </is>
+      </c>
+      <c r="O241" s="32" t="n"/>
     </row>
     <row r="242" ht="66" customHeight="1" s="29">
       <c r="A242" s="30" t="inlineStr">
@@ -15668,6 +18288,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M242" s="33" t="inlineStr">
+        <is>
+          <t>Google Translate</t>
+        </is>
+      </c>
+      <c r="N242" s="33" t="inlineStr">
+        <is>
+          <t>100+ languages
+Translate signs and menus with the camera
+Conversation mode
+Completely free</t>
+        </is>
+      </c>
+      <c r="O242" s="33" t="n"/>
     </row>
     <row r="243" ht="66" customHeight="1" s="29">
       <c r="A243" s="30" t="inlineStr">
@@ -15729,6 +18363,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M243" s="32" t="n"/>
+      <c r="N243" s="32" t="inlineStr">
+        <is>
+          <t>Multilingual translation
+Live translation for group conversations
+Office integration
+Free</t>
+        </is>
+      </c>
+      <c r="O243" s="32" t="n"/>
     </row>
     <row r="244" ht="66" customHeight="1" s="29">
       <c r="A244" s="30" t="inlineStr">
@@ -15790,6 +18434,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M244" s="32" t="n"/>
+      <c r="N244" s="32" t="inlineStr">
+        <is>
+          <t>Especially natural Japanese–Korean translation
+Image and voice translation
+Made by Naver
+Free</t>
+        </is>
+      </c>
+      <c r="O244" s="32" t="n"/>
     </row>
     <row r="245" ht="66" customHeight="1" s="29">
       <c r="A245" s="30" t="inlineStr">
@@ -15851,6 +18505,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M245" s="32" t="inlineStr">
+        <is>
+          <t>Yandex Translate</t>
+        </is>
+      </c>
+      <c r="N245" s="32" t="inlineStr">
+        <is>
+          <t>Strong for Russian and Eastern European languages
+Image and web page translation
+Free
+No sign-up</t>
+        </is>
+      </c>
+      <c r="O245" s="32" t="n"/>
     </row>
     <row r="246" ht="66" customHeight="1" s="29">
       <c r="A246" s="22" t="inlineStr">
@@ -15912,6 +18580,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M246" s="32" t="inlineStr">
+        <is>
+          <t>Baidu Translate</t>
+        </is>
+      </c>
+      <c r="N246" s="32" t="inlineStr">
+        <is>
+          <t>Strong Chinese translation
+Document translation
+Image translation
+Free</t>
+        </is>
+      </c>
+      <c r="O246" s="32" t="n"/>
     </row>
     <row r="247" ht="66" customHeight="1" s="29">
       <c r="A247" s="22" t="inlineStr">
@@ -15973,6 +18655,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M247" s="32" t="inlineStr">
+        <is>
+          <t>Youdao Translate</t>
+        </is>
+      </c>
+      <c r="N247" s="32" t="inlineStr">
+        <is>
+          <t>Chinese translation with many languages
+Dictionary features
+Document translation
+Free</t>
+        </is>
+      </c>
+      <c r="O247" s="32" t="n"/>
     </row>
     <row r="248" ht="66" customHeight="1" s="29">
       <c r="A248" s="30" t="inlineStr">
@@ -16034,6 +18730,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M248" s="32" t="n"/>
+      <c r="N248" s="32" t="inlineStr">
+        <is>
+          <t>Translations with real example sentences
+Dictionary and conjugations
+Rephrasing
+Great for learning languages</t>
+        </is>
+      </c>
+      <c r="O248" s="32" t="n"/>
     </row>
     <row r="249" ht="66" customHeight="1" s="29">
       <c r="A249" s="30" t="inlineStr">
@@ -16091,6 +18797,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M249" s="33" t="n"/>
+      <c r="N249" s="33" t="inlineStr">
+        <is>
+          <t>Shows web pages in original and translated side by side
+Translates PDFs and video subtitles
+Several translation engines
+Browser extension</t>
+        </is>
+      </c>
+      <c r="O249" s="33" t="n"/>
     </row>
     <row r="250" ht="66" customHeight="1" s="29">
       <c r="A250" s="30" t="inlineStr">
@@ -16148,6 +18864,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M250" s="32" t="inlineStr">
+        <is>
+          <t>PLaMo Translate</t>
+        </is>
+      </c>
+      <c r="N250" s="32" t="inlineStr">
+        <is>
+          <t>Translation by a Japanese AI
+Natural Japanese
+Handles long text
+Made by Preferred Networks</t>
+        </is>
+      </c>
+      <c r="O250" s="32" t="n"/>
     </row>
     <row r="251" ht="66" customHeight="1" s="29">
       <c r="A251" s="30" t="inlineStr">
@@ -16205,6 +18935,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M251" s="33" t="n"/>
+      <c r="N251" s="33" t="inlineStr">
+        <is>
+          <t>Ask questions about your PDFs and documents
+Shows sources in answers
+Turns materials into audio overviews
+Completely free</t>
+        </is>
+      </c>
+      <c r="O251" s="33" t="n"/>
     </row>
     <row r="252" ht="66" customHeight="1" s="29">
       <c r="A252" s="30" t="inlineStr">
@@ -16262,6 +19002,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M252" s="32" t="n"/>
+      <c r="N252" s="32" t="inlineStr">
+        <is>
+          <t>Turns text, PDFs and YouTube into mind maps
+Organizes key points
+Edit and export
+Made by Xmind</t>
+        </is>
+      </c>
+      <c r="O252" s="32" t="n"/>
     </row>
     <row r="253" ht="66" customHeight="1" s="29">
       <c r="A253" s="30" t="inlineStr">
@@ -16319,6 +19069,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M253" s="33" t="n"/>
+      <c r="N253" s="33" t="inlineStr">
+        <is>
+          <t>Upload a PDF and ask questions
+Summaries
+Answers with page numbers
+Free tier</t>
+        </is>
+      </c>
+      <c r="O253" s="33" t="n"/>
     </row>
     <row r="254" ht="66" customHeight="1" s="29">
       <c r="A254" s="30" t="inlineStr">
@@ -16376,6 +19136,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M254" s="33" t="n"/>
+      <c r="N254" s="33" t="inlineStr">
+        <is>
+          <t>Ask questions about PDFs and papers
+Compare several files
+Summaries
+Free tier</t>
+        </is>
+      </c>
+      <c r="O254" s="33" t="n"/>
     </row>
     <row r="255" ht="66" customHeight="1" s="29">
       <c r="A255" s="30" t="inlineStr">
@@ -16433,6 +19203,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M255" s="32" t="n"/>
+      <c r="N255" s="32" t="inlineStr">
+        <is>
+          <t>Turns papers into summary cards
+Extracts key figures and findings
+Organizes references
+Free tier</t>
+        </is>
+      </c>
+      <c r="O255" s="32" t="n"/>
     </row>
     <row r="256" ht="66" customHeight="1" s="29">
       <c r="A256" s="30" t="inlineStr">
@@ -16490,6 +19270,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M256" s="32" t="n"/>
+      <c r="N256" s="32" t="inlineStr">
+        <is>
+          <t>Evidence-based answers from papers
+Shows how much studies agree
+With citations
+Free tier</t>
+        </is>
+      </c>
+      <c r="O256" s="32" t="n"/>
     </row>
     <row r="257" ht="66" customHeight="1" s="29">
       <c r="A257" s="30" t="inlineStr">
@@ -16547,6 +19337,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M257" s="32" t="n"/>
+      <c r="N257" s="32" t="inlineStr">
+        <is>
+          <t>Finds papers and summarizes them in tables
+Extracts data from papers
+Speeds up literature reviews
+Free tier</t>
+        </is>
+      </c>
+      <c r="O257" s="32" t="n"/>
     </row>
     <row r="258" ht="66" customHeight="1" s="29">
       <c r="A258" s="30" t="inlineStr">
@@ -16604,6 +19404,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M258" s="32" t="n"/>
+      <c r="N258" s="32" t="inlineStr">
+        <is>
+          <t>Shows whether citations support or dispute
+Checks paper reliability
+Answers with citations
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O258" s="32" t="n"/>
     </row>
     <row r="259" ht="66" customHeight="1" s="29">
       <c r="A259" s="30" t="inlineStr">
@@ -16665,6 +19475,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M259" s="32" t="n"/>
+      <c r="N259" s="32" t="inlineStr">
+        <is>
+          <t>Free paper search
+One-line AI summaries
+Citation network
+Run by a non-profit</t>
+        </is>
+      </c>
+      <c r="O259" s="32" t="n"/>
     </row>
     <row r="260" ht="66" customHeight="1" s="29">
       <c r="A260" s="30" t="inlineStr">
@@ -16722,6 +19542,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M260" s="32" t="n"/>
+      <c r="N260" s="32" t="inlineStr">
+        <is>
+          <t>Explains difficult papers simply
+Literature reviews
+Chat with PDFs
+Free tier</t>
+        </is>
+      </c>
+      <c r="O260" s="32" t="n"/>
     </row>
     <row r="261" ht="66" customHeight="1" s="29">
       <c r="A261" s="30" t="inlineStr">
@@ -16779,6 +19609,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M261" s="32" t="n"/>
+      <c r="N261" s="32" t="inlineStr">
+        <is>
+          <t>Shows related papers as a graph
+Overview of a research field
+Simple to use
+Free tier</t>
+        </is>
+      </c>
+      <c r="O261" s="32" t="n"/>
     </row>
     <row r="262" ht="66" customHeight="1" s="29">
       <c r="A262" s="30" t="inlineStr">
@@ -16836,6 +19676,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M262" s="32" t="n"/>
+      <c r="N262" s="32" t="inlineStr">
+        <is>
+          <t>Discover related papers step by step
+Visualizes connections
+New paper alerts
+Free</t>
+        </is>
+      </c>
+      <c r="O262" s="32" t="n"/>
     </row>
     <row r="263" ht="66" customHeight="1" s="29">
       <c r="A263" s="30" t="inlineStr">
@@ -16893,6 +19743,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M263" s="32" t="n"/>
+      <c r="N263" s="32" t="inlineStr">
+        <is>
+          <t>Citation maps of papers
+Alerts for new papers
+Manage collections
+Free tier</t>
+        </is>
+      </c>
+      <c r="O263" s="32" t="n"/>
     </row>
     <row r="264" ht="66" customHeight="1" s="29">
       <c r="A264" s="30" t="inlineStr">
@@ -16950,6 +19810,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M264" s="32" t="n"/>
+      <c r="N264" s="32" t="inlineStr">
+        <is>
+          <t>Deep, thorough paper search
+Misses less
+Research reports
+Free tier</t>
+        </is>
+      </c>
+      <c r="O264" s="32" t="n"/>
     </row>
     <row r="265" ht="66" customHeight="1" s="29">
       <c r="A265" s="30" t="inlineStr">
@@ -17007,6 +19877,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M265" s="32" t="n"/>
+      <c r="N265" s="32" t="inlineStr">
+        <is>
+          <t>Ask across many papers and documents
+Shows the source paragraph
+Take notes
+Formerly Unriddle</t>
+        </is>
+      </c>
+      <c r="O265" s="32" t="n"/>
     </row>
     <row r="266" ht="66" customHeight="1" s="29">
       <c r="A266" s="30" t="inlineStr">
@@ -17064,6 +19944,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M266" s="33" t="n"/>
+      <c r="N266" s="33" t="inlineStr">
+        <is>
+          <t>Upload Excel or CSV and analyze by chatting
+Automatic charts
+Calculates with Python
+Free tier</t>
+        </is>
+      </c>
+      <c r="O266" s="33" t="n"/>
     </row>
     <row r="267" ht="66" customHeight="1" s="29">
       <c r="A267" s="30" t="inlineStr">
@@ -17125,6 +20015,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M267" s="32" t="n"/>
+      <c r="N267" s="32" t="inlineStr">
+        <is>
+          <t>Solves math accurately
+Statistics and unit conversion
+Scientific data
+Step-by-step solutions are paid</t>
+        </is>
+      </c>
+      <c r="O267" s="32" t="n"/>
     </row>
     <row r="268" ht="66" customHeight="1" s="29">
       <c r="A268" s="30" t="inlineStr">
@@ -17182,6 +20082,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M268" s="33" t="n"/>
+      <c r="N268" s="33" t="inlineStr">
+        <is>
+          <t>Spreadsheet with AI
+Automatic data analysis and summaries
+Connects to other services
+Free tier</t>
+        </is>
+      </c>
+      <c r="O268" s="33" t="n"/>
     </row>
     <row r="269" ht="66" customHeight="1" s="29">
       <c r="A269" s="30" t="inlineStr">
@@ -17243,6 +20153,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M269" s="32" t="n"/>
+      <c r="N269" s="32" t="inlineStr">
+        <is>
+          <t>Process data by connecting blocks
+Automates Excel work
+Machine learning
+Desktop version is free</t>
+        </is>
+      </c>
+      <c r="O269" s="32" t="n"/>
     </row>
     <row r="270" ht="66" customHeight="1" s="29">
       <c r="A270" s="30" t="inlineStr">
@@ -17304,6 +20224,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M270" s="32" t="n"/>
+      <c r="N270" s="32" t="inlineStr">
+        <is>
+          <t>Analyze data by connecting components
+See results as charts
+Great for learning ML
+Free</t>
+        </is>
+      </c>
+      <c r="O270" s="32" t="n"/>
     </row>
     <row r="271" ht="66" customHeight="1" s="29">
       <c r="A271" s="30" t="inlineStr">
@@ -17361,6 +20291,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M271" s="32" t="n"/>
+      <c r="N271" s="32" t="inlineStr">
+        <is>
+          <t>Forecasts time-series data like sales
+Handles seasonality and holidays
+Python and R
+Made by Meta</t>
+        </is>
+      </c>
+      <c r="O271" s="32" t="n"/>
     </row>
     <row r="272" ht="66" customHeight="1" s="29">
       <c r="A272" s="30" t="inlineStr">
@@ -17418,6 +20358,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M272" s="33" t="n"/>
+      <c r="N272" s="33" t="inlineStr">
+        <is>
+          <t>Free RPA on Windows
+Automates Excel, web and desktop tasks
+Records your actions
+Works with AI features</t>
+        </is>
+      </c>
+      <c r="O272" s="33" t="inlineStr">
+        <is>
+          <t>Free for Windows users</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="66" customHeight="1" s="29">
       <c r="A273" s="30" t="inlineStr">
@@ -17475,6 +20429,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M273" s="32" t="n"/>
+      <c r="N273" s="32" t="inlineStr">
+        <is>
+          <t>Automate by connecting thousands of apps
+AI processing steps
+No code
+Free tier</t>
+        </is>
+      </c>
+      <c r="O273" s="32" t="n"/>
     </row>
     <row r="274" ht="66" customHeight="1" s="29">
       <c r="A274" s="30" t="inlineStr">
@@ -17532,6 +20496,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M274" s="32" t="n"/>
+      <c r="N274" s="32" t="inlineStr">
+        <is>
+          <t>Design automations as flowcharts
+Complex logic with branches
+Many app integrations
+Free tier</t>
+        </is>
+      </c>
+      <c r="O274" s="32" t="n"/>
     </row>
     <row r="275" ht="66" customHeight="1" s="29">
       <c r="A275" s="30" t="inlineStr">
@@ -17589,6 +20563,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M275" s="32" t="n"/>
+      <c r="N275" s="32" t="inlineStr">
+        <is>
+          <t>Simple if-this-then-that automation
+Works with phones and smart devices
+Beginner-friendly
+Free tier</t>
+        </is>
+      </c>
+      <c r="O275" s="32" t="n"/>
     </row>
     <row r="276" ht="66" customHeight="1" s="29">
       <c r="A276" s="30" t="inlineStr">
@@ -17646,6 +20630,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M276" s="33" t="n"/>
+      <c r="N276" s="33" t="inlineStr">
+        <is>
+          <t>Automation flows with AI
+Free when self-hosted
+Write code when needed
+Open source</t>
+        </is>
+      </c>
+      <c r="O276" s="33" t="inlineStr">
+        <is>
+          <t>Free when self-hosted</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="66" customHeight="1" s="29">
       <c r="A277" s="30" t="inlineStr">
@@ -17703,6 +20701,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M277" s="32" t="n"/>
+      <c r="N277" s="32" t="inlineStr">
+        <is>
+          <t>Full-featured RPA
+Automates screens and documents
+AI agents
+Free Community edition</t>
+        </is>
+      </c>
+      <c r="O277" s="32" t="inlineStr">
+        <is>
+          <t>Community edition is free (individuals and small teams)</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="66" customHeight="1" s="29">
       <c r="A278" s="30" t="inlineStr">
@@ -17760,6 +20772,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M278" s="32" t="n"/>
+      <c r="N278" s="32" t="inlineStr">
+        <is>
+          <t>Cloud RPA
+Reads documents with AI
+Workflow management
+Community edition</t>
+        </is>
+      </c>
+      <c r="O278" s="32" t="n"/>
     </row>
     <row r="279" ht="66" customHeight="1" s="29">
       <c r="A279" s="30" t="inlineStr">
@@ -17817,6 +20839,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M279" s="32" t="n"/>
+      <c r="N279" s="32" t="inlineStr">
+        <is>
+          <t>Automates browser tasks
+Collects data from web pages
+Works with spreadsheets
+Free tier</t>
+        </is>
+      </c>
+      <c r="O279" s="32" t="n"/>
     </row>
     <row r="280" ht="66" customHeight="1" s="29">
       <c r="A280" s="30" t="inlineStr">
@@ -17874,6 +20906,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M280" s="33" t="n"/>
+      <c r="N280" s="33" t="inlineStr">
+        <is>
+          <t>Automation with AI steps
+Add human approval steps
+Works with Gmail and Slack
+Free tier</t>
+        </is>
+      </c>
+      <c r="O280" s="33" t="n"/>
     </row>
     <row r="281" ht="66" customHeight="1" s="29">
       <c r="A281" s="30" t="inlineStr">
@@ -17931,6 +20973,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M281" s="32" t="n"/>
+      <c r="N281" s="32" t="inlineStr">
+        <is>
+          <t>AI agents that handle email and scheduling
+Start from templates
+Many app integrations
+Free tier</t>
+        </is>
+      </c>
+      <c r="O281" s="32" t="n"/>
     </row>
     <row r="282" ht="66" customHeight="1" s="29">
       <c r="A282" s="30" t="inlineStr">
@@ -17988,6 +21040,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M282" s="32" t="n"/>
+      <c r="N282" s="32" t="inlineStr">
+        <is>
+          <t>Blocks time for work on your calendar
+Reschedules automatically
+Protects habit time
+Google Calendar integration</t>
+        </is>
+      </c>
+      <c r="O282" s="32" t="n"/>
     </row>
     <row r="283" ht="66" customHeight="1" s="29">
       <c r="A283" s="30" t="inlineStr">
@@ -18045,6 +21107,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M283" s="32" t="n"/>
+      <c r="N283" s="32" t="inlineStr">
+        <is>
+          <t>Builds your daily plan from tasks
+Replans when things change
+Project management
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O283" s="32" t="n"/>
     </row>
     <row r="284" ht="66" customHeight="1" s="29">
       <c r="A284" s="30" t="inlineStr">
@@ -18102,6 +21174,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M284" s="32" t="n"/>
+      <c r="N284" s="32" t="inlineStr">
+        <is>
+          <t>Logo ideas from your company name
+Business cards and social assets
+Brand kit
+Downloads are paid</t>
+        </is>
+      </c>
+      <c r="O284" s="32" t="inlineStr">
+        <is>
+          <t>Designing is free; downloads are paid</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="66" customHeight="1" s="29">
       <c r="A285" s="30" t="inlineStr">
@@ -18159,6 +21245,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M285" s="32" t="n"/>
+      <c r="N285" s="32" t="inlineStr">
+        <is>
+          <t>Automatic slide layouts
+Templates
+Consistent team design
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O285" s="32" t="n"/>
     </row>
     <row r="286" ht="66" customHeight="1" s="29">
       <c r="A286" s="30" t="inlineStr">
@@ -18216,6 +21312,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M286" s="32" t="n"/>
+      <c r="N286" s="32" t="inlineStr">
+        <is>
+          <t>App screens from hand sketches
+Turns screenshots into editable designs
+Prototype screen flows
+Free tier</t>
+        </is>
+      </c>
+      <c r="O286" s="32" t="n"/>
     </row>
     <row r="287" ht="66" customHeight="1" s="29">
       <c r="A287" s="30" t="inlineStr">
@@ -18273,6 +21379,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M287" s="33" t="n"/>
+      <c r="N287" s="33" t="inlineStr">
+        <is>
+          <t>The standard UI design tool
+Prototype screens with AI
+Real-time collaboration
+Free plan</t>
+        </is>
+      </c>
+      <c r="O287" s="33" t="n"/>
     </row>
     <row r="288" ht="66" customHeight="1" s="29">
       <c r="A288" s="30" t="inlineStr">
@@ -18330,6 +21446,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M288" s="32" t="n"/>
+      <c r="N288" s="32" t="inlineStr">
+        <is>
+          <t>Publish websites straight from your design
+Generate pages with AI
+Animations
+Free tier</t>
+        </is>
+      </c>
+      <c r="O288" s="32" t="n"/>
     </row>
     <row r="289" ht="66" customHeight="1" s="29">
       <c r="A289" s="30" t="inlineStr">
@@ -18387,6 +21513,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M289" s="32" t="n"/>
+      <c r="N289" s="32" t="inlineStr">
+        <is>
+          <t>Generates app and web screens from text
+Export to Figma
+Code output
+Free from Google</t>
+        </is>
+      </c>
+      <c r="O289" s="32" t="n"/>
     </row>
     <row r="290" ht="66" customHeight="1" s="29">
       <c r="A290" s="30" t="inlineStr">
@@ -18444,6 +21580,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M290" s="32" t="n"/>
+      <c r="N290" s="32" t="inlineStr">
+        <is>
+          <t>Logo and T-shirt design
+Rich text effects
+AI image generation
+Templates</t>
+        </is>
+      </c>
+      <c r="O290" s="32" t="n"/>
     </row>
     <row r="291" ht="66" customHeight="1" s="29">
       <c r="A291" s="30" t="inlineStr">
@@ -18501,6 +21647,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M291" s="32" t="n"/>
+      <c r="N291" s="32" t="inlineStr">
+        <is>
+          <t>Online whiteboard
+AI organizes sticky notes and diagrams
+Real-time collaboration
+Free tier</t>
+        </is>
+      </c>
+      <c r="O291" s="32" t="n"/>
     </row>
     <row r="292" ht="66" customHeight="1" s="29">
       <c r="A292" s="30" t="inlineStr">
@@ -18558,6 +21714,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M292" s="32" t="n"/>
+      <c r="N292" s="32" t="inlineStr">
+        <is>
+          <t>Build chatbots without code
+Embed on web or WhatsApp
+Design conversations as flows
+Free tier</t>
+        </is>
+      </c>
+      <c r="O292" s="32" t="n"/>
     </row>
     <row r="293" ht="66" customHeight="1" s="29">
       <c r="A293" s="30" t="inlineStr">
@@ -18615,6 +21781,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M293" s="32" t="n"/>
+      <c r="N293" s="32" t="inlineStr">
+        <is>
+          <t>Builds a website from your business type
+Booking and invoicing
+For small businesses
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O293" s="32" t="n"/>
     </row>
     <row r="294" ht="66" customHeight="1" s="29">
       <c r="A294" s="30" t="inlineStr">
@@ -18672,6 +21848,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M294" s="32" t="n"/>
+      <c r="N294" s="32" t="inlineStr">
+        <is>
+          <t>AI tutor that guides instead of giving answers
+Math, science and writing
+Free for teachers
+By Khan Academy</t>
+        </is>
+      </c>
+      <c r="O294" s="32" t="inlineStr">
+        <is>
+          <t>Free for teachers</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="66" customHeight="1" s="29">
       <c r="A295" s="30" t="inlineStr">
@@ -18729,6 +21919,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M295" s="32" t="n"/>
+      <c r="N295" s="32" t="inlineStr">
+        <is>
+          <t>Flashcards for memorizing
+AI-generated questions
+Practice tests
+Free tier</t>
+        </is>
+      </c>
+      <c r="O295" s="32" t="n"/>
     </row>
     <row r="296" ht="66" customHeight="1" s="29">
       <c r="A296" s="30" t="inlineStr">
@@ -18790,6 +21990,20 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M296" s="32" t="n"/>
+      <c r="N296" s="32" t="inlineStr">
+        <is>
+          <t>Shows how to solve a photographed equation
+Step-by-step explanations
+Graphs
+Basic features are free</t>
+        </is>
+      </c>
+      <c r="O296" s="32" t="inlineStr">
+        <is>
+          <t>Basic explanations are free</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="66" customHeight="1" s="29">
       <c r="A297" s="30" t="inlineStr">
@@ -18847,6 +22061,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M297" s="32" t="n"/>
+      <c r="N297" s="32" t="inlineStr">
+        <is>
+          <t>AI explains photographed problems
+Math, science and English
+Homework help
+Free tier</t>
+        </is>
+      </c>
+      <c r="O297" s="32" t="n"/>
     </row>
     <row r="298" ht="66" customHeight="1" s="29">
       <c r="A298" s="30" t="inlineStr">
@@ -18904,6 +22128,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M298" s="32" t="n"/>
+      <c r="N298" s="32" t="inlineStr">
+        <is>
+          <t>Post homework questions
+Answers from AI and users
+Many subjects
+Free tier</t>
+        </is>
+      </c>
+      <c r="O298" s="32" t="n"/>
     </row>
     <row r="299" ht="66" customHeight="1" s="29">
       <c r="A299" s="30" t="inlineStr">
@@ -18965,6 +22199,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M299" s="32" t="n"/>
+      <c r="N299" s="32" t="inlineStr">
+        <is>
+          <t>Step-by-step math solutions
+Graphing calculator
+Practice problems
+Free tier</t>
+        </is>
+      </c>
+      <c r="O299" s="32" t="n"/>
     </row>
     <row r="300" ht="66" customHeight="1" s="29">
       <c r="A300" s="30" t="inlineStr">
@@ -19026,6 +22270,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M300" s="32" t="n"/>
+      <c r="N300" s="32" t="inlineStr">
+        <is>
+          <t>Enter math problems for answers
+Algebra, calculus and statistics
+Camera input
+Steps are paid</t>
+        </is>
+      </c>
+      <c r="O300" s="32" t="n"/>
     </row>
     <row r="301" ht="66" customHeight="1" s="29">
       <c r="A301" s="30" t="inlineStr">
@@ -19083,6 +22337,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M301" s="32" t="n"/>
+      <c r="N301" s="32" t="inlineStr">
+        <is>
+          <t>AI scores your English pronunciation
+Advice for each sound
+Conversation practice
+Japanese support</t>
+        </is>
+      </c>
+      <c r="O301" s="32" t="n"/>
     </row>
     <row r="302" ht="66" customHeight="1" s="29">
       <c r="A302" s="30" t="inlineStr">
@@ -19140,6 +22404,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M302" s="33" t="n"/>
+      <c r="N302" s="33" t="inlineStr">
+        <is>
+          <t>Practice English conversation with AI
+Feedback on what you say
+Lessons by situation
+Paid after the trial</t>
+        </is>
+      </c>
+      <c r="O302" s="33" t="n"/>
     </row>
     <row r="303" ht="66" customHeight="1" s="29">
       <c r="A303" s="30" t="inlineStr">
@@ -19197,6 +22471,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M303" s="32" t="n"/>
+      <c r="N303" s="32" t="inlineStr">
+        <is>
+          <t>Learn languages like a game
+40+ languages
+Easy to keep going every day
+Free to use</t>
+        </is>
+      </c>
+      <c r="O303" s="32" t="n"/>
     </row>
     <row r="304" ht="66" customHeight="1" s="29">
       <c r="A304" s="30" t="inlineStr">
@@ -19254,6 +22538,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M304" s="32" t="n"/>
+      <c r="N304" s="32" t="inlineStr">
+        <is>
+          <t>Creates materials and tests for teachers
+Lesson planning
+Feedback comments for students
+Free tier</t>
+        </is>
+      </c>
+      <c r="O304" s="32" t="n"/>
     </row>
     <row r="305" ht="66" customHeight="1" s="29">
       <c r="A305" s="30" t="inlineStr">
@@ -19311,6 +22605,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M305" s="32" t="n"/>
+      <c r="N305" s="32" t="inlineStr">
+        <is>
+          <t>Makes flashcards from notes and PDFs
+AI summaries
+Exam practice
+Free tier</t>
+        </is>
+      </c>
+      <c r="O305" s="32" t="n"/>
     </row>
     <row r="306" ht="66" customHeight="1" s="29">
       <c r="A306" s="30" t="inlineStr">
@@ -19370,6 +22674,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M306" s="32" t="n"/>
+      <c r="N306" s="32" t="inlineStr">
+        <is>
+          <t>Chat with your favorite characters
+Create your own characters
+Voice conversation
+Free tier</t>
+        </is>
+      </c>
+      <c r="O306" s="32" t="n"/>
     </row>
     <row r="307" ht="66" customHeight="1" s="29">
       <c r="A307" s="30" t="inlineStr">
@@ -19427,6 +22741,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M307" s="32" t="n"/>
+      <c r="N307" s="32" t="inlineStr">
+        <is>
+          <t>An AI companion to talk to
+Diary-like conversations
+Mood tracking
+Free tier</t>
+        </is>
+      </c>
+      <c r="O307" s="32" t="n"/>
     </row>
     <row r="308" ht="66" customHeight="1" s="29">
       <c r="A308" s="30" t="inlineStr">
@@ -19484,6 +22808,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M308" s="32" t="n"/>
+      <c r="N308" s="32" t="inlineStr">
+        <is>
+          <t>Conversations based on CBT ideas
+Talk anonymously
+Relaxation exercises
+Free tier</t>
+        </is>
+      </c>
+      <c r="O308" s="32" t="n"/>
     </row>
     <row r="309" ht="66" customHeight="1" s="29">
       <c r="A309" s="30" t="inlineStr">
@@ -19541,6 +22875,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M309" s="32" t="n"/>
+      <c r="N309" s="32" t="inlineStr">
+        <is>
+          <t>Japanese mental-care app
+Talk to an AI about your feelings
+Mood tracking
+Psychology-based exercises</t>
+        </is>
+      </c>
+      <c r="O309" s="32" t="n"/>
     </row>
     <row r="310" ht="66" customHeight="1" s="29">
       <c r="A310" s="30" t="inlineStr">
@@ -19598,6 +22942,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M310" s="32" t="n"/>
+      <c r="N310" s="32" t="inlineStr">
+        <is>
+          <t>Japanese AI you chat with by voice
+Casual conversation partner
+Natural responses
+Free</t>
+        </is>
+      </c>
+      <c r="O310" s="32" t="n"/>
     </row>
     <row r="311" ht="66" customHeight="1" s="29">
       <c r="A311" s="30" t="inlineStr">
@@ -19655,6 +23009,16 @@
           <t>スマホのみ</t>
         </is>
       </c>
+      <c r="M311" s="32" t="n"/>
+      <c r="N311" s="32" t="inlineStr">
+        <is>
+          <t>Symptom check by answering questions
+Possible causes
+Guidance on seeing a doctor
+Free</t>
+        </is>
+      </c>
+      <c r="O311" s="32" t="n"/>
     </row>
     <row r="312" ht="66" customHeight="1" s="29">
       <c r="A312" s="22" t="inlineStr">
@@ -19716,6 +23080,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M312" s="32" t="inlineStr">
+        <is>
+          <t>Ubie</t>
+        </is>
+      </c>
+      <c r="N312" s="32" t="inlineStr">
+        <is>
+          <t>Answer questions about symptoms in Japanese
+Related conditions and where to go
+Hospital search
+Free</t>
+        </is>
+      </c>
+      <c r="O312" s="32" t="n"/>
     </row>
     <row r="313" ht="66" customHeight="1" s="29">
       <c r="A313" s="30" t="inlineStr">
@@ -19777,6 +23155,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M313" s="32" t="n"/>
+      <c r="N313" s="32" t="inlineStr">
+        <is>
+          <t>Symptom checker
+How urgent it is to see a doctor
+Multilingual
+No sign-up</t>
+        </is>
+      </c>
+      <c r="O313" s="32" t="n"/>
     </row>
     <row r="314" ht="66" customHeight="1" s="29">
       <c r="A314" s="30" t="inlineStr">
@@ -19834,6 +23222,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M314" s="32" t="n"/>
+      <c r="N314" s="32" t="inlineStr">
+        <is>
+          <t>Symptom checker
+Guidance on where to get care
+For English speakers
+Free</t>
+        </is>
+      </c>
+      <c r="O314" s="32" t="n"/>
     </row>
     <row r="315" ht="66" customHeight="1" s="29">
       <c r="A315" s="30" t="inlineStr">
@@ -19891,6 +23289,20 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M315" s="32" t="n"/>
+      <c r="N315" s="32" t="inlineStr">
+        <is>
+          <t>Answers based on medical papers
+Shows the source papers
+For healthcare professionals
+Free for professionals</t>
+        </is>
+      </c>
+      <c r="O315" s="32" t="inlineStr">
+        <is>
+          <t>Free for healthcare professionals</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="66" customHeight="1" s="29">
       <c r="A316" s="30" t="inlineStr">
@@ -19948,6 +23360,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M316" s="32" t="n"/>
+      <c r="N316" s="32" t="inlineStr">
+        <is>
+          <t>Diagnostic support for clinicians
+Differential diagnosis ideas
+Clinical note drafting
+Free tier</t>
+        </is>
+      </c>
+      <c r="O316" s="32" t="n"/>
     </row>
     <row r="317" ht="66" customHeight="1" s="29">
       <c r="A317" s="30" t="inlineStr">
@@ -20005,6 +23427,16 @@
           <t>PC＋スマホ</t>
         </is>
       </c>
+      <c r="M317" s="32" t="n"/>
+      <c r="N317" s="32" t="inlineStr">
+        <is>
+          <t>Symptom checker
+Health articles
+Self-care suggestions
+Free</t>
+        </is>
+      </c>
+      <c r="O317" s="32" t="n"/>
     </row>
     <row r="318" ht="66" customHeight="1" s="29">
       <c r="A318" s="30" t="inlineStr">
@@ -20062,6 +23494,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M318" s="32" t="n"/>
+      <c r="N318" s="32" t="inlineStr">
+        <is>
+          <t>Simulates robots in a virtual world
+Creates AI training data
+Physics simulation
+Free</t>
+        </is>
+      </c>
+      <c r="O318" s="32" t="n"/>
     </row>
     <row r="319" ht="66" customHeight="1" s="29">
       <c r="A319" s="30" t="inlineStr">
@@ -20119,6 +23561,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M319" s="32" t="n"/>
+      <c r="N319" s="32" t="inlineStr">
+        <is>
+          <t>Standard framework for building robots
+Lots of sensor and motor packages
+Widely used in research
+Free</t>
+        </is>
+      </c>
+      <c r="O319" s="32" t="n"/>
     </row>
     <row r="320" ht="66" customHeight="1" s="29">
       <c r="A320" s="30" t="inlineStr">
@@ -20176,6 +23628,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M320" s="32" t="n"/>
+      <c r="N320" s="32" t="inlineStr">
+        <is>
+          <t>Train AI with low-cost robot arms
+Share trained models and data
+Develop in Python
+Free</t>
+        </is>
+      </c>
+      <c r="O320" s="32" t="n"/>
     </row>
     <row r="321" ht="66" customHeight="1" s="29">
       <c r="A321" s="30" t="inlineStr">
@@ -20233,6 +23695,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M321" s="32" t="n"/>
+      <c r="N321" s="32" t="inlineStr">
+        <is>
+          <t>Build AI that runs on microcontrollers
+Analyze sensor data
+Train through a visual interface
+Free tier</t>
+        </is>
+      </c>
+      <c r="O321" s="32" t="n"/>
     </row>
     <row r="322" ht="66" customHeight="1" s="29">
       <c r="A322" s="30" t="inlineStr">
@@ -20290,6 +23762,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M322" s="32" t="n"/>
+      <c r="N322" s="32" t="inlineStr">
+        <is>
+          <t>Build image recognition models
+Label images
+Used for visual inspection
+Free tier</t>
+        </is>
+      </c>
+      <c r="O322" s="32" t="n"/>
     </row>
     <row r="323" ht="66" customHeight="1" s="29">
       <c r="A323" s="30" t="inlineStr">
@@ -20347,6 +23829,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M323" s="32" t="n"/>
+      <c r="N323" s="32" t="inlineStr">
+        <is>
+          <t>Real-time object detection
+A few lines of Python
+Runs on phones and small devices
+Open source</t>
+        </is>
+      </c>
+      <c r="O323" s="32" t="n"/>
     </row>
     <row r="324" ht="66" customHeight="1" s="29">
       <c r="A324" s="30" t="inlineStr">
@@ -20404,6 +23896,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M324" s="32" t="n"/>
+      <c r="N324" s="32" t="inlineStr">
+        <is>
+          <t>The standard image processing library
+Analyzes camera video
+Detects faces and objects
+Free</t>
+        </is>
+      </c>
+      <c r="O324" s="32" t="n"/>
     </row>
     <row r="325" ht="66" customHeight="1" s="29">
       <c r="A325" s="30" t="inlineStr">
@@ -20461,6 +23963,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M325" s="32" t="n"/>
+      <c r="N325" s="32" t="inlineStr">
+        <is>
+          <t>Visual inspection AI for manufacturing
+Learns from few images
+Extracts data from documents
+Free tier</t>
+        </is>
+      </c>
+      <c r="O325" s="32" t="n"/>
     </row>
     <row r="326" ht="66" customHeight="1" s="29">
       <c r="A326" s="30" t="inlineStr">
@@ -20518,6 +24030,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M326" s="32" t="n"/>
+      <c r="N326" s="32" t="inlineStr">
+        <is>
+          <t>Robot simulation software
+For education and research
+Many robot models
+Free</t>
+        </is>
+      </c>
+      <c r="O326" s="32" t="n"/>
     </row>
     <row r="327" ht="66" customHeight="1" s="29">
       <c r="A327" s="30" t="inlineStr">
@@ -20575,6 +24097,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M327" s="32" t="n"/>
+      <c r="N327" s="32" t="inlineStr">
+        <is>
+          <t>Accurate physics simulation
+Reinforcement learning for robots
+Made by DeepMind
+Free</t>
+        </is>
+      </c>
+      <c r="O327" s="32" t="n"/>
     </row>
     <row r="328" ht="66" customHeight="1" s="29">
       <c r="A328" s="30" t="inlineStr">
@@ -20632,6 +24164,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M328" s="32" t="n"/>
+      <c r="N328" s="32" t="inlineStr">
+        <is>
+          <t>3D models from text or images
+Automatic textures
+Export to Unity and Blender
+Free tier</t>
+        </is>
+      </c>
+      <c r="O328" s="32" t="n"/>
     </row>
     <row r="329" ht="66" customHeight="1" s="29">
       <c r="A329" s="30" t="inlineStr">
@@ -20689,6 +24231,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M329" s="32" t="n"/>
+      <c r="N329" s="32" t="inlineStr">
+        <is>
+          <t>3D model from a single image
+Rigging for animation
+For game assets
+Free tier</t>
+        </is>
+      </c>
+      <c r="O329" s="32" t="n"/>
     </row>
     <row r="330" ht="66" customHeight="1" s="29">
       <c r="A330" s="30" t="inlineStr">
@@ -20746,6 +24298,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M330" s="32" t="n"/>
+      <c r="N330" s="32" t="inlineStr">
+        <is>
+          <t>Detailed 3D model generation
+From images or text
+Professional quality
+Free tier</t>
+        </is>
+      </c>
+      <c r="O330" s="32" t="n"/>
     </row>
     <row r="331" ht="66" customHeight="1" s="29">
       <c r="A331" s="30" t="inlineStr">
@@ -20803,6 +24365,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M331" s="33" t="n"/>
+      <c r="N331" s="33" t="inlineStr">
+        <is>
+          <t>Open 3D generation from Tencent
+Image to 3D
+With textures
+Free</t>
+        </is>
+      </c>
+      <c r="O331" s="33" t="n"/>
     </row>
     <row r="332" ht="66" customHeight="1" s="29">
       <c r="A332" s="30" t="inlineStr">
@@ -20860,6 +24432,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M332" s="33" t="n"/>
+      <c r="N332" s="33" t="inlineStr">
+        <is>
+          <t>Open 3D generation from Microsoft
+Image to 3D
+For research
+Runs locally</t>
+        </is>
+      </c>
+      <c r="O332" s="33" t="n"/>
     </row>
     <row r="333" ht="66" customHeight="1" s="29">
       <c r="A333" s="30" t="inlineStr">
@@ -20917,6 +24499,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M333" s="32" t="n"/>
+      <c r="N333" s="32" t="inlineStr">
+        <is>
+          <t>3D design in the browser
+Generate 3D objects with AI
+Embed on websites
+Free tier</t>
+        </is>
+      </c>
+      <c r="O333" s="32" t="n"/>
     </row>
     <row r="334" ht="66" customHeight="1" s="29">
       <c r="A334" s="30" t="inlineStr">
@@ -20974,6 +24566,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M334" s="32" t="n"/>
+      <c r="N334" s="32" t="inlineStr">
+        <is>
+          <t>Build browser games by chatting
+Publish your games
+Remix other people's games
+Free tier</t>
+        </is>
+      </c>
+      <c r="O334" s="32" t="n"/>
     </row>
     <row r="335" ht="66" customHeight="1" s="29">
       <c r="A335" s="30" t="inlineStr">
@@ -21031,6 +24633,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M335" s="33" t="n"/>
+      <c r="N335" s="33" t="inlineStr">
+        <is>
+          <t>AI assistant inside the Unity Editor
+Writes and fixes C# scripts
+Generates image and sound assets
+Depends on your Unity plan</t>
+        </is>
+      </c>
+      <c r="O335" s="33" t="inlineStr">
+        <is>
+          <t>Depends on your Unity plan</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="66" customHeight="1" s="29">
       <c r="A336" s="30" t="inlineStr">
@@ -21088,6 +24704,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M336" s="32" t="n"/>
+      <c r="N336" s="32" t="inlineStr">
+        <is>
+          <t>Natural conversations with game characters
+Set personality and memory
+Speech synthesis
+Unity and Unreal support</t>
+        </is>
+      </c>
+      <c r="O336" s="32" t="n"/>
     </row>
     <row r="337" ht="66" customHeight="1" s="29">
       <c r="A337" s="30" t="inlineStr">
@@ -21145,6 +24771,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M337" s="33" t="n"/>
+      <c r="N337" s="33" t="inlineStr">
+        <is>
+          <t>AI built into Android Studio
+Generates and explains Kotlin code
+Explains the cause of errors
+Free for individuals</t>
+        </is>
+      </c>
+      <c r="O337" s="33" t="inlineStr">
+        <is>
+          <t>Free for individuals</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="66" customHeight="1" s="29">
       <c r="A338" s="30" t="inlineStr">
@@ -21202,6 +24842,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M338" s="32" t="n"/>
+      <c r="N338" s="32" t="inlineStr">
+        <is>
+          <t>Build mobile apps without code
+Generate screens with AI
+Export Flutter code
+Firebase integration</t>
+        </is>
+      </c>
+      <c r="O338" s="32" t="n"/>
     </row>
     <row r="339" ht="66" customHeight="1" s="29">
       <c r="A339" s="26" t="inlineStr">
@@ -21259,6 +24909,20 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M339" s="32" t="inlineStr">
+        <is>
+          <t>Better Analyst (formerly Formula Bot)</t>
+        </is>
+      </c>
+      <c r="N339" s="32" t="inlineStr">
+        <is>
+          <t>Analyze data by chatting and make charts
+Generates Excel and spreadsheet formulas
+Converts PDF tables to Excel
+Automates dashboards and reports</t>
+        </is>
+      </c>
+      <c r="O339" s="32" t="n"/>
     </row>
     <row r="340" ht="66" customHeight="1" s="29">
       <c r="A340" s="30" t="inlineStr">
@@ -21316,6 +24980,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M340" s="32" t="n"/>
+      <c r="N340" s="32" t="inlineStr">
+        <is>
+          <t>Use AI functions in spreadsheets
+Classify and summarize lots of data
+Excel and Google Sheets
+Free tier</t>
+        </is>
+      </c>
+      <c r="O340" s="32" t="n"/>
     </row>
     <row r="341" ht="66" customHeight="1" s="29">
       <c r="A341" s="30" t="inlineStr">
@@ -21373,6 +25047,16 @@
           <t>PCのみ</t>
         </is>
       </c>
+      <c r="M341" s="33" t="n"/>
+      <c r="N341" s="33" t="inlineStr">
+        <is>
+          <t>Generates Excel and spreadsheet formulas
+Explains and fixes formulas
+Writes VBA and Apps Script
+Free tier</t>
+        </is>
+      </c>
+      <c r="O341" s="33" t="n"/>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="29">
       <c r="G342" s="28" t="n"/>
@@ -25287,7 +28971,7 @@
       <c r="K993" s="28" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L993">
+  <autoFilter ref="A1:O993">
     <filterColumn colId="0" hiddenButton="0" showButton="1">
       <filters blank="1">
         <filter val="UiPath"/>

--- a/data/ai-tools.xlsx
+++ b/data/ai-tools.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIツール一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カテゴリ一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AIツール一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="カテゴリ一覧" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AIツール一覧'!$A$1:$O$993</definedName>
@@ -1748,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O991"/>
+  <dimension ref="A1:O990"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24" customWidth="1" style="29" min="1" max="1"/>
@@ -23243,97 +23243,30 @@
     <row r="315" ht="66" customHeight="1" s="29">
       <c r="A315" s="30" t="inlineStr">
         <is>
-          <t>Healthily</t>
+          <t>NVIDIA Isaac Sim</t>
         </is>
       </c>
       <c r="B315" s="33" t="inlineStr">
         <is>
-          <t>https://www.livehealthily.com</t>
+          <t>https://developer.nvidia.com/isaac/sim</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
         <is>
-          <t>イギリス</t>
+          <t>アメリカ</t>
         </is>
       </c>
       <c r="D315" s="33" t="inlineStr">
         <is>
-          <t>Healthily</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E315" s="32" t="inlineStr">
         <is>
-          <t>医療・ヘルスケア</t>
+          <t>製造・ロボティクス</t>
         </is>
       </c>
       <c r="F315" s="32" t="inlineStr">
-        <is>
-          <t>症状チェック
-健康に関する記事
-セルフケアの提案
-無料</t>
-        </is>
-      </c>
-      <c r="G315" s="34" t="inlineStr">
-        <is>
-          <t>完全無料</t>
-        </is>
-      </c>
-      <c r="H315" s="32" t="inlineStr">
-        <is>
-          <t>無料で利用可能</t>
-        </is>
-      </c>
-      <c r="I315" s="35" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="J315" s="35" t="n"/>
-      <c r="K315" s="35" t="n"/>
-      <c r="L315" s="35" t="inlineStr">
-        <is>
-          <t>PC＋スマホ</t>
-        </is>
-      </c>
-      <c r="M315" s="32" t="n"/>
-      <c r="N315" s="32" t="inlineStr">
-        <is>
-          <t>Symptom checker
-Health articles
-Self-care suggestions
-Free</t>
-        </is>
-      </c>
-      <c r="O315" s="32" t="n"/>
-    </row>
-    <row r="316" ht="66" customHeight="1" s="29">
-      <c r="A316" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA Isaac Sim</t>
-        </is>
-      </c>
-      <c r="B316" s="33" t="inlineStr">
-        <is>
-          <t>https://developer.nvidia.com/isaac/sim</t>
-        </is>
-      </c>
-      <c r="C316" s="32" t="inlineStr">
-        <is>
-          <t>アメリカ</t>
-        </is>
-      </c>
-      <c r="D316" s="33" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="E316" s="32" t="inlineStr">
-        <is>
-          <t>製造・ロボティクス</t>
-        </is>
-      </c>
-      <c r="F316" s="32" t="inlineStr">
         <is>
           <t>ロボットの動きを仮想空間でシミュレーション
 AIの学習データ作成
@@ -23341,30 +23274,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G316" s="34" t="inlineStr">
+      <c r="G315" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H316" s="32" t="inlineStr">
+      <c r="H315" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I316" s="35" t="inlineStr">
+      <c r="I315" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J316" s="35" t="n"/>
-      <c r="K316" s="35" t="n"/>
-      <c r="L316" s="35" t="inlineStr">
+      <c r="J315" s="35" t="n"/>
+      <c r="K315" s="35" t="n"/>
+      <c r="L315" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M316" s="32" t="n"/>
-      <c r="N316" s="32" t="inlineStr">
+      <c r="M315" s="32" t="n"/>
+      <c r="N315" s="32" t="inlineStr">
         <is>
           <t>Simulates robots in a virtual world
 Creates AI training data
@@ -23372,35 +23305,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O316" s="32" t="n"/>
-    </row>
-    <row r="317" ht="66" customHeight="1" s="29">
-      <c r="A317" s="30" t="inlineStr">
+      <c r="O315" s="32" t="n"/>
+    </row>
+    <row r="316" ht="66" customHeight="1" s="29">
+      <c r="A316" s="30" t="inlineStr">
         <is>
           <t>ROS 2</t>
         </is>
       </c>
-      <c r="B317" s="33" t="inlineStr">
+      <c r="B316" s="33" t="inlineStr">
         <is>
           <t>https://www.ros.org</t>
         </is>
       </c>
-      <c r="C317" s="32" t="inlineStr">
+      <c r="C316" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D317" s="33" t="inlineStr">
+      <c r="D316" s="33" t="inlineStr">
         <is>
           <t>Open Robotics</t>
         </is>
       </c>
-      <c r="E317" s="32" t="inlineStr">
+      <c r="E316" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス</t>
         </is>
       </c>
-      <c r="F317" s="32" t="inlineStr">
+      <c r="F316" s="32" t="inlineStr">
         <is>
           <t>ロボット開発の標準的な仕組み
 センサー・モーターの部品が豊富
@@ -23408,30 +23341,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G317" s="34" t="inlineStr">
+      <c r="G316" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H317" s="32" t="inlineStr">
+      <c r="H316" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I317" s="35" t="inlineStr">
+      <c r="I316" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J317" s="35" t="n"/>
-      <c r="K317" s="35" t="n"/>
-      <c r="L317" s="35" t="inlineStr">
+      <c r="J316" s="35" t="n"/>
+      <c r="K316" s="35" t="n"/>
+      <c r="L316" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M317" s="32" t="n"/>
-      <c r="N317" s="32" t="inlineStr">
+      <c r="M316" s="32" t="n"/>
+      <c r="N316" s="32" t="inlineStr">
         <is>
           <t>Standard framework for building robots
 Lots of sensor and motor packages
@@ -23439,35 +23372,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O317" s="32" t="n"/>
-    </row>
-    <row r="318" ht="66" customHeight="1" s="29">
-      <c r="A318" s="30" t="inlineStr">
+      <c r="O316" s="32" t="n"/>
+    </row>
+    <row r="317" ht="66" customHeight="1" s="29">
+      <c r="A317" s="30" t="inlineStr">
         <is>
           <t>LeRobot</t>
         </is>
       </c>
-      <c r="B318" s="33" t="inlineStr">
+      <c r="B317" s="33" t="inlineStr">
         <is>
           <t>https://huggingface.co/lerobot</t>
         </is>
       </c>
-      <c r="C318" s="32" t="inlineStr">
+      <c r="C317" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D318" s="33" t="inlineStr">
+      <c r="D317" s="33" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
       </c>
-      <c r="E318" s="32" t="inlineStr">
+      <c r="E317" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、開発者向けツール</t>
         </is>
       </c>
-      <c r="F318" s="32" t="inlineStr">
+      <c r="F317" s="32" t="inlineStr">
         <is>
           <t>安価なロボットアームでAIを学習
 学習済みモデルとデータを共有
@@ -23475,30 +23408,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G318" s="34" t="inlineStr">
+      <c r="G317" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H318" s="32" t="inlineStr">
+      <c r="H317" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I318" s="35" t="inlineStr">
+      <c r="I317" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J318" s="35" t="n"/>
-      <c r="K318" s="35" t="n"/>
-      <c r="L318" s="35" t="inlineStr">
+      <c r="J317" s="35" t="n"/>
+      <c r="K317" s="35" t="n"/>
+      <c r="L317" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M318" s="32" t="n"/>
-      <c r="N318" s="32" t="inlineStr">
+      <c r="M317" s="32" t="n"/>
+      <c r="N317" s="32" t="inlineStr">
         <is>
           <t>Train AI with low-cost robot arms
 Share trained models and data
@@ -23506,35 +23439,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O318" s="32" t="n"/>
-    </row>
-    <row r="319" ht="66" customHeight="1" s="29">
-      <c r="A319" s="30" t="inlineStr">
+      <c r="O317" s="32" t="n"/>
+    </row>
+    <row r="318" ht="66" customHeight="1" s="29">
+      <c r="A318" s="30" t="inlineStr">
         <is>
           <t>Edge Impulse</t>
         </is>
       </c>
-      <c r="B319" s="33" t="inlineStr">
+      <c r="B318" s="33" t="inlineStr">
         <is>
           <t>https://edgeimpulse.com</t>
         </is>
       </c>
-      <c r="C319" s="32" t="inlineStr">
+      <c r="C318" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D319" s="33" t="inlineStr">
+      <c r="D318" s="33" t="inlineStr">
         <is>
           <t>Edge Impulse（Qualcomm）</t>
         </is>
       </c>
-      <c r="E319" s="32" t="inlineStr">
+      <c r="E318" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、開発者向けツール</t>
         </is>
       </c>
-      <c r="F319" s="32" t="inlineStr">
+      <c r="F318" s="32" t="inlineStr">
         <is>
           <t>マイコン・小型機器で動くAIを作成
 センサーデータの分析
@@ -23542,30 +23475,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G319" s="34" t="inlineStr">
+      <c r="G318" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H319" s="32" t="inlineStr">
+      <c r="H318" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I319" s="35" t="inlineStr">
+      <c r="I318" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J319" s="35" t="n"/>
-      <c r="K319" s="35" t="n"/>
-      <c r="L319" s="35" t="inlineStr">
+      <c r="J318" s="35" t="n"/>
+      <c r="K318" s="35" t="n"/>
+      <c r="L318" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M319" s="32" t="n"/>
-      <c r="N319" s="32" t="inlineStr">
+      <c r="M318" s="32" t="n"/>
+      <c r="N318" s="32" t="inlineStr">
         <is>
           <t>Build AI that runs on microcontrollers
 Analyze sensor data
@@ -23573,35 +23506,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O319" s="32" t="n"/>
-    </row>
-    <row r="320" ht="66" customHeight="1" s="29">
-      <c r="A320" s="30" t="inlineStr">
+      <c r="O318" s="32" t="n"/>
+    </row>
+    <row r="319" ht="66" customHeight="1" s="29">
+      <c r="A319" s="30" t="inlineStr">
         <is>
           <t>Roboflow</t>
         </is>
       </c>
-      <c r="B320" s="33" t="inlineStr">
+      <c r="B319" s="33" t="inlineStr">
         <is>
           <t>https://roboflow.com</t>
         </is>
       </c>
-      <c r="C320" s="32" t="inlineStr">
+      <c r="C319" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D320" s="33" t="inlineStr">
+      <c r="D319" s="33" t="inlineStr">
         <is>
           <t>Roboflow</t>
         </is>
       </c>
-      <c r="E320" s="32" t="inlineStr">
+      <c r="E319" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、画像編集、開発者向けツール</t>
         </is>
       </c>
-      <c r="F320" s="32" t="inlineStr">
+      <c r="F319" s="32" t="inlineStr">
         <is>
           <t>画像認識モデルを作成
 画像へのラベル付け
@@ -23609,30 +23542,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G320" s="34" t="inlineStr">
+      <c r="G319" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H320" s="32" t="inlineStr">
+      <c r="H319" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I320" s="35" t="inlineStr">
+      <c r="I319" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J320" s="35" t="n"/>
-      <c r="K320" s="35" t="n"/>
-      <c r="L320" s="35" t="inlineStr">
+      <c r="J319" s="35" t="n"/>
+      <c r="K319" s="35" t="n"/>
+      <c r="L319" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M320" s="32" t="n"/>
-      <c r="N320" s="32" t="inlineStr">
+      <c r="M319" s="32" t="n"/>
+      <c r="N319" s="32" t="inlineStr">
         <is>
           <t>Build image recognition models
 Label images
@@ -23640,35 +23573,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O320" s="32" t="n"/>
-    </row>
-    <row r="321" ht="66" customHeight="1" s="29">
-      <c r="A321" s="30" t="inlineStr">
+      <c r="O319" s="32" t="n"/>
+    </row>
+    <row r="320" ht="66" customHeight="1" s="29">
+      <c r="A320" s="30" t="inlineStr">
         <is>
           <t>Ultralytics YOLO</t>
         </is>
       </c>
-      <c r="B321" s="33" t="inlineStr">
+      <c r="B320" s="33" t="inlineStr">
         <is>
           <t>https://www.ultralytics.com</t>
         </is>
       </c>
-      <c r="C321" s="32" t="inlineStr">
+      <c r="C320" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D321" s="33" t="inlineStr">
+      <c r="D320" s="33" t="inlineStr">
         <is>
           <t>Ultralytics</t>
         </is>
       </c>
-      <c r="E321" s="32" t="inlineStr">
+      <c r="E320" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、開発者向けツール</t>
         </is>
       </c>
-      <c r="F321" s="32" t="inlineStr">
+      <c r="F320" s="32" t="inlineStr">
         <is>
           <t>リアルタイムの物体検出
 数行のPythonで利用
@@ -23676,30 +23609,30 @@
 オープンソース</t>
         </is>
       </c>
-      <c r="G321" s="34" t="inlineStr">
+      <c r="G320" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H321" s="32" t="inlineStr">
+      <c r="H320" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I321" s="35" t="inlineStr">
+      <c r="I320" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J321" s="35" t="n"/>
-      <c r="K321" s="35" t="n"/>
-      <c r="L321" s="35" t="inlineStr">
+      <c r="J320" s="35" t="n"/>
+      <c r="K320" s="35" t="n"/>
+      <c r="L320" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M321" s="32" t="n"/>
-      <c r="N321" s="32" t="inlineStr">
+      <c r="M320" s="32" t="n"/>
+      <c r="N320" s="32" t="inlineStr">
         <is>
           <t>Real-time object detection
 A few lines of Python
@@ -23707,35 +23640,35 @@
 Open source</t>
         </is>
       </c>
-      <c r="O321" s="32" t="n"/>
-    </row>
-    <row r="322" ht="66" customHeight="1" s="29">
-      <c r="A322" s="30" t="inlineStr">
+      <c r="O320" s="32" t="n"/>
+    </row>
+    <row r="321" ht="66" customHeight="1" s="29">
+      <c r="A321" s="30" t="inlineStr">
         <is>
           <t>OpenCV</t>
         </is>
       </c>
-      <c r="B322" s="33" t="inlineStr">
+      <c r="B321" s="33" t="inlineStr">
         <is>
           <t>https://opencv.org</t>
         </is>
       </c>
-      <c r="C322" s="32" t="inlineStr">
+      <c r="C321" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D322" s="33" t="inlineStr">
+      <c r="D321" s="33" t="inlineStr">
         <is>
           <t>OpenCV.org</t>
         </is>
       </c>
-      <c r="E322" s="32" t="inlineStr">
+      <c r="E321" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、開発者向けツール</t>
         </is>
       </c>
-      <c r="F322" s="32" t="inlineStr">
+      <c r="F321" s="32" t="inlineStr">
         <is>
           <t>画像処理の定番ライブラリ
 カメラ映像の解析
@@ -23743,30 +23676,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G322" s="34" t="inlineStr">
+      <c r="G321" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H322" s="32" t="inlineStr">
+      <c r="H321" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I322" s="35" t="inlineStr">
+      <c r="I321" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J322" s="35" t="n"/>
-      <c r="K322" s="35" t="n"/>
-      <c r="L322" s="35" t="inlineStr">
+      <c r="J321" s="35" t="n"/>
+      <c r="K321" s="35" t="n"/>
+      <c r="L321" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M322" s="32" t="n"/>
-      <c r="N322" s="32" t="inlineStr">
+      <c r="M321" s="32" t="n"/>
+      <c r="N321" s="32" t="inlineStr">
         <is>
           <t>The standard image processing library
 Analyzes camera video
@@ -23774,35 +23707,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O322" s="32" t="n"/>
-    </row>
-    <row r="323" ht="66" customHeight="1" s="29">
-      <c r="A323" s="30" t="inlineStr">
+      <c r="O321" s="32" t="n"/>
+    </row>
+    <row r="322" ht="66" customHeight="1" s="29">
+      <c r="A322" s="30" t="inlineStr">
         <is>
           <t>LandingAI</t>
         </is>
       </c>
-      <c r="B323" s="33" t="inlineStr">
+      <c r="B322" s="33" t="inlineStr">
         <is>
           <t>https://landing.ai</t>
         </is>
       </c>
-      <c r="C323" s="32" t="inlineStr">
+      <c r="C322" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D323" s="33" t="inlineStr">
+      <c r="D322" s="33" t="inlineStr">
         <is>
           <t>LandingAI</t>
         </is>
       </c>
-      <c r="E323" s="32" t="inlineStr">
+      <c r="E322" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス</t>
         </is>
       </c>
-      <c r="F323" s="32" t="inlineStr">
+      <c r="F322" s="32" t="inlineStr">
         <is>
           <t>製造業の外観検査AI
 少ない画像で学習
@@ -23810,30 +23743,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G323" s="34" t="inlineStr">
+      <c r="G322" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H323" s="32" t="inlineStr">
+      <c r="H322" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I323" s="35" t="inlineStr">
+      <c r="I322" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J323" s="35" t="n"/>
-      <c r="K323" s="35" t="n"/>
-      <c r="L323" s="35" t="inlineStr">
+      <c r="J322" s="35" t="n"/>
+      <c r="K322" s="35" t="n"/>
+      <c r="L322" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M323" s="32" t="n"/>
-      <c r="N323" s="32" t="inlineStr">
+      <c r="M322" s="32" t="n"/>
+      <c r="N322" s="32" t="inlineStr">
         <is>
           <t>Visual inspection AI for manufacturing
 Learns from few images
@@ -23841,35 +23774,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O323" s="32" t="n"/>
-    </row>
-    <row r="324" ht="66" customHeight="1" s="29">
-      <c r="A324" s="30" t="inlineStr">
+      <c r="O322" s="32" t="n"/>
+    </row>
+    <row r="323" ht="66" customHeight="1" s="29">
+      <c r="A323" s="30" t="inlineStr">
         <is>
           <t>Webots</t>
         </is>
       </c>
-      <c r="B324" s="33" t="inlineStr">
+      <c r="B323" s="33" t="inlineStr">
         <is>
           <t>https://cyberbotics.com</t>
         </is>
       </c>
-      <c r="C324" s="32" t="inlineStr">
+      <c r="C323" s="32" t="inlineStr">
         <is>
           <t>スイス</t>
         </is>
       </c>
-      <c r="D324" s="33" t="inlineStr">
+      <c r="D323" s="33" t="inlineStr">
         <is>
           <t>Cyberbotics</t>
         </is>
       </c>
-      <c r="E324" s="32" t="inlineStr">
+      <c r="E323" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス、学習・教育</t>
         </is>
       </c>
-      <c r="F324" s="32" t="inlineStr">
+      <c r="F323" s="32" t="inlineStr">
         <is>
           <t>ロボットのシミュレーションソフト
 教育・研究向け
@@ -23877,30 +23810,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G324" s="34" t="inlineStr">
+      <c r="G323" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H324" s="32" t="inlineStr">
+      <c r="H323" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I324" s="35" t="inlineStr">
+      <c r="I323" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J324" s="35" t="n"/>
-      <c r="K324" s="35" t="n"/>
-      <c r="L324" s="35" t="inlineStr">
+      <c r="J323" s="35" t="n"/>
+      <c r="K323" s="35" t="n"/>
+      <c r="L323" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M324" s="32" t="n"/>
-      <c r="N324" s="32" t="inlineStr">
+      <c r="M323" s="32" t="n"/>
+      <c r="N323" s="32" t="inlineStr">
         <is>
           <t>Robot simulation software
 For education and research
@@ -23908,35 +23841,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O324" s="32" t="n"/>
-    </row>
-    <row r="325" ht="66" customHeight="1" s="29">
-      <c r="A325" s="30" t="inlineStr">
+      <c r="O323" s="32" t="n"/>
+    </row>
+    <row r="324" ht="66" customHeight="1" s="29">
+      <c r="A324" s="30" t="inlineStr">
         <is>
           <t>MuJoCo</t>
         </is>
       </c>
-      <c r="B325" s="33" t="inlineStr">
+      <c r="B324" s="33" t="inlineStr">
         <is>
           <t>https://mujoco.org</t>
         </is>
       </c>
-      <c r="C325" s="32" t="inlineStr">
+      <c r="C324" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D325" s="33" t="inlineStr">
+      <c r="D324" s="33" t="inlineStr">
         <is>
           <t>Google DeepMind</t>
         </is>
       </c>
-      <c r="E325" s="32" t="inlineStr">
+      <c r="E324" s="32" t="inlineStr">
         <is>
           <t>製造・ロボティクス</t>
         </is>
       </c>
-      <c r="F325" s="32" t="inlineStr">
+      <c r="F324" s="32" t="inlineStr">
         <is>
           <t>高精度な物理シミュレーション
 ロボットの強化学習
@@ -23944,30 +23877,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G325" s="34" t="inlineStr">
+      <c r="G324" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H325" s="32" t="inlineStr">
+      <c r="H324" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I325" s="35" t="inlineStr">
+      <c r="I324" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J325" s="35" t="n"/>
-      <c r="K325" s="35" t="n"/>
-      <c r="L325" s="35" t="inlineStr">
+      <c r="J324" s="35" t="n"/>
+      <c r="K324" s="35" t="n"/>
+      <c r="L324" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M325" s="32" t="n"/>
-      <c r="N325" s="32" t="inlineStr">
+      <c r="M324" s="32" t="n"/>
+      <c r="N324" s="32" t="inlineStr">
         <is>
           <t>Accurate physics simulation
 Reinforcement learning for robots
@@ -23975,35 +23908,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O325" s="32" t="n"/>
-    </row>
-    <row r="326" ht="66" customHeight="1" s="29">
-      <c r="A326" s="30" t="inlineStr">
+      <c r="O324" s="32" t="n"/>
+    </row>
+    <row r="325" ht="66" customHeight="1" s="29">
+      <c r="A325" s="30" t="inlineStr">
         <is>
           <t>Meshy</t>
         </is>
       </c>
-      <c r="B326" s="33" t="inlineStr">
+      <c r="B325" s="33" t="inlineStr">
         <is>
           <t>https://www.meshy.ai</t>
         </is>
       </c>
-      <c r="C326" s="32" t="inlineStr">
+      <c r="C325" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D326" s="33" t="inlineStr">
+      <c r="D325" s="33" t="inlineStr">
         <is>
           <t>Meshy</t>
         </is>
       </c>
-      <c r="E326" s="33" t="inlineStr">
+      <c r="E325" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成、ゲーム開発</t>
         </is>
       </c>
-      <c r="F326" s="32" t="inlineStr">
+      <c r="F325" s="32" t="inlineStr">
         <is>
           <t>文章・画像から3Dモデルを生成
 テクスチャを自動作成
@@ -24011,30 +23944,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G326" s="34" t="inlineStr">
+      <c r="G325" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H326" s="32" t="inlineStr">
+      <c r="H325" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I326" s="35" t="inlineStr">
+      <c r="I325" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J326" s="35" t="n"/>
-      <c r="K326" s="35" t="n"/>
-      <c r="L326" s="35" t="inlineStr">
+      <c r="J325" s="35" t="n"/>
+      <c r="K325" s="35" t="n"/>
+      <c r="L325" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M326" s="32" t="n"/>
-      <c r="N326" s="32" t="inlineStr">
+      <c r="M325" s="32" t="n"/>
+      <c r="N325" s="32" t="inlineStr">
         <is>
           <t>3D models from text or images
 Automatic textures
@@ -24042,35 +23975,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O326" s="32" t="n"/>
-    </row>
-    <row r="327" ht="66" customHeight="1" s="29">
-      <c r="A327" s="30" t="inlineStr">
+      <c r="O325" s="32" t="n"/>
+    </row>
+    <row r="326" ht="66" customHeight="1" s="29">
+      <c r="A326" s="30" t="inlineStr">
         <is>
           <t>Tripo AI</t>
         </is>
       </c>
-      <c r="B327" s="33" t="inlineStr">
+      <c r="B326" s="33" t="inlineStr">
         <is>
           <t>https://www.tripo3d.ai</t>
         </is>
       </c>
-      <c r="C327" s="32" t="inlineStr">
+      <c r="C326" s="32" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="D327" s="33" t="inlineStr">
+      <c r="D326" s="33" t="inlineStr">
         <is>
           <t>VAST</t>
         </is>
       </c>
-      <c r="E327" s="33" t="inlineStr">
+      <c r="E326" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成、ゲーム開発</t>
         </is>
       </c>
-      <c r="F327" s="32" t="inlineStr">
+      <c r="F326" s="32" t="inlineStr">
         <is>
           <t>画像1枚から3Dモデル
 動かすための骨組み（リギング）
@@ -24078,30 +24011,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G327" s="34" t="inlineStr">
+      <c r="G326" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H327" s="32" t="inlineStr">
+      <c r="H326" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I327" s="35" t="inlineStr">
+      <c r="I326" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J327" s="35" t="n"/>
-      <c r="K327" s="35" t="n"/>
-      <c r="L327" s="35" t="inlineStr">
+      <c r="J326" s="35" t="n"/>
+      <c r="K326" s="35" t="n"/>
+      <c r="L326" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M327" s="32" t="n"/>
-      <c r="N327" s="32" t="inlineStr">
+      <c r="M326" s="32" t="n"/>
+      <c r="N326" s="32" t="inlineStr">
         <is>
           <t>3D model from a single image
 Rigging for animation
@@ -24109,35 +24042,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O327" s="32" t="n"/>
-    </row>
-    <row r="328" ht="66" customHeight="1" s="29">
-      <c r="A328" s="30" t="inlineStr">
+      <c r="O326" s="32" t="n"/>
+    </row>
+    <row r="327" ht="66" customHeight="1" s="29">
+      <c r="A327" s="30" t="inlineStr">
         <is>
           <t>Hyper3D Rodin</t>
         </is>
       </c>
-      <c r="B328" s="33" t="inlineStr">
+      <c r="B327" s="33" t="inlineStr">
         <is>
           <t>https://hyper3d.ai</t>
         </is>
       </c>
-      <c r="C328" s="32" t="inlineStr">
+      <c r="C327" s="32" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="D328" s="33" t="inlineStr">
+      <c r="D327" s="33" t="inlineStr">
         <is>
           <t>Deemos</t>
         </is>
       </c>
-      <c r="E328" s="33" t="inlineStr">
+      <c r="E327" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成</t>
         </is>
       </c>
-      <c r="F328" s="32" t="inlineStr">
+      <c r="F327" s="32" t="inlineStr">
         <is>
           <t>精細な3Dモデルを生成
 画像・文章から作成
@@ -24145,30 +24078,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G328" s="34" t="inlineStr">
+      <c r="G327" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H328" s="32" t="inlineStr">
+      <c r="H327" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I328" s="35" t="inlineStr">
+      <c r="I327" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J328" s="35" t="n"/>
-      <c r="K328" s="35" t="n"/>
-      <c r="L328" s="35" t="inlineStr">
+      <c r="J327" s="35" t="n"/>
+      <c r="K327" s="35" t="n"/>
+      <c r="L327" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M328" s="32" t="n"/>
-      <c r="N328" s="32" t="inlineStr">
+      <c r="M327" s="32" t="n"/>
+      <c r="N327" s="32" t="inlineStr">
         <is>
           <t>Detailed 3D model generation
 From images or text
@@ -24176,35 +24109,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O328" s="32" t="n"/>
-    </row>
-    <row r="329" ht="66" customHeight="1" s="29">
-      <c r="A329" s="30" t="inlineStr">
+      <c r="O327" s="32" t="n"/>
+    </row>
+    <row r="328" ht="66" customHeight="1" s="29">
+      <c r="A328" s="30" t="inlineStr">
         <is>
           <t>Hunyuan3D</t>
         </is>
       </c>
-      <c r="B329" s="33" t="inlineStr">
+      <c r="B328" s="33" t="inlineStr">
         <is>
           <t>https://3d.hunyuan.tencent.com</t>
         </is>
       </c>
-      <c r="C329" s="32" t="inlineStr">
+      <c r="C328" s="32" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="D329" s="33" t="inlineStr">
+      <c r="D328" s="33" t="inlineStr">
         <is>
           <t>Tencent</t>
         </is>
       </c>
-      <c r="E329" s="33" t="inlineStr">
+      <c r="E328" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成</t>
         </is>
       </c>
-      <c r="F329" s="33" t="inlineStr">
+      <c r="F328" s="33" t="inlineStr">
         <is>
           <t>Tencentのオープンな3D生成
 画像から3D
@@ -24212,30 +24145,30 @@
 無料</t>
         </is>
       </c>
-      <c r="G329" s="34" t="inlineStr">
+      <c r="G328" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H329" s="32" t="inlineStr">
+      <c r="H328" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I329" s="35" t="inlineStr">
+      <c r="I328" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J329" s="35" t="n"/>
-      <c r="K329" s="35" t="n"/>
-      <c r="L329" s="35" t="inlineStr">
+      <c r="J328" s="35" t="n"/>
+      <c r="K328" s="35" t="n"/>
+      <c r="L328" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M329" s="33" t="n"/>
-      <c r="N329" s="33" t="inlineStr">
+      <c r="M328" s="33" t="n"/>
+      <c r="N328" s="33" t="inlineStr">
         <is>
           <t>Open 3D generation from Tencent
 Image to 3D
@@ -24243,35 +24176,35 @@
 Free</t>
         </is>
       </c>
-      <c r="O329" s="33" t="n"/>
-    </row>
-    <row r="330" ht="66" customHeight="1" s="29">
-      <c r="A330" s="30" t="inlineStr">
+      <c r="O328" s="33" t="n"/>
+    </row>
+    <row r="329" ht="66" customHeight="1" s="29">
+      <c r="A329" s="30" t="inlineStr">
         <is>
           <t>TRELLIS</t>
         </is>
       </c>
-      <c r="B330" s="33" t="inlineStr">
+      <c r="B329" s="33" t="inlineStr">
         <is>
           <t>https://github.com/microsoft/TRELLIS</t>
         </is>
       </c>
-      <c r="C330" s="32" t="inlineStr">
+      <c r="C329" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D330" s="33" t="inlineStr">
+      <c r="D329" s="33" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="E330" s="33" t="inlineStr">
+      <c r="E329" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成、開発者向けツール</t>
         </is>
       </c>
-      <c r="F330" s="33" t="inlineStr">
+      <c r="F329" s="33" t="inlineStr">
         <is>
           <t>Microsoftのオープンな3D生成
 画像から3D
@@ -24279,30 +24212,30 @@
 ローカル実行</t>
         </is>
       </c>
-      <c r="G330" s="34" t="inlineStr">
+      <c r="G329" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H330" s="32" t="inlineStr">
+      <c r="H329" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I330" s="35" t="inlineStr">
+      <c r="I329" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J330" s="35" t="n"/>
-      <c r="K330" s="35" t="n"/>
-      <c r="L330" s="35" t="inlineStr">
+      <c r="J329" s="35" t="n"/>
+      <c r="K329" s="35" t="n"/>
+      <c r="L329" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M330" s="33" t="n"/>
-      <c r="N330" s="33" t="inlineStr">
+      <c r="M329" s="33" t="n"/>
+      <c r="N329" s="33" t="inlineStr">
         <is>
           <t>Open 3D generation from Microsoft
 Image to 3D
@@ -24310,35 +24243,35 @@
 Runs locally</t>
         </is>
       </c>
-      <c r="O330" s="33" t="n"/>
-    </row>
-    <row r="331" ht="66" customHeight="1" s="29">
-      <c r="A331" s="30" t="inlineStr">
+      <c r="O329" s="33" t="n"/>
+    </row>
+    <row r="330" ht="66" customHeight="1" s="29">
+      <c r="A330" s="30" t="inlineStr">
         <is>
           <t>Spline</t>
         </is>
       </c>
-      <c r="B331" s="33" t="inlineStr">
+      <c r="B330" s="33" t="inlineStr">
         <is>
           <t>https://spline.design</t>
         </is>
       </c>
-      <c r="C331" s="32" t="inlineStr">
+      <c r="C330" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D331" s="33" t="inlineStr">
+      <c r="D330" s="33" t="inlineStr">
         <is>
           <t>Spline</t>
         </is>
       </c>
-      <c r="E331" s="33" t="inlineStr">
+      <c r="E330" s="33" t="inlineStr">
         <is>
           <t>3Dモデル生成、デザイン・UI/UX</t>
         </is>
       </c>
-      <c r="F331" s="32" t="inlineStr">
+      <c r="F330" s="32" t="inlineStr">
         <is>
           <t>ブラウザで3Dデザイン
 AIで3Dオブジェクトを生成
@@ -24346,30 +24279,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G331" s="34" t="inlineStr">
+      <c r="G330" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H331" s="32" t="inlineStr">
+      <c r="H330" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I331" s="35" t="inlineStr">
+      <c r="I330" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J331" s="35" t="n"/>
-      <c r="K331" s="35" t="n"/>
-      <c r="L331" s="35" t="inlineStr">
+      <c r="J330" s="35" t="n"/>
+      <c r="K330" s="35" t="n"/>
+      <c r="L330" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M331" s="32" t="n"/>
-      <c r="N331" s="32" t="inlineStr">
+      <c r="M330" s="32" t="n"/>
+      <c r="N330" s="32" t="inlineStr">
         <is>
           <t>3D design in the browser
 Generate 3D objects with AI
@@ -24377,35 +24310,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O331" s="32" t="n"/>
-    </row>
-    <row r="332" ht="66" customHeight="1" s="29">
-      <c r="A332" s="30" t="inlineStr">
+      <c r="O330" s="32" t="n"/>
+    </row>
+    <row r="331" ht="66" customHeight="1" s="29">
+      <c r="A331" s="30" t="inlineStr">
         <is>
           <t>Rosebud AI</t>
         </is>
       </c>
-      <c r="B332" s="33" t="inlineStr">
+      <c r="B331" s="33" t="inlineStr">
         <is>
           <t>https://rosebud.ai</t>
         </is>
       </c>
-      <c r="C332" s="32" t="inlineStr">
+      <c r="C331" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D332" s="33" t="inlineStr">
+      <c r="D331" s="33" t="inlineStr">
         <is>
           <t>Rosebud AI</t>
         </is>
       </c>
-      <c r="E332" s="32" t="inlineStr">
+      <c r="E331" s="32" t="inlineStr">
         <is>
           <t>ゲーム開発、ノーコードでアプリ作成</t>
         </is>
       </c>
-      <c r="F332" s="32" t="inlineStr">
+      <c r="F331" s="32" t="inlineStr">
         <is>
           <t>会話でブラウザゲームを作成
 作ったゲームを公開
@@ -24413,30 +24346,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G332" s="34" t="inlineStr">
+      <c r="G331" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H332" s="32" t="inlineStr">
+      <c r="H331" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I332" s="35" t="inlineStr">
+      <c r="I331" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J332" s="35" t="n"/>
-      <c r="K332" s="35" t="n"/>
-      <c r="L332" s="35" t="inlineStr">
+      <c r="J331" s="35" t="n"/>
+      <c r="K331" s="35" t="n"/>
+      <c r="L331" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M332" s="32" t="n"/>
-      <c r="N332" s="32" t="inlineStr">
+      <c r="M331" s="32" t="n"/>
+      <c r="N331" s="32" t="inlineStr">
         <is>
           <t>Build browser games by chatting
 Publish your games
@@ -24444,35 +24377,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O332" s="32" t="n"/>
-    </row>
-    <row r="333" ht="66" customHeight="1" s="29">
-      <c r="A333" s="30" t="inlineStr">
+      <c r="O331" s="32" t="n"/>
+    </row>
+    <row r="332" ht="66" customHeight="1" s="29">
+      <c r="A332" s="30" t="inlineStr">
         <is>
           <t>Unity AI</t>
         </is>
       </c>
-      <c r="B333" s="33" t="inlineStr">
+      <c r="B332" s="33" t="inlineStr">
         <is>
           <t>https://unity.com/features/ai</t>
         </is>
       </c>
-      <c r="C333" s="32" t="inlineStr">
+      <c r="C332" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D333" s="33" t="inlineStr">
+      <c r="D332" s="33" t="inlineStr">
         <is>
           <t>Unity</t>
         </is>
       </c>
-      <c r="E333" s="32" t="inlineStr">
+      <c r="E332" s="32" t="inlineStr">
         <is>
           <t>ゲーム開発、コード補完</t>
         </is>
       </c>
-      <c r="F333" s="33" t="inlineStr">
+      <c r="F332" s="33" t="inlineStr">
         <is>
           <t>Unityエディタ内のAIアシスタント
 C#スクリプトの作成・修正
@@ -24480,30 +24413,30 @@
 プランにより利用範囲が異なる</t>
         </is>
       </c>
-      <c r="G333" s="34" t="inlineStr">
+      <c r="G332" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H333" s="33" t="inlineStr">
+      <c r="H332" s="33" t="inlineStr">
         <is>
           <t>Unityのプランにより利用範囲が異なる</t>
         </is>
       </c>
-      <c r="I333" s="35" t="inlineStr">
+      <c r="I332" s="35" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="J333" s="35" t="n"/>
-      <c r="K333" s="35" t="n"/>
-      <c r="L333" s="35" t="inlineStr">
+      <c r="J332" s="35" t="n"/>
+      <c r="K332" s="35" t="n"/>
+      <c r="L332" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M333" s="33" t="n"/>
-      <c r="N333" s="33" t="inlineStr">
+      <c r="M332" s="33" t="n"/>
+      <c r="N332" s="33" t="inlineStr">
         <is>
           <t>AI assistant inside the Unity Editor
 Writes and fixes C# scripts
@@ -24511,39 +24444,39 @@
 Depends on your Unity plan</t>
         </is>
       </c>
-      <c r="O333" s="33" t="inlineStr">
+      <c r="O332" s="33" t="inlineStr">
         <is>
           <t>Depends on your Unity plan</t>
         </is>
       </c>
     </row>
-    <row r="334" ht="66" customHeight="1" s="29">
-      <c r="A334" s="30" t="inlineStr">
+    <row r="333" ht="66" customHeight="1" s="29">
+      <c r="A333" s="30" t="inlineStr">
         <is>
           <t>Inworld AI</t>
         </is>
       </c>
-      <c r="B334" s="33" t="inlineStr">
+      <c r="B333" s="33" t="inlineStr">
         <is>
           <t>https://inworld.ai</t>
         </is>
       </c>
-      <c r="C334" s="32" t="inlineStr">
+      <c r="C333" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D334" s="33" t="inlineStr">
+      <c r="D333" s="33" t="inlineStr">
         <is>
           <t>Inworld AI</t>
         </is>
       </c>
-      <c r="E334" s="32" t="inlineStr">
+      <c r="E333" s="32" t="inlineStr">
         <is>
           <t>ゲーム開発、開発者向けツール</t>
         </is>
       </c>
-      <c r="F334" s="32" t="inlineStr">
+      <c r="F333" s="32" t="inlineStr">
         <is>
           <t>ゲームキャラクターと自然に会話
 キャラの性格・記憶を設定
@@ -24551,30 +24484,30 @@
 Unity・Unreal対応</t>
         </is>
       </c>
-      <c r="G334" s="34" t="inlineStr">
+      <c r="G333" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H334" s="32" t="inlineStr">
+      <c r="H333" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I334" s="35" t="inlineStr">
+      <c r="I333" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J334" s="35" t="n"/>
-      <c r="K334" s="35" t="n"/>
-      <c r="L334" s="35" t="inlineStr">
+      <c r="J333" s="35" t="n"/>
+      <c r="K333" s="35" t="n"/>
+      <c r="L333" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M334" s="32" t="n"/>
-      <c r="N334" s="32" t="inlineStr">
+      <c r="M333" s="32" t="n"/>
+      <c r="N333" s="32" t="inlineStr">
         <is>
           <t>Natural conversations with game characters
 Set personality and memory
@@ -24582,35 +24515,35 @@
 Unity and Unreal support</t>
         </is>
       </c>
-      <c r="O334" s="32" t="n"/>
-    </row>
-    <row r="335" ht="66" customHeight="1" s="29">
-      <c r="A335" s="30" t="inlineStr">
+      <c r="O333" s="32" t="n"/>
+    </row>
+    <row r="334" ht="66" customHeight="1" s="29">
+      <c r="A334" s="30" t="inlineStr">
         <is>
           <t>Gemini in Android Studio</t>
         </is>
       </c>
-      <c r="B335" s="33" t="inlineStr">
+      <c r="B334" s="33" t="inlineStr">
         <is>
           <t>https://developer.android.com/studio/gemini/overview</t>
         </is>
       </c>
-      <c r="C335" s="32" t="inlineStr">
+      <c r="C334" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D335" s="33" t="inlineStr">
+      <c r="D334" s="33" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E335" s="33" t="inlineStr">
+      <c r="E334" s="33" t="inlineStr">
         <is>
           <t>Android開発、コード補完</t>
         </is>
       </c>
-      <c r="F335" s="33" t="inlineStr">
+      <c r="F334" s="33" t="inlineStr">
         <is>
           <t>Android Studioに組み込まれたAI
 Kotlinコードの生成・説明
@@ -24618,30 +24551,30 @@
 個人は無料</t>
         </is>
       </c>
-      <c r="G335" s="34" t="inlineStr">
+      <c r="G334" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H335" s="32" t="inlineStr">
+      <c r="H334" s="32" t="inlineStr">
         <is>
           <t>個人利用は無料</t>
         </is>
       </c>
-      <c r="I335" s="35" t="inlineStr">
+      <c r="I334" s="35" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="J335" s="35" t="n"/>
-      <c r="K335" s="35" t="n"/>
-      <c r="L335" s="35" t="inlineStr">
+      <c r="J334" s="35" t="n"/>
+      <c r="K334" s="35" t="n"/>
+      <c r="L334" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M335" s="33" t="n"/>
-      <c r="N335" s="33" t="inlineStr">
+      <c r="M334" s="33" t="n"/>
+      <c r="N334" s="33" t="inlineStr">
         <is>
           <t>AI built into Android Studio
 Generates and explains Kotlin code
@@ -24649,39 +24582,39 @@
 Free for individuals</t>
         </is>
       </c>
-      <c r="O335" s="33" t="inlineStr">
+      <c r="O334" s="33" t="inlineStr">
         <is>
           <t>Free for individuals</t>
         </is>
       </c>
     </row>
-    <row r="336" ht="66" customHeight="1" s="29">
-      <c r="A336" s="30" t="inlineStr">
+    <row r="335" ht="66" customHeight="1" s="29">
+      <c r="A335" s="30" t="inlineStr">
         <is>
           <t>FlutterFlow</t>
         </is>
       </c>
-      <c r="B336" s="33" t="inlineStr">
+      <c r="B335" s="33" t="inlineStr">
         <is>
           <t>https://www.flutterflow.io</t>
         </is>
       </c>
-      <c r="C336" s="32" t="inlineStr">
+      <c r="C335" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D336" s="33" t="inlineStr">
+      <c r="D335" s="33" t="inlineStr">
         <is>
           <t>FlutterFlow</t>
         </is>
       </c>
-      <c r="E336" s="33" t="inlineStr">
+      <c r="E335" s="33" t="inlineStr">
         <is>
           <t>Android開発、ノーコードでアプリ作成</t>
         </is>
       </c>
-      <c r="F336" s="32" t="inlineStr">
+      <c r="F335" s="32" t="inlineStr">
         <is>
           <t>ノーコードでスマホアプリ
 AIで画面を生成
@@ -24689,30 +24622,30 @@
 Firebase連携</t>
         </is>
       </c>
-      <c r="G336" s="34" t="inlineStr">
+      <c r="G335" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H336" s="32" t="inlineStr">
+      <c r="H335" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I336" s="35" t="inlineStr">
+      <c r="I335" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J336" s="35" t="n"/>
-      <c r="K336" s="35" t="n"/>
-      <c r="L336" s="35" t="inlineStr">
+      <c r="J335" s="35" t="n"/>
+      <c r="K335" s="35" t="n"/>
+      <c r="L335" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M336" s="32" t="n"/>
-      <c r="N336" s="32" t="inlineStr">
+      <c r="M335" s="32" t="n"/>
+      <c r="N335" s="32" t="inlineStr">
         <is>
           <t>Build mobile apps without code
 Generate screens with AI
@@ -24720,35 +24653,35 @@
 Firebase integration</t>
         </is>
       </c>
-      <c r="O336" s="32" t="n"/>
-    </row>
-    <row r="337" ht="66" customHeight="1" s="29">
-      <c r="A337" s="26" t="inlineStr">
+      <c r="O335" s="32" t="n"/>
+    </row>
+    <row r="336" ht="66" customHeight="1" s="29">
+      <c r="A336" s="26" t="inlineStr">
         <is>
           <t>Better Analyst（旧Formula Bot）</t>
         </is>
       </c>
-      <c r="B337" s="31" t="inlineStr">
+      <c r="B336" s="31" t="inlineStr">
         <is>
           <t>https://betteranalyst.com</t>
         </is>
       </c>
-      <c r="C337" s="32" t="inlineStr">
+      <c r="C336" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D337" s="33" t="inlineStr">
+      <c r="D336" s="33" t="inlineStr">
         <is>
           <t>Better Analyst</t>
         </is>
       </c>
-      <c r="E337" s="33" t="inlineStr">
+      <c r="E336" s="33" t="inlineStr">
         <is>
           <t>Excel・事務作業、データ分析・予測</t>
         </is>
       </c>
-      <c r="F337" s="32" t="inlineStr">
+      <c r="F336" s="32" t="inlineStr">
         <is>
           <t>会話でデータを分析してグラフを作成
 Excel・スプレッドシートの関数を生成
@@ -24756,34 +24689,34 @@
 ダッシュボード・定期レポートを自動化</t>
         </is>
       </c>
-      <c r="G337" s="34" t="inlineStr">
+      <c r="G336" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H337" s="32" t="inlineStr">
+      <c r="H336" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I337" s="35" t="inlineStr">
+      <c r="I336" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J337" s="35" t="n"/>
-      <c r="K337" s="35" t="n"/>
-      <c r="L337" s="35" t="inlineStr">
+      <c r="J336" s="35" t="n"/>
+      <c r="K336" s="35" t="n"/>
+      <c r="L336" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M337" s="32" t="inlineStr">
+      <c r="M336" s="32" t="inlineStr">
         <is>
           <t>Better Analyst (formerly Formula Bot)</t>
         </is>
       </c>
-      <c r="N337" s="32" t="inlineStr">
+      <c r="N336" s="32" t="inlineStr">
         <is>
           <t>Analyze data by chatting and make charts
 Generates Excel and spreadsheet formulas
@@ -24791,35 +24724,35 @@
 Automates dashboards and reports</t>
         </is>
       </c>
-      <c r="O337" s="32" t="n"/>
-    </row>
-    <row r="338" ht="66" customHeight="1" s="29">
-      <c r="A338" s="30" t="inlineStr">
+      <c r="O336" s="32" t="n"/>
+    </row>
+    <row r="337" ht="66" customHeight="1" s="29">
+      <c r="A337" s="30" t="inlineStr">
         <is>
           <t>Numerous.ai</t>
         </is>
       </c>
-      <c r="B338" s="33" t="inlineStr">
+      <c r="B337" s="33" t="inlineStr">
         <is>
           <t>https://numerous.ai</t>
         </is>
       </c>
-      <c r="C338" s="32" t="inlineStr">
+      <c r="C337" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D338" s="33" t="inlineStr">
+      <c r="D337" s="33" t="inlineStr">
         <is>
           <t>Numerous.ai</t>
         </is>
       </c>
-      <c r="E338" s="33" t="inlineStr">
+      <c r="E337" s="33" t="inlineStr">
         <is>
           <t>Excel・事務作業</t>
         </is>
       </c>
-      <c r="F338" s="32" t="inlineStr">
+      <c r="F337" s="32" t="inlineStr">
         <is>
           <t>スプレッドシートでAI関数を使える
 大量データの分類・要約
@@ -24827,30 +24760,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G338" s="34" t="inlineStr">
+      <c r="G337" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H338" s="32" t="inlineStr">
+      <c r="H337" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I338" s="35" t="inlineStr">
+      <c r="I337" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J338" s="35" t="n"/>
-      <c r="K338" s="35" t="n"/>
-      <c r="L338" s="35" t="inlineStr">
+      <c r="J337" s="35" t="n"/>
+      <c r="K337" s="35" t="n"/>
+      <c r="L337" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M338" s="32" t="n"/>
-      <c r="N338" s="32" t="inlineStr">
+      <c r="M337" s="32" t="n"/>
+      <c r="N337" s="32" t="inlineStr">
         <is>
           <t>Use AI functions in spreadsheets
 Classify and summarize lots of data
@@ -24858,35 +24791,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O338" s="32" t="n"/>
-    </row>
-    <row r="339" ht="66" customHeight="1" s="29">
-      <c r="A339" s="30" t="inlineStr">
+      <c r="O337" s="32" t="n"/>
+    </row>
+    <row r="338" ht="66" customHeight="1" s="29">
+      <c r="A338" s="30" t="inlineStr">
         <is>
           <t>Sheet+</t>
         </is>
       </c>
-      <c r="B339" s="33" t="inlineStr">
+      <c r="B338" s="33" t="inlineStr">
         <is>
           <t>https://sheetplus.ai</t>
         </is>
       </c>
-      <c r="C339" s="32" t="inlineStr">
+      <c r="C338" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D339" s="33" t="inlineStr">
+      <c r="D338" s="33" t="inlineStr">
         <is>
           <t>Sheet+</t>
         </is>
       </c>
-      <c r="E339" s="33" t="inlineStr">
+      <c r="E338" s="33" t="inlineStr">
         <is>
           <t>Excel・事務作業</t>
         </is>
       </c>
-      <c r="F339" s="33" t="inlineStr">
+      <c r="F338" s="33" t="inlineStr">
         <is>
           <t>Excel・スプレッドシートの関数を生成
 関数の説明・修正
@@ -24894,30 +24827,30 @@
 無料枠</t>
         </is>
       </c>
-      <c r="G339" s="34" t="inlineStr">
+      <c r="G338" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H339" s="32" t="inlineStr">
+      <c r="H338" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I339" s="35" t="inlineStr">
+      <c r="I338" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J339" s="35" t="n"/>
-      <c r="K339" s="35" t="n"/>
-      <c r="L339" s="35" t="inlineStr">
+      <c r="J338" s="35" t="n"/>
+      <c r="K338" s="35" t="n"/>
+      <c r="L338" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M339" s="33" t="n"/>
-      <c r="N339" s="33" t="inlineStr">
+      <c r="M338" s="33" t="n"/>
+      <c r="N338" s="33" t="inlineStr">
         <is>
           <t>Generates Excel and spreadsheet formulas
 Explains and fixes formulas
@@ -24925,35 +24858,35 @@
 Free tier</t>
         </is>
       </c>
-      <c r="O339" s="33" t="n"/>
-    </row>
-    <row r="340" ht="66" customHeight="1" s="29">
-      <c r="A340" s="30" t="inlineStr">
+      <c r="O338" s="33" t="n"/>
+    </row>
+    <row r="339" ht="66" customHeight="1" s="29">
+      <c r="A339" s="30" t="inlineStr">
         <is>
           <t>Arena（旧LMArena）</t>
         </is>
       </c>
-      <c r="B340" s="33" t="inlineStr">
+      <c r="B339" s="33" t="inlineStr">
         <is>
           <t>https://arena.ai</t>
         </is>
       </c>
-      <c r="C340" s="32" t="inlineStr">
+      <c r="C339" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D340" s="33" t="inlineStr">
+      <c r="D339" s="33" t="inlineStr">
         <is>
           <t>Arena</t>
         </is>
       </c>
-      <c r="E340" s="33" t="inlineStr">
+      <c r="E339" s="33" t="inlineStr">
         <is>
           <t>情報検索・リサーチ、パーソナルアシスタント、開発者向けツール</t>
         </is>
       </c>
-      <c r="F340" s="33" t="inlineStr">
+      <c r="F339" s="33" t="inlineStr">
         <is>
           <t>複数のAIの答えを並べて比較
 最新AIを無料で試せる
@@ -24961,34 +24894,34 @@
 画像・コードのAIも比較</t>
         </is>
       </c>
-      <c r="G340" s="34" t="inlineStr">
+      <c r="G339" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H340" s="32" t="inlineStr">
+      <c r="H339" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I340" s="35" t="inlineStr">
+      <c r="I339" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J340" s="35" t="inlineStr">
+      <c r="J339" s="35" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="K340" s="35" t="n"/>
-      <c r="L340" s="35" t="inlineStr">
+      <c r="K339" s="35" t="n"/>
+      <c r="L339" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M340" s="33" t="n"/>
-      <c r="N340" s="33" t="inlineStr">
+      <c r="M339" s="33" t="n"/>
+      <c r="N339" s="33" t="inlineStr">
         <is>
           <t>Compare answers from AIs side by side
 Try the latest models for free
@@ -24996,39 +24929,39 @@
 Also compares image and code AIs</t>
         </is>
       </c>
-      <c r="O340" s="33" t="inlineStr">
+      <c r="O339" s="33" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
     </row>
-    <row r="341" ht="66" customHeight="1" s="29">
-      <c r="A341" s="30" t="inlineStr">
+    <row r="340" ht="66" customHeight="1" s="29">
+      <c r="A340" s="30" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="B341" s="33" t="inlineStr">
+      <c r="B340" s="33" t="inlineStr">
         <is>
           <t>https://www.perplexity.ai/comet</t>
         </is>
       </c>
-      <c r="C341" s="32" t="inlineStr">
+      <c r="C340" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D341" s="33" t="inlineStr">
+      <c r="D340" s="33" t="inlineStr">
         <is>
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="E341" s="33" t="inlineStr">
+      <c r="E340" s="33" t="inlineStr">
         <is>
           <t>情報検索・リサーチ、パーソナルアシスタント、タスクの自動化（RPA連携）</t>
         </is>
       </c>
-      <c r="F341" s="33" t="inlineStr">
+      <c r="F340" s="33" t="inlineStr">
         <is>
           <t>AIが組み込まれたWebブラウザ
 閲覧中のページを要約・質問
@@ -25036,30 +24969,30 @@
 スマホ版もあり</t>
         </is>
       </c>
-      <c r="G341" s="34" t="inlineStr">
+      <c r="G340" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H341" s="32" t="inlineStr">
+      <c r="H340" s="32" t="inlineStr">
         <is>
           <t>ブラウザは無料（高度な機能は有料プラン）</t>
         </is>
       </c>
-      <c r="I341" s="35" t="inlineStr">
+      <c r="I340" s="35" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="J341" s="35" t="n"/>
-      <c r="K341" s="35" t="n"/>
-      <c r="L341" s="35" t="inlineStr">
+      <c r="J340" s="35" t="n"/>
+      <c r="K340" s="35" t="n"/>
+      <c r="L340" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M341" s="33" t="n"/>
-      <c r="N341" s="33" t="inlineStr">
+      <c r="M340" s="33" t="n"/>
+      <c r="N340" s="33" t="inlineStr">
         <is>
           <t>Web browser with built-in AI
 Summarize and ask about any page
@@ -25067,39 +25000,39 @@
 Mobile apps available</t>
         </is>
       </c>
-      <c r="O341" s="33" t="inlineStr">
+      <c r="O340" s="33" t="inlineStr">
         <is>
           <t>Browser is free (advanced features on paid plans)</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="66" customHeight="1" s="29">
-      <c r="A342" s="30" t="inlineStr">
+    <row r="341" ht="66" customHeight="1" s="29">
+      <c r="A341" s="30" t="inlineStr">
         <is>
           <t>TurboScribe</t>
         </is>
       </c>
-      <c r="B342" s="33" t="inlineStr">
+      <c r="B341" s="33" t="inlineStr">
         <is>
           <t>https://turboscribe.ai</t>
         </is>
       </c>
-      <c r="C342" s="32" t="inlineStr">
+      <c r="C341" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D342" s="33" t="inlineStr">
+      <c r="D341" s="33" t="inlineStr">
         <is>
           <t>TurboScribe</t>
         </is>
       </c>
-      <c r="E342" s="33" t="inlineStr">
+      <c r="E341" s="33" t="inlineStr">
         <is>
           <t>音声認識、要約と構造化、言語・翻訳</t>
         </is>
       </c>
-      <c r="F342" s="33" t="inlineStr">
+      <c r="F341" s="33" t="inlineStr">
         <is>
           <t>音声・動画を高精度で文字起こし
 日本語を含む98言語以上
@@ -25107,30 +25040,30 @@
 字幕（SRT）・Wordで出力</t>
         </is>
       </c>
-      <c r="G342" s="34" t="inlineStr">
+      <c r="G341" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H342" s="32" t="inlineStr">
+      <c r="H341" s="32" t="inlineStr">
         <is>
           <t>1日3ファイルまで（1ファイル30分以内）</t>
         </is>
       </c>
-      <c r="I342" s="35" t="inlineStr">
+      <c r="I341" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J342" s="35" t="n"/>
-      <c r="K342" s="35" t="n"/>
-      <c r="L342" s="35" t="inlineStr">
+      <c r="J341" s="35" t="n"/>
+      <c r="K341" s="35" t="n"/>
+      <c r="L341" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M342" s="33" t="n"/>
-      <c r="N342" s="33" t="inlineStr">
+      <c r="M341" s="33" t="n"/>
+      <c r="N341" s="33" t="inlineStr">
         <is>
           <t>Accurate transcription of audio and video
 98+ languages including Japanese
@@ -25138,39 +25071,39 @@
 Export as subtitles (SRT) or Word</t>
         </is>
       </c>
-      <c r="O342" s="33" t="inlineStr">
+      <c r="O341" s="33" t="inlineStr">
         <is>
           <t>3 files per day (up to 30 min each)</t>
         </is>
       </c>
     </row>
-    <row r="343" ht="66" customHeight="1" s="29">
-      <c r="A343" s="30" t="inlineStr">
+    <row r="342" ht="66" customHeight="1" s="29">
+      <c r="A342" s="30" t="inlineStr">
         <is>
           <t>Z.ai（GLM）</t>
         </is>
       </c>
-      <c r="B343" s="33" t="inlineStr">
+      <c r="B342" s="33" t="inlineStr">
         <is>
           <t>https://chat.z.ai</t>
         </is>
       </c>
-      <c r="C343" s="32" t="inlineStr">
+      <c r="C342" s="32" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="D343" s="33" t="inlineStr">
+      <c r="D342" s="33" t="inlineStr">
         <is>
           <t>Zhipu AI</t>
         </is>
       </c>
-      <c r="E343" s="33" t="inlineStr">
+      <c r="E342" s="33" t="inlineStr">
         <is>
           <t>パーソナルアシスタント、開発者向けツール、テキスト生成・AI執筆</t>
         </is>
       </c>
-      <c r="F343" s="33" t="inlineStr">
+      <c r="F342" s="33" t="inlineStr">
         <is>
           <t>最新のGLMモデルと会話
 Webサイト・コードを作成
@@ -25178,30 +25111,30 @@
 智谱清言の海外版</t>
         </is>
       </c>
-      <c r="G343" s="34" t="inlineStr">
+      <c r="G342" s="34" t="inlineStr">
         <is>
           <t>完全無料</t>
         </is>
       </c>
-      <c r="H343" s="32" t="inlineStr">
+      <c r="H342" s="32" t="inlineStr">
         <is>
           <t>無料で利用可能</t>
         </is>
       </c>
-      <c r="I343" s="35" t="inlineStr">
+      <c r="I342" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J343" s="35" t="n"/>
-      <c r="K343" s="35" t="n"/>
-      <c r="L343" s="35" t="inlineStr">
+      <c r="J342" s="35" t="n"/>
+      <c r="K342" s="35" t="n"/>
+      <c r="L342" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M343" s="33" t="n"/>
-      <c r="N343" s="33" t="inlineStr">
+      <c r="M342" s="33" t="n"/>
+      <c r="N342" s="33" t="inlineStr">
         <is>
           <t>Chat with the latest GLM models
 Builds websites and code
@@ -25209,39 +25142,39 @@
 International version of ChatGLM</t>
         </is>
       </c>
-      <c r="O343" s="33" t="inlineStr">
+      <c r="O342" s="33" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
     </row>
-    <row r="344" ht="66" customHeight="1" s="29">
-      <c r="A344" s="30" t="inlineStr">
+    <row r="343" ht="66" customHeight="1" s="29">
+      <c r="A343" s="30" t="inlineStr">
         <is>
           <t>Zed</t>
         </is>
       </c>
-      <c r="B344" s="33" t="inlineStr">
+      <c r="B343" s="33" t="inlineStr">
         <is>
           <t>https://zed.dev</t>
         </is>
       </c>
-      <c r="C344" s="32" t="inlineStr">
+      <c r="C343" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D344" s="33" t="inlineStr">
+      <c r="D343" s="33" t="inlineStr">
         <is>
           <t>Zed Industries</t>
         </is>
       </c>
-      <c r="E344" s="33" t="inlineStr">
+      <c r="E343" s="33" t="inlineStr">
         <is>
           <t>コード補完、開発者向けツール</t>
         </is>
       </c>
-      <c r="F344" s="33" t="inlineStr">
+      <c r="F343" s="33" t="inlineStr">
         <is>
           <t>とても軽くて速いコードエディタ
 AIが次の編集を予測
@@ -25249,30 +25182,30 @@
 Windows・Mac・Linux対応</t>
         </is>
       </c>
-      <c r="G344" s="34" t="inlineStr">
+      <c r="G343" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H344" s="32" t="inlineStr">
+      <c r="H343" s="32" t="inlineStr">
         <is>
           <t>エディタは無料（AI編集予測は月2,000回まで）</t>
         </is>
       </c>
-      <c r="I344" s="35" t="inlineStr">
+      <c r="I343" s="35" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J344" s="35" t="n"/>
-      <c r="K344" s="35" t="n"/>
-      <c r="L344" s="35" t="inlineStr">
+      <c r="J343" s="35" t="n"/>
+      <c r="K343" s="35" t="n"/>
+      <c r="L343" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M344" s="33" t="n"/>
-      <c r="N344" s="33" t="inlineStr">
+      <c r="M343" s="33" t="n"/>
+      <c r="N343" s="33" t="inlineStr">
         <is>
           <t>Very fast, lightweight code editor
 AI predicts your next edit
@@ -25280,39 +25213,39 @@
 Windows, Mac and Linux</t>
         </is>
       </c>
-      <c r="O344" s="33" t="inlineStr">
+      <c r="O343" s="33" t="inlineStr">
         <is>
           <t>Editor is free (2,000 AI edit predictions/month)</t>
         </is>
       </c>
     </row>
-    <row r="345" ht="66" customHeight="1" s="29">
-      <c r="A345" s="30" t="inlineStr">
+    <row r="344" ht="66" customHeight="1" s="29">
+      <c r="A344" s="30" t="inlineStr">
         <is>
           <t>Gizmo</t>
         </is>
       </c>
-      <c r="B345" s="33" t="inlineStr">
+      <c r="B344" s="33" t="inlineStr">
         <is>
           <t>https://gizmo.ai</t>
         </is>
       </c>
-      <c r="C345" s="32" t="inlineStr">
+      <c r="C344" s="32" t="inlineStr">
         <is>
           <t>イギリス</t>
         </is>
       </c>
-      <c r="D345" s="33" t="inlineStr">
+      <c r="D344" s="33" t="inlineStr">
         <is>
           <t>Gizmo</t>
         </is>
       </c>
-      <c r="E345" s="33" t="inlineStr">
+      <c r="E344" s="33" t="inlineStr">
         <is>
           <t>学習・教育、要約と構造化</t>
         </is>
       </c>
-      <c r="F345" s="33" t="inlineStr">
+      <c r="F344" s="33" t="inlineStr">
         <is>
           <t>PDF・動画から暗記カードを自動作成
 クイズ形式で楽しく復習
@@ -25320,30 +25253,30 @@
 スマホアプリあり</t>
         </is>
       </c>
-      <c r="G345" s="34" t="inlineStr">
+      <c r="G344" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H345" s="32" t="inlineStr">
+      <c r="H344" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（回数・機能に制限）</t>
         </is>
       </c>
-      <c r="I345" s="35" t="inlineStr">
+      <c r="I344" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J345" s="35" t="n"/>
-      <c r="K345" s="35" t="n"/>
-      <c r="L345" s="35" t="inlineStr">
+      <c r="J344" s="35" t="n"/>
+      <c r="K344" s="35" t="n"/>
+      <c r="L344" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M345" s="33" t="n"/>
-      <c r="N345" s="33" t="inlineStr">
+      <c r="M344" s="33" t="n"/>
+      <c r="N344" s="33" t="inlineStr">
         <is>
           <t>Turns PDFs and videos into flashcards
 Fun quiz-style review
@@ -25351,35 +25284,35 @@
 Mobile app available</t>
         </is>
       </c>
-      <c r="O345" s="33" t="n"/>
-    </row>
-    <row r="346" ht="66" customHeight="1" s="29">
-      <c r="A346" s="30" t="inlineStr">
+      <c r="O344" s="33" t="n"/>
+    </row>
+    <row r="345" ht="66" customHeight="1" s="29">
+      <c r="A345" s="30" t="inlineStr">
         <is>
           <t>Granola</t>
         </is>
       </c>
-      <c r="B346" s="33" t="inlineStr">
+      <c r="B345" s="33" t="inlineStr">
         <is>
           <t>https://www.granola.ai</t>
         </is>
       </c>
-      <c r="C346" s="32" t="inlineStr">
+      <c r="C345" s="32" t="inlineStr">
         <is>
           <t>イギリス</t>
         </is>
       </c>
-      <c r="D346" s="33" t="inlineStr">
+      <c r="D345" s="33" t="inlineStr">
         <is>
           <t>Granola</t>
         </is>
       </c>
-      <c r="E346" s="33" t="inlineStr">
+      <c r="E345" s="33" t="inlineStr">
         <is>
           <t>音声認識、要約と構造化、Excel・事務作業</t>
         </is>
       </c>
-      <c r="F346" s="33" t="inlineStr">
+      <c r="F345" s="33" t="inlineStr">
         <is>
           <t>会議にボットを入れずに記録
 自分のメモとAI要約を合体
@@ -25387,30 +25320,30 @@
 PC・スマホに対応</t>
         </is>
       </c>
-      <c r="G346" s="34" t="inlineStr">
+      <c r="G345" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H346" s="32" t="inlineStr">
+      <c r="H345" s="32" t="inlineStr">
         <is>
           <t>無料プランあり（メモの閲覧は30日分まで）</t>
         </is>
       </c>
-      <c r="I346" s="35" t="inlineStr">
+      <c r="I345" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J346" s="35" t="n"/>
-      <c r="K346" s="35" t="n"/>
-      <c r="L346" s="35" t="inlineStr">
+      <c r="J345" s="35" t="n"/>
+      <c r="K345" s="35" t="n"/>
+      <c r="L345" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M346" s="33" t="n"/>
-      <c r="N346" s="33" t="inlineStr">
+      <c r="M345" s="33" t="n"/>
+      <c r="N345" s="33" t="inlineStr">
         <is>
           <t>Records meetings without a bot joining
 Merges your notes with an AI summary
@@ -25418,39 +25351,39 @@
 Desktop and mobile</t>
         </is>
       </c>
-      <c r="O346" s="33" t="inlineStr">
+      <c r="O345" s="33" t="inlineStr">
         <is>
           <t>Free plan (notes history limited to 30 days)</t>
         </is>
       </c>
     </row>
-    <row r="347" ht="66" customHeight="1" s="29">
-      <c r="A347" s="30" t="inlineStr">
+    <row r="346" ht="66" customHeight="1" s="29">
+      <c r="A346" s="30" t="inlineStr">
         <is>
           <t>LTX Studio</t>
         </is>
       </c>
-      <c r="B347" s="33" t="inlineStr">
+      <c r="B346" s="33" t="inlineStr">
         <is>
           <t>https://ltx.io/studio</t>
         </is>
       </c>
-      <c r="C347" s="32" t="inlineStr">
+      <c r="C346" s="32" t="inlineStr">
         <is>
           <t>イスラエル</t>
         </is>
       </c>
-      <c r="D347" s="33" t="inlineStr">
+      <c r="D346" s="33" t="inlineStr">
         <is>
           <t>Lightricks</t>
         </is>
       </c>
-      <c r="E347" s="33" t="inlineStr">
+      <c r="E346" s="33" t="inlineStr">
         <is>
           <t>動画作成、画像作成</t>
         </is>
       </c>
-      <c r="F347" s="33" t="inlineStr">
+      <c r="F346" s="33" t="inlineStr">
         <is>
           <t>台本から絵コンテ・動画を作成
 登場人物の見た目をそろえられる
@@ -25458,30 +25391,30 @@
 カメラの動きも指定</t>
         </is>
       </c>
-      <c r="G347" s="34" t="inlineStr">
+      <c r="G346" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H347" s="32" t="inlineStr">
+      <c r="H346" s="32" t="inlineStr">
         <is>
           <t>登録時に800クレジット（1回のみ・個人利用）</t>
         </is>
       </c>
-      <c r="I347" s="35" t="inlineStr">
+      <c r="I346" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J347" s="35" t="n"/>
-      <c r="K347" s="35" t="n"/>
-      <c r="L347" s="35" t="inlineStr">
+      <c r="J346" s="35" t="n"/>
+      <c r="K346" s="35" t="n"/>
+      <c r="L346" s="35" t="inlineStr">
         <is>
           <t>PCのみ</t>
         </is>
       </c>
-      <c r="M347" s="33" t="n"/>
-      <c r="N347" s="33" t="inlineStr">
+      <c r="M346" s="33" t="n"/>
+      <c r="N346" s="33" t="inlineStr">
         <is>
           <t>Storyboards and videos from a script
 Keeps characters consistent
@@ -25489,39 +25422,39 @@
 Control camera movement</t>
         </is>
       </c>
-      <c r="O347" s="33" t="inlineStr">
+      <c r="O346" s="33" t="inlineStr">
         <is>
           <t>800 credits on signup (one-time, personal use)</t>
         </is>
       </c>
     </row>
-    <row r="348" ht="66" customHeight="1" s="29">
-      <c r="A348" s="30" t="inlineStr">
+    <row r="347" ht="66" customHeight="1" s="29">
+      <c r="A347" s="30" t="inlineStr">
         <is>
           <t>Doctronic</t>
         </is>
       </c>
-      <c r="B348" s="33" t="inlineStr">
+      <c r="B347" s="33" t="inlineStr">
         <is>
           <t>https://www.doctronic.ai</t>
         </is>
       </c>
-      <c r="C348" s="32" t="inlineStr">
+      <c r="C347" s="32" t="inlineStr">
         <is>
           <t>アメリカ</t>
         </is>
       </c>
-      <c r="D348" s="33" t="inlineStr">
+      <c r="D347" s="33" t="inlineStr">
         <is>
           <t>Doctronic</t>
         </is>
       </c>
-      <c r="E348" s="33" t="inlineStr">
+      <c r="E347" s="33" t="inlineStr">
         <is>
           <t>医療・ヘルスケア</t>
         </is>
       </c>
-      <c r="F348" s="33" t="inlineStr">
+      <c r="F347" s="33" t="inlineStr">
         <is>
           <t>AIに症状を相談できる
 24時間いつでも利用
@@ -25529,30 +25462,30 @@
 医師の診察は米国のみ・有料</t>
         </is>
       </c>
-      <c r="G348" s="34" t="inlineStr">
+      <c r="G347" s="34" t="inlineStr">
         <is>
           <t>無料枠あり</t>
         </is>
       </c>
-      <c r="H348" s="32" t="inlineStr">
+      <c r="H347" s="32" t="inlineStr">
         <is>
           <t>AI相談は無料（オンライン診察は米国のみ・有料）</t>
         </is>
       </c>
-      <c r="I348" s="35" t="inlineStr">
+      <c r="I347" s="35" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J348" s="35" t="n"/>
-      <c r="K348" s="35" t="n"/>
-      <c r="L348" s="35" t="inlineStr">
+      <c r="J347" s="35" t="n"/>
+      <c r="K347" s="35" t="n"/>
+      <c r="L347" s="35" t="inlineStr">
         <is>
           <t>PC＋スマホ</t>
         </is>
       </c>
-      <c r="M348" s="33" t="n"/>
-      <c r="N348" s="33" t="inlineStr">
+      <c r="M347" s="33" t="n"/>
+      <c r="N347" s="33" t="inlineStr">
         <is>
           <t>Ask an AI about your symptoms
 Available 24/7
@@ -25560,65 +25493,701 @@
 Doctor visits are US-only and paid</t>
         </is>
       </c>
+      <c r="O347" s="33" t="inlineStr">
+        <is>
+          <t>AI chat is free (doctor visits US-only, paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="66" customHeight="1" s="29">
+      <c r="A348" s="30" t="inlineStr">
+        <is>
+          <t>Tensor.Art</t>
+        </is>
+      </c>
+      <c r="B348" s="33" t="inlineStr">
+        <is>
+          <t>https://tensor.art</t>
+        </is>
+      </c>
+      <c r="C348" s="32" t="inlineStr">
+        <is>
+          <t>中国（香港）</t>
+        </is>
+      </c>
+      <c r="D348" s="33" t="inlineStr">
+        <is>
+          <t>Echo International HK</t>
+        </is>
+      </c>
+      <c r="E348" s="33" t="inlineStr">
+        <is>
+          <t>画像作成、画像編集</t>
+        </is>
+      </c>
+      <c r="F348" s="33" t="inlineStr">
+        <is>
+          <t>1万以上の画像生成モデルを選べる
+Stable Diffusion・FLUXに対応
+GPU不要でブラウザから生成
+毎日無料クレジット</t>
+        </is>
+      </c>
+      <c r="G348" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H348" s="32" t="inlineStr">
+        <is>
+          <t>毎日もらえる無料クレジットの範囲で生成</t>
+        </is>
+      </c>
+      <c r="I348" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J348" s="35" t="n"/>
+      <c r="K348" s="35" t="n"/>
+      <c r="L348" s="35" t="inlineStr">
+        <is>
+          <t>PC＋スマホ</t>
+        </is>
+      </c>
+      <c r="M348" s="33" t="n"/>
+      <c r="N348" s="33" t="inlineStr">
+        <is>
+          <t>Choose from 10,000+ image models
+Supports Stable Diffusion and FLUX
+Generate in the browser, no GPU needed
+Free credits every day</t>
+        </is>
+      </c>
       <c r="O348" s="33" t="inlineStr">
         <is>
-          <t>AI chat is free (doctor visits US-only, paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="15.75" customHeight="1" s="29">
-      <c r="G349" s="28" t="n"/>
-      <c r="I349" s="28" t="n"/>
-      <c r="J349" s="28" t="n"/>
-      <c r="K349" s="28" t="n"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1" s="29">
-      <c r="G350" s="28" t="n"/>
-      <c r="I350" s="28" t="n"/>
-      <c r="J350" s="28" t="n"/>
-      <c r="K350" s="28" t="n"/>
-    </row>
-    <row r="351" ht="15.75" customHeight="1" s="29">
-      <c r="G351" s="28" t="n"/>
-      <c r="I351" s="28" t="n"/>
-      <c r="J351" s="28" t="n"/>
-      <c r="K351" s="28" t="n"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1" s="29">
-      <c r="G352" s="28" t="n"/>
-      <c r="I352" s="28" t="n"/>
-      <c r="J352" s="28" t="n"/>
-      <c r="K352" s="28" t="n"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1" s="29">
-      <c r="G353" s="28" t="n"/>
-      <c r="I353" s="28" t="n"/>
-      <c r="J353" s="28" t="n"/>
-      <c r="K353" s="28" t="n"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1" s="29">
-      <c r="G354" s="28" t="n"/>
-      <c r="I354" s="28" t="n"/>
-      <c r="J354" s="28" t="n"/>
-      <c r="K354" s="28" t="n"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1" s="29">
-      <c r="G355" s="28" t="n"/>
-      <c r="I355" s="28" t="n"/>
-      <c r="J355" s="28" t="n"/>
-      <c r="K355" s="28" t="n"/>
-    </row>
-    <row r="356" ht="15.75" customHeight="1" s="29">
-      <c r="G356" s="28" t="n"/>
-      <c r="I356" s="28" t="n"/>
-      <c r="J356" s="28" t="n"/>
-      <c r="K356" s="28" t="n"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1" s="29">
-      <c r="G357" s="28" t="n"/>
-      <c r="I357" s="28" t="n"/>
-      <c r="J357" s="28" t="n"/>
-      <c r="K357" s="28" t="n"/>
+          <t>Generate within free daily credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="66" customHeight="1" s="29">
+      <c r="A349" s="30" t="inlineStr">
+        <is>
+          <t>PixAI</t>
+        </is>
+      </c>
+      <c r="B349" s="33" t="inlineStr">
+        <is>
+          <t>https://pixai.art</t>
+        </is>
+      </c>
+      <c r="C349" s="32" t="inlineStr">
+        <is>
+          <t>アメリカ</t>
+        </is>
+      </c>
+      <c r="D349" s="33" t="inlineStr">
+        <is>
+          <t>Mewtant</t>
+        </is>
+      </c>
+      <c r="E349" s="33" t="inlineStr">
+        <is>
+          <t>画像作成</t>
+        </is>
+      </c>
+      <c r="F349" s="33" t="inlineStr">
+        <is>
+          <t>アニメ・イラスト風の画像が得意
+オリジナルキャラクターを作成
+作品を共有するコミュニティ
+毎日無料クレジット</t>
+        </is>
+      </c>
+      <c r="G349" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H349" s="32" t="inlineStr">
+        <is>
+          <t>毎日もらえる無料クレジットの範囲で生成</t>
+        </is>
+      </c>
+      <c r="I349" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J349" s="35" t="n"/>
+      <c r="K349" s="35" t="n"/>
+      <c r="L349" s="35" t="inlineStr">
+        <is>
+          <t>PC＋スマホ</t>
+        </is>
+      </c>
+      <c r="M349" s="33" t="n"/>
+      <c r="N349" s="33" t="inlineStr">
+        <is>
+          <t>Specializes in anime and illustration styles
+Create original characters
+Community for sharing artwork
+Free credits every day</t>
+        </is>
+      </c>
+      <c r="O349" s="33" t="inlineStr">
+        <is>
+          <t>Generate within free daily credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="66" customHeight="1" s="29">
+      <c r="A350" s="30" t="inlineStr">
+        <is>
+          <t>Lovart</t>
+        </is>
+      </c>
+      <c r="B350" s="33" t="inlineStr">
+        <is>
+          <t>https://www.lovart.ai</t>
+        </is>
+      </c>
+      <c r="C350" s="32" t="inlineStr">
+        <is>
+          <t>アメリカ</t>
+        </is>
+      </c>
+      <c r="D350" s="33" t="inlineStr">
+        <is>
+          <t>Resonate International</t>
+        </is>
+      </c>
+      <c r="E350" s="33" t="inlineStr">
+        <is>
+          <t>デザイン・UI/UX、画像作成</t>
+        </is>
+      </c>
+      <c r="F350" s="33" t="inlineStr">
+        <is>
+          <t>指示するだけでデザイン一式を作成
+ロゴ・SNS画像・広告をまとめて
+キャンバス上で部分修正
+毎日無料クレジット</t>
+        </is>
+      </c>
+      <c r="G350" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H350" s="32" t="inlineStr">
+        <is>
+          <t>毎日もらえる無料クレジットの範囲で利用可能</t>
+        </is>
+      </c>
+      <c r="I350" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J350" s="35" t="n"/>
+      <c r="K350" s="35" t="n"/>
+      <c r="L350" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M350" s="33" t="n"/>
+      <c r="N350" s="33" t="inlineStr">
+        <is>
+          <t>Creates a full design set from a prompt
+Logos, social images and ads together
+Edit parts directly on the canvas
+Free credits every day</t>
+        </is>
+      </c>
+      <c r="O350" s="33" t="inlineStr">
+        <is>
+          <t>Use within free daily credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="66" customHeight="1" s="29">
+      <c r="A351" s="30" t="inlineStr">
+        <is>
+          <t>イルシル</t>
+        </is>
+      </c>
+      <c r="B351" s="33" t="inlineStr">
+        <is>
+          <t>https://irusiru.jp</t>
+        </is>
+      </c>
+      <c r="C351" s="32" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D351" s="33" t="inlineStr">
+        <is>
+          <t>イルシル</t>
+        </is>
+      </c>
+      <c r="E351" s="33" t="inlineStr">
+        <is>
+          <t>デザイン・UI/UX、Excel・事務作業、日本語特化</t>
+        </is>
+      </c>
+      <c r="F351" s="33" t="inlineStr">
+        <is>
+          <t>キーワードからスライドを自動作成
+日本のビジネス向けテンプレート
+PowerPoint形式で保存
+日本語の資料作りに強い</t>
+        </is>
+      </c>
+      <c r="G351" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H351" s="32" t="inlineStr">
+        <is>
+          <t>無料プランあり（作成できるスライドは3つまで）</t>
+        </is>
+      </c>
+      <c r="I351" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J351" s="35" t="n"/>
+      <c r="K351" s="35" t="n"/>
+      <c r="L351" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M351" s="33" t="n"/>
+      <c r="N351" s="33" t="inlineStr">
+        <is>
+          <t>Generates slides from keywords
+Templates for Japanese business
+Export to PowerPoint
+Strong for Japanese presentations</t>
+        </is>
+      </c>
+      <c r="O351" s="33" t="inlineStr">
+        <is>
+          <t>Free plan (up to 3 slide decks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="66" customHeight="1" s="29">
+      <c r="A352" s="30" t="inlineStr">
+        <is>
+          <t>Eraser</t>
+        </is>
+      </c>
+      <c r="B352" s="33" t="inlineStr">
+        <is>
+          <t>https://www.eraser.io</t>
+        </is>
+      </c>
+      <c r="C352" s="32" t="inlineStr">
+        <is>
+          <t>アメリカ</t>
+        </is>
+      </c>
+      <c r="D352" s="33" t="inlineStr">
+        <is>
+          <t>Eraser</t>
+        </is>
+      </c>
+      <c r="E352" s="33" t="inlineStr">
+        <is>
+          <t>デザイン・UI/UX、開発者向けツール、要約と構造化</t>
+        </is>
+      </c>
+      <c r="F352" s="33" t="inlineStr">
+        <is>
+          <t>文章から構成図・フローチャートを作成
+システム設計図に強い
+図と文書を1か所で管理
+チームで共同編集</t>
+        </is>
+      </c>
+      <c r="G352" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H352" s="32" t="inlineStr">
+        <is>
+          <t>無料プランあり（ファイル数・AI図の作成回数に制限）</t>
+        </is>
+      </c>
+      <c r="I352" s="35" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J352" s="35" t="n"/>
+      <c r="K352" s="35" t="n"/>
+      <c r="L352" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M352" s="33" t="n"/>
+      <c r="N352" s="33" t="inlineStr">
+        <is>
+          <t>Creates diagrams and flowcharts from text
+Great for system architecture
+Diagrams and docs in one place
+Team collaboration</t>
+        </is>
+      </c>
+      <c r="O352" s="33" t="inlineStr">
+        <is>
+          <t>Free plan (limited files and AI diagrams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="66" customHeight="1" s="29">
+      <c r="A353" s="30" t="inlineStr">
+        <is>
+          <t>Opal</t>
+        </is>
+      </c>
+      <c r="B353" s="33" t="inlineStr">
+        <is>
+          <t>https://opal.google</t>
+        </is>
+      </c>
+      <c r="C353" s="32" t="inlineStr">
+        <is>
+          <t>アメリカ</t>
+        </is>
+      </c>
+      <c r="D353" s="33" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E353" s="33" t="inlineStr">
+        <is>
+          <t>ノーコードでアプリ作成、タスクの自動化（RPA連携）</t>
+        </is>
+      </c>
+      <c r="F353" s="33" t="inlineStr">
+        <is>
+          <t>言葉で説明するだけでAIミニアプリを作成
+手順を図で確認・編集
+作ったアプリを共有
+Google Labsの無料サービス</t>
+        </is>
+      </c>
+      <c r="G353" s="34" t="inlineStr">
+        <is>
+          <t>完全無料</t>
+        </is>
+      </c>
+      <c r="H353" s="32" t="n"/>
+      <c r="I353" s="35" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J353" s="35" t="n"/>
+      <c r="K353" s="35" t="n"/>
+      <c r="L353" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M353" s="33" t="n"/>
+      <c r="N353" s="33" t="inlineStr">
+        <is>
+          <t>Builds AI mini-apps from a description
+View and edit steps visually
+Share the apps you make
+Free Google Labs experiment</t>
+        </is>
+      </c>
+      <c r="O353" s="33" t="n"/>
+    </row>
+    <row r="354" ht="66" customHeight="1" s="29">
+      <c r="A354" s="30" t="inlineStr">
+        <is>
+          <t>Wispr Flow</t>
+        </is>
+      </c>
+      <c r="B354" s="33" t="inlineStr">
+        <is>
+          <t>https://wisprflow.ai</t>
+        </is>
+      </c>
+      <c r="C354" s="32" t="inlineStr">
+        <is>
+          <t>アメリカ</t>
+        </is>
+      </c>
+      <c r="D354" s="33" t="inlineStr">
+        <is>
+          <t>Wispr</t>
+        </is>
+      </c>
+      <c r="E354" s="33" t="inlineStr">
+        <is>
+          <t>音声認識、テキスト生成・AI執筆、Excel・事務作業</t>
+        </is>
+      </c>
+      <c r="F354" s="33" t="inlineStr">
+        <is>
+          <t>話した言葉をどのアプリにも入力
+言い間違いやつなぎ言葉を自動で整える
+Windows・Mac・スマホ対応
+キーボードより速く文章入力</t>
+        </is>
+      </c>
+      <c r="G354" s="34" t="inlineStr">
+        <is>
+          <t>無料枠あり</t>
+        </is>
+      </c>
+      <c r="H354" s="32" t="inlineStr">
+        <is>
+          <t>無料プランあり（PCは週2,000語まで）</t>
+        </is>
+      </c>
+      <c r="I354" s="35" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J354" s="35" t="n"/>
+      <c r="K354" s="35" t="n"/>
+      <c r="L354" s="35" t="inlineStr">
+        <is>
+          <t>PC＋スマホ</t>
+        </is>
+      </c>
+      <c r="M354" s="33" t="n"/>
+      <c r="N354" s="33" t="inlineStr">
+        <is>
+          <t>Dictate into any app
+Cleans up filler words and mistakes
+Works on Windows, Mac and phones
+Write faster than typing</t>
+        </is>
+      </c>
+      <c r="O354" s="33" t="inlineStr">
+        <is>
+          <t>Free plan (2,000 words/week on desktop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="66" customHeight="1" s="29">
+      <c r="A355" s="30" t="inlineStr">
+        <is>
+          <t>VoiceTra</t>
+        </is>
+      </c>
+      <c r="B355" s="33" t="inlineStr">
+        <is>
+          <t>https://voicetra.nict.go.jp</t>
+        </is>
+      </c>
+      <c r="C355" s="32" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D355" s="33" t="inlineStr">
+        <is>
+          <t>情報通信研究機構（NICT）</t>
+        </is>
+      </c>
+      <c r="E355" s="33" t="inlineStr">
+        <is>
+          <t>言語・翻訳、音声認識、日本語特化</t>
+        </is>
+      </c>
+      <c r="F355" s="33" t="inlineStr">
+        <is>
+          <t>話すだけで31言語に翻訳
+1台のスマホで2人が会話
+旅行・接客の会話に強い
+国の研究機関が提供・完全無料</t>
+        </is>
+      </c>
+      <c r="G355" s="34" t="inlineStr">
+        <is>
+          <t>完全無料</t>
+        </is>
+      </c>
+      <c r="H355" s="32" t="n"/>
+      <c r="I355" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J355" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="K355" s="35" t="n"/>
+      <c r="L355" s="35" t="inlineStr">
+        <is>
+          <t>スマホのみ</t>
+        </is>
+      </c>
+      <c r="M355" s="33" t="n"/>
+      <c r="N355" s="33" t="inlineStr">
+        <is>
+          <t>Speak to translate into 31 languages
+Two people can talk on one phone
+Great for travel and customer service
+Free from a Japanese national research institute</t>
+        </is>
+      </c>
+      <c r="O355" s="33" t="n"/>
+    </row>
+    <row r="356" ht="66" customHeight="1" s="29">
+      <c r="A356" s="30" t="inlineStr">
+        <is>
+          <t>AivisSpeech</t>
+        </is>
+      </c>
+      <c r="B356" s="33" t="inlineStr">
+        <is>
+          <t>https://aivis-project.com</t>
+        </is>
+      </c>
+      <c r="C356" s="32" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D356" s="33" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E356" s="33" t="inlineStr">
+        <is>
+          <t>音楽・音声生成、日本語特化</t>
+        </is>
+      </c>
+      <c r="F356" s="33" t="inlineStr">
+        <is>
+          <t>感情豊かで自然な日本語音声
+パソコンで動く無料ソフト
+声のモデルを追加できる
+商用利用もクレジット表記不要</t>
+        </is>
+      </c>
+      <c r="G356" s="34" t="inlineStr">
+        <is>
+          <t>完全無料</t>
+        </is>
+      </c>
+      <c r="H356" s="32" t="n"/>
+      <c r="I356" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J356" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="K356" s="35" t="n"/>
+      <c r="L356" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M356" s="33" t="n"/>
+      <c r="N356" s="33" t="inlineStr">
+        <is>
+          <t>Expressive, natural Japanese voices
+Free software that runs on your PC
+Add more voice models
+Commercial use without credit</t>
+        </is>
+      </c>
+      <c r="O356" s="33" t="n"/>
+    </row>
+    <row r="357" ht="66" customHeight="1" s="29">
+      <c r="A357" s="30" t="inlineStr">
+        <is>
+          <t>COEIROINK</t>
+        </is>
+      </c>
+      <c r="B357" s="33" t="inlineStr">
+        <is>
+          <t>https://coeiroink.com</t>
+        </is>
+      </c>
+      <c r="C357" s="32" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D357" s="33" t="inlineStr">
+        <is>
+          <t>シロワニ</t>
+        </is>
+      </c>
+      <c r="E357" s="33" t="inlineStr">
+        <is>
+          <t>音楽・音声生成、日本語特化</t>
+        </is>
+      </c>
+      <c r="F357" s="33" t="inlineStr">
+        <is>
+          <t>無料の日本語音声合成ソフト
+つくよみちゃんなどキャラクターの声
+Windows・Mac・Linux対応
+商用利用可（クレジット表記が必要）</t>
+        </is>
+      </c>
+      <c r="G357" s="34" t="inlineStr">
+        <is>
+          <t>完全無料</t>
+        </is>
+      </c>
+      <c r="H357" s="32" t="n"/>
+      <c r="I357" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="J357" s="35" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="K357" s="35" t="n"/>
+      <c r="L357" s="35" t="inlineStr">
+        <is>
+          <t>PCのみ</t>
+        </is>
+      </c>
+      <c r="M357" s="33" t="n"/>
+      <c r="N357" s="33" t="inlineStr">
+        <is>
+          <t>Free Japanese speech synthesis software
+Character voices such as Tsukuyomi-chan
+Windows, Mac and Linux
+Commercial use OK (credit required)</t>
+        </is>
+      </c>
+      <c r="O357" s="33" t="n"/>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="29">
       <c r="G358" s="28" t="n"/>
@@ -29418,12 +29987,7 @@
       <c r="J990" s="28" t="n"/>
       <c r="K990" s="28" t="n"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1" s="29">
-      <c r="G991" s="28" t="n"/>
-      <c r="I991" s="28" t="n"/>
-      <c r="J991" s="28" t="n"/>
-      <c r="K991" s="28" t="n"/>
-    </row>
+    <row r="991" ht="15.75" customHeight="1" s="29"/>
     <row r="992" ht="15.75" customHeight="1" s="29"/>
     <row r="993" ht="15.75" customHeight="1" s="29"/>
   </sheetData>
